--- a/docs/docs_tester_cinema.xlsx
+++ b/docs/docs_tester_cinema.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\project\ktpm_hk2_25_26_big_exercise\KTPM_Cinema\docs\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Project\CineFlow\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4698A91A-A754-4DE4-93B6-DC75C1410A31}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{02A811D3-E4BE-4D4D-B712-1223E1AE8537}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="768" yWindow="768" windowWidth="23040" windowHeight="14100" tabRatio="821" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="821" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Cover" sheetId="97" r:id="rId1"/>
@@ -50,7 +50,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="97">
   <si>
     <t>TEST CASE</t>
   </si>
@@ -239,6 +239,146 @@
   <si>
     <t>CFAPI_MD02_User</t>
   </si>
+  <si>
+    <t>1. Register bằng Email + OTP</t>
+  </si>
+  <si>
+    <t>Đăng ký thành công</t>
+  </si>
+  <si>
+    <t>1. Nhập email -&gt; nhận OTP
+2. Nhập đầy đủ thong tin và OTP hợp lệ</t>
+  </si>
+  <si>
+    <t>Tại tài khoản thành công</t>
+  </si>
+  <si>
+    <t>Thiếu OTP</t>
+  </si>
+  <si>
+    <t>Không nhập OTP</t>
+  </si>
+  <si>
+    <t>Báo lỗi "OTP is required"</t>
+  </si>
+  <si>
+    <t>OTP hết hạn hoặc sai</t>
+  </si>
+  <si>
+    <t>Nhập OTP cũ, OTP đã được gửi trước đó 5 phút hoặc OTP sai</t>
+  </si>
+  <si>
+    <t>Báo lỗi "OTP has expired or does not exist"</t>
+  </si>
+  <si>
+    <t>TC3</t>
+  </si>
+  <si>
+    <t>TC4</t>
+  </si>
+  <si>
+    <t>Email đã tồn tại</t>
+  </si>
+  <si>
+    <t>Dùng email đã đăng ký</t>
+  </si>
+  <si>
+    <t>Email sai định dạng</t>
+  </si>
+  <si>
+    <t>email có dạng: abc</t>
+  </si>
+  <si>
+    <t>Thiếu thuộc tính cần thiết</t>
+  </si>
+  <si>
+    <t>Không nhập password hoặc username</t>
+  </si>
+  <si>
+    <t>2. Login bằng Email</t>
+  </si>
+  <si>
+    <t>TC03</t>
+  </si>
+  <si>
+    <t>TC04</t>
+  </si>
+  <si>
+    <t>TC05</t>
+  </si>
+  <si>
+    <t>TC06</t>
+  </si>
+  <si>
+    <t>Login thành công</t>
+  </si>
+  <si>
+    <t>Nhập đúng email và password</t>
+  </si>
+  <si>
+    <t>Email chưa đăng ký</t>
+  </si>
+  <si>
+    <t>Nhập email không tồn tại</t>
+  </si>
+  <si>
+    <t>Thiếu email</t>
+  </si>
+  <si>
+    <t>Không nhập email</t>
+  </si>
+  <si>
+    <t>TC07</t>
+  </si>
+  <si>
+    <t>Password sai định dạng</t>
+  </si>
+  <si>
+    <t>Nhập password có độ dài &lt; 6 hoặc &gt;32
+Nhập password không có chữ hoa….</t>
+  </si>
+  <si>
+    <t>Thiếu password</t>
+  </si>
+  <si>
+    <t>Login thất bại</t>
+  </si>
+  <si>
+    <t>Nhập sai thông tin email hoặc password</t>
+  </si>
+  <si>
+    <t>3. Login bằng Google</t>
+  </si>
+  <si>
+    <t>Login bằng Google email chưa tồn tại</t>
+  </si>
+  <si>
+    <t>Login bằng Google (user cũ)</t>
+  </si>
+  <si>
+    <t>Login bằng Google (user mới)</t>
+  </si>
+  <si>
+    <t>Login bằng Google email đã tồn tại</t>
+  </si>
+  <si>
+    <t>Tạo accout + đăng nhập</t>
+  </si>
+  <si>
+    <t>Đăng nhập thành công</t>
+  </si>
+  <si>
+    <t>Token google gửi sai</t>
+  </si>
+  <si>
+    <t>Gửi token sai</t>
+  </si>
+  <si>
+    <t>User thoát login</t>
+  </si>
+  <si>
+    <t>Thoát bên Google</t>
+  </si>
 </sst>
 </file>
 
@@ -248,7 +388,7 @@
     <numFmt numFmtId="164" formatCode="[$-409]d\-mmm\-yy;@"/>
     <numFmt numFmtId="165" formatCode="0.000"/>
   </numFmts>
-  <fonts count="22">
+  <fonts count="26">
     <font>
       <sz val="11"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -380,8 +520,32 @@
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="128"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color indexed="8"/>
+      <name val="Tahoma"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color indexed="8"/>
+      <name val="Tahoma"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Tahoma"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <color indexed="8"/>
+      <name val="Tahoma"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -418,6 +582,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="35">
     <border>
@@ -889,7 +1059,7 @@
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="131">
+  <cellXfs count="145">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -1145,6 +1315,75 @@
     <xf numFmtId="0" fontId="17" fillId="3" borderId="12" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="15" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="16" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="24" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="18" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="24" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="18" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="25" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="3" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="26" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="28" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="29" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="30" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="27" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="32" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="15" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="16" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="31" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="15" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -1163,9 +1402,6 @@
     <xf numFmtId="0" fontId="9" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="15" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
@@ -1175,71 +1411,45 @@
     <xf numFmtId="0" fontId="3" fillId="3" borderId="17" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="6" borderId="15" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="22" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="24" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="18" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="24" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="18" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="25" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="3" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="26" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="28" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="29" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="30" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="27" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="32" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="15" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="16" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="31" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="15" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="16" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="5">
@@ -1861,9 +2071,9 @@
       <c r="A1" s="31" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="103"/>
-      <c r="C1" s="103"/>
-      <c r="D1" s="103"/>
+      <c r="B1" s="126"/>
+      <c r="C1" s="126"/>
+      <c r="D1" s="126"/>
       <c r="E1" s="32"/>
       <c r="F1" s="32"/>
       <c r="G1" s="32"/>
@@ -1875,9 +2085,9 @@
     </row>
     <row r="2" spans="1:12" s="25" customFormat="1" ht="11.25" customHeight="1" thickBot="1">
       <c r="A2" s="33"/>
-      <c r="B2" s="104"/>
-      <c r="C2" s="104"/>
-      <c r="D2" s="104"/>
+      <c r="B2" s="127"/>
+      <c r="C2" s="127"/>
+      <c r="D2" s="127"/>
       <c r="E2" s="32"/>
       <c r="F2" s="32"/>
       <c r="G2" s="32"/>
@@ -1900,45 +2110,45 @@
       <c r="F3" s="35"/>
       <c r="G3" s="35"/>
       <c r="H3" s="35"/>
-      <c r="I3" s="105"/>
-      <c r="J3" s="105"/>
-      <c r="K3" s="105"/>
+      <c r="I3" s="102"/>
+      <c r="J3" s="102"/>
+      <c r="K3" s="102"/>
       <c r="L3" s="53"/>
     </row>
     <row r="4" spans="1:12" s="26" customFormat="1" ht="13.2">
       <c r="A4" s="36" t="s">
         <v>19</v>
       </c>
-      <c r="B4" s="106" t="s">
+      <c r="B4" s="128" t="s">
         <v>49</v>
       </c>
-      <c r="C4" s="107"/>
-      <c r="D4" s="108"/>
+      <c r="C4" s="129"/>
+      <c r="D4" s="130"/>
       <c r="E4" s="35"/>
       <c r="F4" s="35"/>
       <c r="G4" s="35"/>
       <c r="H4" s="35"/>
-      <c r="I4" s="105"/>
-      <c r="J4" s="105"/>
-      <c r="K4" s="105"/>
+      <c r="I4" s="102"/>
+      <c r="J4" s="102"/>
+      <c r="K4" s="102"/>
       <c r="L4" s="53"/>
     </row>
     <row r="5" spans="1:12" s="27" customFormat="1" ht="15" customHeight="1">
       <c r="A5" s="36" t="s">
         <v>20</v>
       </c>
-      <c r="B5" s="99" t="s">
+      <c r="B5" s="122" t="s">
         <v>44</v>
       </c>
-      <c r="C5" s="100"/>
-      <c r="D5" s="101"/>
+      <c r="C5" s="123"/>
+      <c r="D5" s="124"/>
       <c r="E5" s="37"/>
       <c r="F5" s="37"/>
       <c r="G5" s="37"/>
       <c r="H5" s="37"/>
-      <c r="I5" s="102"/>
-      <c r="J5" s="102"/>
-      <c r="K5" s="102"/>
+      <c r="I5" s="125"/>
+      <c r="J5" s="125"/>
+      <c r="K5" s="125"/>
       <c r="L5" s="54"/>
     </row>
     <row r="6" spans="1:12" s="26" customFormat="1" ht="15" customHeight="1">
@@ -1960,9 +2170,9 @@
       <c r="F6" s="42"/>
       <c r="G6" s="42"/>
       <c r="H6" s="42"/>
-      <c r="I6" s="105"/>
-      <c r="J6" s="105"/>
-      <c r="K6" s="105"/>
+      <c r="I6" s="102"/>
+      <c r="J6" s="102"/>
+      <c r="K6" s="102"/>
       <c r="L6" s="53"/>
     </row>
     <row r="7" spans="1:12" s="26" customFormat="1" ht="15" customHeight="1" thickBot="1">
@@ -1984,16 +2194,16 @@
       <c r="F7" s="47"/>
       <c r="G7" s="47"/>
       <c r="H7" s="47"/>
-      <c r="I7" s="105"/>
-      <c r="J7" s="105"/>
-      <c r="K7" s="105"/>
+      <c r="I7" s="102"/>
+      <c r="J7" s="102"/>
+      <c r="K7" s="102"/>
       <c r="L7" s="53"/>
     </row>
     <row r="8" spans="1:12" s="26" customFormat="1" ht="15" customHeight="1">
-      <c r="A8" s="110"/>
-      <c r="B8" s="110"/>
-      <c r="C8" s="110"/>
-      <c r="D8" s="110"/>
+      <c r="A8" s="103"/>
+      <c r="B8" s="103"/>
+      <c r="C8" s="103"/>
+      <c r="D8" s="103"/>
       <c r="E8" s="42"/>
       <c r="F8" s="42"/>
       <c r="G8" s="42"/>
@@ -2004,76 +2214,76 @@
       <c r="L8" s="53"/>
     </row>
     <row r="9" spans="1:12" s="28" customFormat="1" ht="12" customHeight="1">
-      <c r="A9" s="111" t="s">
+      <c r="A9" s="104" t="s">
         <v>25</v>
       </c>
-      <c r="B9" s="113" t="s">
+      <c r="B9" s="106" t="s">
         <v>26</v>
       </c>
-      <c r="C9" s="111" t="s">
+      <c r="C9" s="104" t="s">
         <v>27</v>
       </c>
-      <c r="D9" s="115" t="s">
+      <c r="D9" s="108" t="s">
         <v>28</v>
       </c>
-      <c r="E9" s="116"/>
-      <c r="F9" s="116"/>
-      <c r="G9" s="117"/>
-      <c r="H9" s="121" t="s">
+      <c r="E9" s="109"/>
+      <c r="F9" s="109"/>
+      <c r="G9" s="110"/>
+      <c r="H9" s="114" t="s">
         <v>29</v>
       </c>
-      <c r="I9" s="122" t="s">
+      <c r="I9" s="115" t="s">
         <v>30</v>
       </c>
-      <c r="J9" s="122" t="s">
+      <c r="J9" s="115" t="s">
         <v>31</v>
       </c>
-      <c r="K9" s="122" t="s">
+      <c r="K9" s="115" t="s">
         <v>32</v>
       </c>
       <c r="L9" s="56"/>
     </row>
     <row r="10" spans="1:12" s="26" customFormat="1" ht="12" customHeight="1">
-      <c r="A10" s="112"/>
-      <c r="B10" s="114"/>
-      <c r="C10" s="112"/>
-      <c r="D10" s="118"/>
-      <c r="E10" s="119"/>
-      <c r="F10" s="119"/>
-      <c r="G10" s="120"/>
-      <c r="H10" s="111"/>
-      <c r="I10" s="111"/>
-      <c r="J10" s="111"/>
-      <c r="K10" s="111"/>
+      <c r="A10" s="105"/>
+      <c r="B10" s="107"/>
+      <c r="C10" s="105"/>
+      <c r="D10" s="111"/>
+      <c r="E10" s="112"/>
+      <c r="F10" s="112"/>
+      <c r="G10" s="113"/>
+      <c r="H10" s="104"/>
+      <c r="I10" s="104"/>
+      <c r="J10" s="104"/>
+      <c r="K10" s="104"/>
       <c r="L10" s="53"/>
     </row>
     <row r="11" spans="1:12" s="29" customFormat="1" ht="15">
-      <c r="A11" s="123"/>
-      <c r="B11" s="123"/>
-      <c r="C11" s="123"/>
-      <c r="D11" s="123"/>
-      <c r="E11" s="123"/>
-      <c r="F11" s="123"/>
-      <c r="G11" s="123"/>
-      <c r="H11" s="123"/>
-      <c r="I11" s="123"/>
-      <c r="J11" s="123"/>
-      <c r="K11" s="124"/>
+      <c r="A11" s="116"/>
+      <c r="B11" s="116"/>
+      <c r="C11" s="116"/>
+      <c r="D11" s="116"/>
+      <c r="E11" s="116"/>
+      <c r="F11" s="116"/>
+      <c r="G11" s="116"/>
+      <c r="H11" s="116"/>
+      <c r="I11" s="116"/>
+      <c r="J11" s="116"/>
+      <c r="K11" s="117"/>
     </row>
     <row r="12" spans="1:12" s="30" customFormat="1" ht="13.2">
-      <c r="A12" s="125" t="s">
+      <c r="A12" s="118" t="s">
         <v>33</v>
       </c>
-      <c r="B12" s="126"/>
-      <c r="C12" s="126"/>
-      <c r="D12" s="126"/>
-      <c r="E12" s="126"/>
-      <c r="F12" s="126"/>
-      <c r="G12" s="126"/>
-      <c r="H12" s="126"/>
-      <c r="I12" s="126"/>
-      <c r="J12" s="126"/>
-      <c r="K12" s="127"/>
+      <c r="B12" s="119"/>
+      <c r="C12" s="119"/>
+      <c r="D12" s="119"/>
+      <c r="E12" s="119"/>
+      <c r="F12" s="119"/>
+      <c r="G12" s="119"/>
+      <c r="H12" s="119"/>
+      <c r="I12" s="119"/>
+      <c r="J12" s="119"/>
+      <c r="K12" s="120"/>
     </row>
     <row r="13" spans="1:12" s="30" customFormat="1" ht="13.2" outlineLevel="1">
       <c r="A13" s="49" t="s">
@@ -2081,9 +2291,9 @@
       </c>
       <c r="B13" s="50"/>
       <c r="C13" s="51"/>
-      <c r="D13" s="128"/>
-      <c r="E13" s="128"/>
-      <c r="F13" s="128"/>
+      <c r="D13" s="121"/>
+      <c r="E13" s="121"/>
+      <c r="F13" s="121"/>
       <c r="G13" s="51"/>
       <c r="H13" s="51"/>
       <c r="I13" s="89"/>
@@ -2094,9 +2304,9 @@
       <c r="A14" s="49"/>
       <c r="B14" s="50"/>
       <c r="C14" s="51"/>
-      <c r="D14" s="109"/>
-      <c r="E14" s="109"/>
-      <c r="F14" s="109"/>
+      <c r="D14" s="99"/>
+      <c r="E14" s="99"/>
+      <c r="F14" s="99"/>
       <c r="G14" s="51"/>
       <c r="H14" s="51"/>
       <c r="I14" s="89"/>
@@ -2107,9 +2317,9 @@
       <c r="A15" s="49"/>
       <c r="B15" s="50"/>
       <c r="C15" s="51"/>
-      <c r="D15" s="109"/>
-      <c r="E15" s="109"/>
-      <c r="F15" s="109"/>
+      <c r="D15" s="99"/>
+      <c r="E15" s="99"/>
+      <c r="F15" s="99"/>
       <c r="G15" s="51"/>
       <c r="H15" s="51"/>
       <c r="I15" s="89"/>
@@ -2120,9 +2330,9 @@
       <c r="A16" s="49"/>
       <c r="B16" s="50"/>
       <c r="C16" s="51"/>
-      <c r="D16" s="109"/>
-      <c r="E16" s="109"/>
-      <c r="F16" s="109"/>
+      <c r="D16" s="99"/>
+      <c r="E16" s="99"/>
+      <c r="F16" s="99"/>
       <c r="G16" s="51"/>
       <c r="H16" s="51"/>
       <c r="I16" s="89"/>
@@ -2133,9 +2343,9 @@
       <c r="A17" s="49"/>
       <c r="B17" s="50"/>
       <c r="C17" s="51"/>
-      <c r="D17" s="109"/>
-      <c r="E17" s="109"/>
-      <c r="F17" s="109"/>
+      <c r="D17" s="99"/>
+      <c r="E17" s="99"/>
+      <c r="F17" s="99"/>
       <c r="G17" s="51"/>
       <c r="H17" s="51"/>
       <c r="I17" s="89"/>
@@ -2146,9 +2356,9 @@
       <c r="A18" s="49"/>
       <c r="B18" s="50"/>
       <c r="C18" s="51"/>
-      <c r="D18" s="109"/>
-      <c r="E18" s="109"/>
-      <c r="F18" s="109"/>
+      <c r="D18" s="99"/>
+      <c r="E18" s="99"/>
+      <c r="F18" s="99"/>
       <c r="G18" s="51"/>
       <c r="H18" s="51"/>
       <c r="I18" s="89"/>
@@ -2159,9 +2369,9 @@
       <c r="A19" s="49"/>
       <c r="B19" s="50"/>
       <c r="C19" s="51"/>
-      <c r="D19" s="109"/>
-      <c r="E19" s="109"/>
-      <c r="F19" s="109"/>
+      <c r="D19" s="99"/>
+      <c r="E19" s="99"/>
+      <c r="F19" s="99"/>
       <c r="G19" s="51"/>
       <c r="H19" s="51"/>
       <c r="I19" s="89"/>
@@ -2169,9 +2379,9 @@
       <c r="K19" s="51"/>
     </row>
     <row r="20" spans="1:11" s="30" customFormat="1" ht="13.2" outlineLevel="1">
-      <c r="A20" s="129"/>
-      <c r="B20" s="130"/>
-      <c r="C20" s="130"/>
+      <c r="A20" s="100"/>
+      <c r="B20" s="101"/>
+      <c r="C20" s="101"/>
       <c r="D20" s="48"/>
       <c r="E20" s="48"/>
       <c r="F20" s="48"/>
@@ -2185,9 +2395,9 @@
       <c r="A21" s="49"/>
       <c r="B21" s="50"/>
       <c r="C21" s="51"/>
-      <c r="D21" s="109"/>
-      <c r="E21" s="109"/>
-      <c r="F21" s="109"/>
+      <c r="D21" s="99"/>
+      <c r="E21" s="99"/>
+      <c r="F21" s="99"/>
       <c r="G21" s="51"/>
       <c r="H21" s="51"/>
       <c r="I21" s="89"/>
@@ -2198,9 +2408,9 @@
       <c r="A22" s="49"/>
       <c r="B22" s="50"/>
       <c r="C22" s="51"/>
-      <c r="D22" s="109"/>
-      <c r="E22" s="109"/>
-      <c r="F22" s="109"/>
+      <c r="D22" s="99"/>
+      <c r="E22" s="99"/>
+      <c r="F22" s="99"/>
       <c r="G22" s="51"/>
       <c r="H22" s="51"/>
       <c r="I22" s="89"/>
@@ -2211,9 +2421,9 @@
       <c r="A23" s="49"/>
       <c r="B23" s="50"/>
       <c r="C23" s="51"/>
-      <c r="D23" s="109"/>
-      <c r="E23" s="109"/>
-      <c r="F23" s="109"/>
+      <c r="D23" s="99"/>
+      <c r="E23" s="99"/>
+      <c r="F23" s="99"/>
       <c r="G23" s="51"/>
       <c r="H23" s="51"/>
       <c r="I23" s="89"/>
@@ -2224,9 +2434,9 @@
       <c r="A24" s="49"/>
       <c r="B24" s="50"/>
       <c r="C24" s="51"/>
-      <c r="D24" s="109"/>
-      <c r="E24" s="109"/>
-      <c r="F24" s="109"/>
+      <c r="D24" s="99"/>
+      <c r="E24" s="99"/>
+      <c r="F24" s="99"/>
       <c r="G24" s="51"/>
       <c r="H24" s="51"/>
       <c r="I24" s="89"/>
@@ -2237,9 +2447,9 @@
       <c r="A25" s="49"/>
       <c r="B25" s="50"/>
       <c r="C25" s="51"/>
-      <c r="D25" s="109"/>
-      <c r="E25" s="109"/>
-      <c r="F25" s="109"/>
+      <c r="D25" s="99"/>
+      <c r="E25" s="99"/>
+      <c r="F25" s="99"/>
       <c r="G25" s="51"/>
       <c r="H25" s="51"/>
       <c r="I25" s="89"/>
@@ -2250,9 +2460,9 @@
       <c r="A26" s="49"/>
       <c r="B26" s="50"/>
       <c r="C26" s="51"/>
-      <c r="D26" s="109"/>
-      <c r="E26" s="109"/>
-      <c r="F26" s="109"/>
+      <c r="D26" s="99"/>
+      <c r="E26" s="99"/>
+      <c r="F26" s="99"/>
       <c r="G26" s="51"/>
       <c r="H26" s="51"/>
       <c r="I26" s="89"/>
@@ -2260,9 +2470,9 @@
       <c r="K26" s="51"/>
     </row>
     <row r="27" spans="1:11" s="30" customFormat="1" ht="13.2" outlineLevel="1">
-      <c r="A27" s="129"/>
-      <c r="B27" s="130"/>
-      <c r="C27" s="130"/>
+      <c r="A27" s="100"/>
+      <c r="B27" s="101"/>
+      <c r="C27" s="101"/>
       <c r="D27" s="48"/>
       <c r="E27" s="48"/>
       <c r="F27" s="48"/>
@@ -2276,9 +2486,9 @@
       <c r="A28" s="49"/>
       <c r="B28" s="50"/>
       <c r="C28" s="51"/>
-      <c r="D28" s="109"/>
-      <c r="E28" s="109"/>
-      <c r="F28" s="109"/>
+      <c r="D28" s="99"/>
+      <c r="E28" s="99"/>
+      <c r="F28" s="99"/>
       <c r="G28" s="51"/>
       <c r="H28" s="51"/>
       <c r="I28" s="89"/>
@@ -2289,9 +2499,9 @@
       <c r="A29" s="49"/>
       <c r="B29" s="50"/>
       <c r="C29" s="51"/>
-      <c r="D29" s="109"/>
-      <c r="E29" s="109"/>
-      <c r="F29" s="109"/>
+      <c r="D29" s="99"/>
+      <c r="E29" s="99"/>
+      <c r="F29" s="99"/>
       <c r="G29" s="51"/>
       <c r="H29" s="51"/>
       <c r="I29" s="89"/>
@@ -2302,9 +2512,9 @@
       <c r="A30" s="49"/>
       <c r="B30" s="50"/>
       <c r="C30" s="51"/>
-      <c r="D30" s="109"/>
-      <c r="E30" s="109"/>
-      <c r="F30" s="109"/>
+      <c r="D30" s="99"/>
+      <c r="E30" s="99"/>
+      <c r="F30" s="99"/>
       <c r="G30" s="51"/>
       <c r="H30" s="51"/>
       <c r="I30" s="89"/>
@@ -2315,9 +2525,9 @@
       <c r="A31" s="49"/>
       <c r="B31" s="50"/>
       <c r="C31" s="51"/>
-      <c r="D31" s="109"/>
-      <c r="E31" s="109"/>
-      <c r="F31" s="109"/>
+      <c r="D31" s="99"/>
+      <c r="E31" s="99"/>
+      <c r="F31" s="99"/>
       <c r="G31" s="51"/>
       <c r="H31" s="51"/>
       <c r="I31" s="89"/>
@@ -2328,9 +2538,9 @@
       <c r="A32" s="49"/>
       <c r="B32" s="50"/>
       <c r="C32" s="51"/>
-      <c r="D32" s="109"/>
-      <c r="E32" s="109"/>
-      <c r="F32" s="109"/>
+      <c r="D32" s="99"/>
+      <c r="E32" s="99"/>
+      <c r="F32" s="99"/>
       <c r="G32" s="51"/>
       <c r="H32" s="51"/>
       <c r="I32" s="89"/>
@@ -2341,9 +2551,1300 @@
       <c r="A33" s="49"/>
       <c r="B33" s="50"/>
       <c r="C33" s="51"/>
-      <c r="D33" s="109"/>
-      <c r="E33" s="109"/>
-      <c r="F33" s="109"/>
+      <c r="D33" s="99"/>
+      <c r="E33" s="99"/>
+      <c r="F33" s="99"/>
+      <c r="G33" s="51"/>
+      <c r="H33" s="51"/>
+      <c r="I33" s="89"/>
+      <c r="J33" s="51"/>
+      <c r="K33" s="51"/>
+    </row>
+    <row r="34" spans="1:11" ht="12" customHeight="1"/>
+    <row r="35" spans="1:11" ht="12" customHeight="1"/>
+    <row r="36" spans="1:11" ht="12" customHeight="1"/>
+    <row r="37" spans="1:11" ht="12" customHeight="1"/>
+    <row r="38" spans="1:11" ht="12" customHeight="1"/>
+    <row r="39" spans="1:11" ht="12" customHeight="1"/>
+    <row r="40" spans="1:11" ht="12" customHeight="1"/>
+    <row r="41" spans="1:11" ht="12" customHeight="1"/>
+    <row r="42" spans="1:11" ht="12" customHeight="1"/>
+    <row r="43" spans="1:11" ht="12" customHeight="1"/>
+    <row r="44" spans="1:11" ht="12" customHeight="1"/>
+    <row r="45" spans="1:11" ht="12" customHeight="1"/>
+    <row r="46" spans="1:11" ht="12" customHeight="1"/>
+    <row r="47" spans="1:11" ht="12" customHeight="1"/>
+    <row r="48" spans="1:11" ht="12" customHeight="1"/>
+    <row r="49" ht="12" customHeight="1"/>
+    <row r="50" ht="12" customHeight="1"/>
+    <row r="51" ht="12" customHeight="1"/>
+    <row r="52" ht="12" customHeight="1"/>
+    <row r="53" ht="12" customHeight="1"/>
+    <row r="54" ht="12" customHeight="1"/>
+    <row r="55" ht="12" customHeight="1"/>
+    <row r="56" ht="12" customHeight="1"/>
+    <row r="57" ht="12" customHeight="1"/>
+    <row r="58" ht="12" customHeight="1"/>
+    <row r="59" ht="12" customHeight="1"/>
+    <row r="60" ht="12" customHeight="1"/>
+    <row r="61" ht="12" customHeight="1"/>
+    <row r="62" ht="12" customHeight="1"/>
+    <row r="63" ht="12" customHeight="1"/>
+    <row r="64" ht="12" customHeight="1"/>
+    <row r="65" ht="12" customHeight="1"/>
+    <row r="66" ht="12" customHeight="1"/>
+    <row r="67" ht="12" customHeight="1"/>
+    <row r="68" ht="12" customHeight="1"/>
+    <row r="69" ht="12" customHeight="1"/>
+    <row r="70" ht="12" customHeight="1"/>
+    <row r="71" ht="12" customHeight="1"/>
+  </sheetData>
+  <mergeCells count="41">
+    <mergeCell ref="B5:D5"/>
+    <mergeCell ref="I5:K5"/>
+    <mergeCell ref="B1:D2"/>
+    <mergeCell ref="B3:D3"/>
+    <mergeCell ref="I3:K3"/>
+    <mergeCell ref="B4:D4"/>
+    <mergeCell ref="I4:K4"/>
+    <mergeCell ref="D15:F15"/>
+    <mergeCell ref="I6:K6"/>
+    <mergeCell ref="I7:K7"/>
+    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="A9:A10"/>
+    <mergeCell ref="B9:B10"/>
+    <mergeCell ref="C9:C10"/>
+    <mergeCell ref="D9:G10"/>
+    <mergeCell ref="H9:H10"/>
+    <mergeCell ref="I9:I10"/>
+    <mergeCell ref="J9:J10"/>
+    <mergeCell ref="K9:K10"/>
+    <mergeCell ref="A11:K11"/>
+    <mergeCell ref="A12:K12"/>
+    <mergeCell ref="D13:F13"/>
+    <mergeCell ref="D14:F14"/>
+    <mergeCell ref="A27:C27"/>
+    <mergeCell ref="D16:F16"/>
+    <mergeCell ref="D17:F17"/>
+    <mergeCell ref="D18:F18"/>
+    <mergeCell ref="D19:F19"/>
+    <mergeCell ref="A20:C20"/>
+    <mergeCell ref="D21:F21"/>
+    <mergeCell ref="D33:F33"/>
+    <mergeCell ref="D22:F22"/>
+    <mergeCell ref="D23:F23"/>
+    <mergeCell ref="D24:F24"/>
+    <mergeCell ref="D25:F25"/>
+    <mergeCell ref="D26:F26"/>
+    <mergeCell ref="D28:F28"/>
+    <mergeCell ref="D29:F29"/>
+    <mergeCell ref="D30:F30"/>
+    <mergeCell ref="D31:F31"/>
+    <mergeCell ref="D32:F32"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <sheetPr>
+    <outlinePr summaryBelow="0" summaryRight="0"/>
+  </sheetPr>
+  <dimension ref="A1:K72"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="13.8" outlineLevelRow="1"/>
+  <cols>
+    <col min="1" max="1" width="18" customWidth="1"/>
+    <col min="2" max="2" width="18.109375" customWidth="1"/>
+    <col min="3" max="3" width="42.109375" customWidth="1"/>
+    <col min="4" max="4" width="28.109375" customWidth="1"/>
+    <col min="5" max="5" width="13.109375" customWidth="1"/>
+    <col min="6" max="6" width="18.44140625" hidden="1" customWidth="1"/>
+    <col min="7" max="7" width="38" customWidth="1"/>
+    <col min="8" max="8" width="17.109375" customWidth="1"/>
+    <col min="9" max="9" width="9" style="6"/>
+    <col min="10" max="10" width="18" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:11" s="25" customFormat="1" ht="12.75" customHeight="1">
+      <c r="A1" s="31" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="126"/>
+      <c r="C1" s="126"/>
+      <c r="D1" s="126"/>
+      <c r="E1" s="32"/>
+      <c r="F1" s="32"/>
+      <c r="G1" s="32"/>
+      <c r="H1" s="32"/>
+      <c r="I1" s="52"/>
+      <c r="J1" s="32"/>
+      <c r="K1" s="33"/>
+    </row>
+    <row r="2" spans="1:11" s="25" customFormat="1" ht="11.25" customHeight="1" thickBot="1">
+      <c r="A2" s="33"/>
+      <c r="B2" s="127"/>
+      <c r="C2" s="127"/>
+      <c r="D2" s="127"/>
+      <c r="E2" s="32"/>
+      <c r="F2" s="32"/>
+      <c r="G2" s="32"/>
+      <c r="H2" s="32"/>
+      <c r="I2" s="52"/>
+      <c r="J2" s="32"/>
+      <c r="K2" s="33"/>
+    </row>
+    <row r="3" spans="1:11" s="26" customFormat="1" ht="15" customHeight="1">
+      <c r="A3" s="34" t="s">
+        <v>18</v>
+      </c>
+      <c r="B3" s="96" t="s">
+        <v>4</v>
+      </c>
+      <c r="C3" s="96"/>
+      <c r="D3" s="97"/>
+      <c r="E3" s="35"/>
+      <c r="F3" s="35"/>
+      <c r="G3" s="35"/>
+      <c r="H3" s="102"/>
+      <c r="I3" s="102"/>
+      <c r="J3" s="102"/>
+      <c r="K3" s="53"/>
+    </row>
+    <row r="4" spans="1:11" s="26" customFormat="1" ht="13.2">
+      <c r="A4" s="36" t="s">
+        <v>19</v>
+      </c>
+      <c r="B4" s="128" t="s">
+        <v>50</v>
+      </c>
+      <c r="C4" s="129"/>
+      <c r="D4" s="130"/>
+      <c r="E4" s="35"/>
+      <c r="F4" s="35"/>
+      <c r="G4" s="35"/>
+      <c r="H4" s="102"/>
+      <c r="I4" s="102"/>
+      <c r="J4" s="102"/>
+      <c r="K4" s="53"/>
+    </row>
+    <row r="5" spans="1:11" s="27" customFormat="1" ht="15" customHeight="1">
+      <c r="A5" s="36" t="s">
+        <v>20</v>
+      </c>
+      <c r="B5" s="122" t="s">
+        <v>44</v>
+      </c>
+      <c r="C5" s="123"/>
+      <c r="D5" s="124"/>
+      <c r="E5" s="37"/>
+      <c r="F5" s="37"/>
+      <c r="G5" s="37"/>
+      <c r="H5" s="125"/>
+      <c r="I5" s="125"/>
+      <c r="J5" s="125"/>
+      <c r="K5" s="54"/>
+    </row>
+    <row r="6" spans="1:11" s="26" customFormat="1" ht="15" customHeight="1">
+      <c r="A6" s="38" t="s">
+        <v>21</v>
+      </c>
+      <c r="B6" s="39">
+        <f>COUNTIF(I12:I34,"Pass")</f>
+        <v>0</v>
+      </c>
+      <c r="C6" s="40" t="s">
+        <v>22</v>
+      </c>
+      <c r="D6" s="41">
+        <f>COUNTIF(I10:I753,"Pending")</f>
+        <v>0</v>
+      </c>
+      <c r="E6" s="42"/>
+      <c r="F6" s="42"/>
+      <c r="G6" s="42"/>
+      <c r="H6" s="102"/>
+      <c r="I6" s="102"/>
+      <c r="J6" s="102"/>
+      <c r="K6" s="53"/>
+    </row>
+    <row r="7" spans="1:11" s="26" customFormat="1" ht="15" customHeight="1" thickBot="1">
+      <c r="A7" s="43" t="s">
+        <v>23</v>
+      </c>
+      <c r="B7" s="44">
+        <f>COUNTIF(I12:I34,"Fail")</f>
+        <v>0</v>
+      </c>
+      <c r="C7" s="45" t="s">
+        <v>24</v>
+      </c>
+      <c r="D7" s="46">
+        <f>COUNTIF(A12:A34, "TC*")</f>
+        <v>18</v>
+      </c>
+      <c r="E7" s="47"/>
+      <c r="F7" s="47"/>
+      <c r="G7" s="47"/>
+      <c r="H7" s="102"/>
+      <c r="I7" s="102"/>
+      <c r="J7" s="102"/>
+      <c r="K7" s="53"/>
+    </row>
+    <row r="8" spans="1:11" s="26" customFormat="1" ht="15" customHeight="1">
+      <c r="A8" s="103"/>
+      <c r="B8" s="103"/>
+      <c r="C8" s="103"/>
+      <c r="D8" s="103"/>
+      <c r="E8" s="42"/>
+      <c r="F8" s="42"/>
+      <c r="G8" s="42"/>
+      <c r="H8" s="42"/>
+      <c r="I8" s="55"/>
+      <c r="J8" s="55"/>
+      <c r="K8" s="53"/>
+    </row>
+    <row r="9" spans="1:11" s="28" customFormat="1" ht="12" customHeight="1">
+      <c r="A9" s="104" t="s">
+        <v>25</v>
+      </c>
+      <c r="B9" s="106" t="s">
+        <v>26</v>
+      </c>
+      <c r="C9" s="104" t="s">
+        <v>27</v>
+      </c>
+      <c r="D9" s="108" t="s">
+        <v>28</v>
+      </c>
+      <c r="E9" s="109"/>
+      <c r="F9" s="110"/>
+      <c r="G9" s="114" t="s">
+        <v>29</v>
+      </c>
+      <c r="H9" s="115" t="s">
+        <v>30</v>
+      </c>
+      <c r="I9" s="115" t="s">
+        <v>31</v>
+      </c>
+      <c r="J9" s="115" t="s">
+        <v>32</v>
+      </c>
+      <c r="K9" s="56"/>
+    </row>
+    <row r="10" spans="1:11" s="26" customFormat="1" ht="12" customHeight="1">
+      <c r="A10" s="105"/>
+      <c r="B10" s="107"/>
+      <c r="C10" s="105"/>
+      <c r="D10" s="111"/>
+      <c r="E10" s="112"/>
+      <c r="F10" s="113"/>
+      <c r="G10" s="104"/>
+      <c r="H10" s="104"/>
+      <c r="I10" s="104"/>
+      <c r="J10" s="104"/>
+      <c r="K10" s="53"/>
+    </row>
+    <row r="11" spans="1:11" s="29" customFormat="1" ht="15">
+      <c r="A11" s="116"/>
+      <c r="B11" s="116"/>
+      <c r="C11" s="116"/>
+      <c r="D11" s="116"/>
+      <c r="E11" s="116"/>
+      <c r="F11" s="116"/>
+      <c r="G11" s="116"/>
+      <c r="H11" s="116"/>
+      <c r="I11" s="116"/>
+      <c r="J11" s="117"/>
+    </row>
+    <row r="12" spans="1:11" s="30" customFormat="1" ht="13.2">
+      <c r="A12" s="118" t="s">
+        <v>51</v>
+      </c>
+      <c r="B12" s="119"/>
+      <c r="C12" s="119"/>
+      <c r="D12" s="119"/>
+      <c r="E12" s="119"/>
+      <c r="F12" s="119"/>
+      <c r="G12" s="119"/>
+      <c r="H12" s="119"/>
+      <c r="I12" s="119"/>
+      <c r="J12" s="120"/>
+    </row>
+    <row r="13" spans="1:11" s="30" customFormat="1" ht="26.4" outlineLevel="1">
+      <c r="A13" s="49" t="s">
+        <v>45</v>
+      </c>
+      <c r="B13" s="50" t="s">
+        <v>52</v>
+      </c>
+      <c r="C13" s="51" t="s">
+        <v>53</v>
+      </c>
+      <c r="D13" s="143" t="s">
+        <v>54</v>
+      </c>
+      <c r="E13" s="144"/>
+      <c r="F13" s="51"/>
+      <c r="G13" s="51"/>
+      <c r="H13" s="89"/>
+      <c r="I13" s="51"/>
+      <c r="J13" s="51"/>
+    </row>
+    <row r="14" spans="1:11" s="30" customFormat="1" ht="13.2" outlineLevel="1">
+      <c r="A14" s="49" t="s">
+        <v>47</v>
+      </c>
+      <c r="B14" s="50" t="s">
+        <v>55</v>
+      </c>
+      <c r="C14" s="51" t="s">
+        <v>56</v>
+      </c>
+      <c r="D14" s="139" t="s">
+        <v>57</v>
+      </c>
+      <c r="E14" s="140"/>
+      <c r="F14" s="51"/>
+      <c r="G14" s="51"/>
+      <c r="H14" s="89"/>
+      <c r="I14" s="51"/>
+      <c r="J14" s="51"/>
+    </row>
+    <row r="15" spans="1:11" s="30" customFormat="1" ht="26.4" outlineLevel="1">
+      <c r="A15" s="49" t="s">
+        <v>70</v>
+      </c>
+      <c r="B15" s="50" t="s">
+        <v>58</v>
+      </c>
+      <c r="C15" s="51" t="s">
+        <v>59</v>
+      </c>
+      <c r="D15" s="139" t="s">
+        <v>60</v>
+      </c>
+      <c r="E15" s="140"/>
+      <c r="F15" s="51"/>
+      <c r="G15" s="51"/>
+      <c r="H15" s="89"/>
+      <c r="I15" s="51"/>
+      <c r="J15" s="51"/>
+    </row>
+    <row r="16" spans="1:11" s="30" customFormat="1" ht="13.2" outlineLevel="1">
+      <c r="A16" s="49" t="s">
+        <v>71</v>
+      </c>
+      <c r="B16" s="50" t="s">
+        <v>63</v>
+      </c>
+      <c r="C16" s="51" t="s">
+        <v>64</v>
+      </c>
+      <c r="D16" s="139"/>
+      <c r="E16" s="140"/>
+      <c r="F16" s="51"/>
+      <c r="G16" s="51"/>
+      <c r="H16" s="89"/>
+      <c r="I16" s="51"/>
+      <c r="J16" s="51"/>
+    </row>
+    <row r="17" spans="1:10" s="30" customFormat="1" ht="13.2" outlineLevel="1">
+      <c r="A17" s="49" t="s">
+        <v>72</v>
+      </c>
+      <c r="B17" s="50" t="s">
+        <v>65</v>
+      </c>
+      <c r="C17" s="51" t="s">
+        <v>66</v>
+      </c>
+      <c r="D17" s="139"/>
+      <c r="E17" s="140"/>
+      <c r="F17" s="51"/>
+      <c r="G17" s="51"/>
+      <c r="H17" s="89"/>
+      <c r="I17" s="51"/>
+      <c r="J17" s="51"/>
+    </row>
+    <row r="18" spans="1:10" s="30" customFormat="1" ht="26.4" outlineLevel="1">
+      <c r="A18" s="49" t="s">
+        <v>73</v>
+      </c>
+      <c r="B18" s="50" t="s">
+        <v>67</v>
+      </c>
+      <c r="C18" s="51" t="s">
+        <v>68</v>
+      </c>
+      <c r="D18" s="139"/>
+      <c r="E18" s="140"/>
+      <c r="F18" s="51"/>
+      <c r="G18" s="51"/>
+      <c r="H18" s="89"/>
+      <c r="I18" s="51"/>
+      <c r="J18" s="51"/>
+    </row>
+    <row r="19" spans="1:10" s="30" customFormat="1" ht="26.4" outlineLevel="1">
+      <c r="A19" s="49" t="s">
+        <v>80</v>
+      </c>
+      <c r="B19" s="50" t="s">
+        <v>81</v>
+      </c>
+      <c r="C19" s="131" t="s">
+        <v>82</v>
+      </c>
+      <c r="D19" s="139"/>
+      <c r="E19" s="140"/>
+      <c r="F19" s="51"/>
+      <c r="G19" s="51"/>
+      <c r="H19" s="89"/>
+      <c r="I19" s="51"/>
+      <c r="J19" s="51"/>
+    </row>
+    <row r="20" spans="1:10" s="30" customFormat="1" ht="13.2" outlineLevel="1">
+      <c r="A20" s="118" t="s">
+        <v>69</v>
+      </c>
+      <c r="B20" s="119"/>
+      <c r="C20" s="119"/>
+      <c r="D20" s="48"/>
+      <c r="E20" s="48"/>
+      <c r="F20" s="48"/>
+      <c r="G20" s="48"/>
+      <c r="H20" s="48"/>
+      <c r="I20" s="48"/>
+      <c r="J20" s="57"/>
+    </row>
+    <row r="21" spans="1:10" s="30" customFormat="1" ht="13.2" outlineLevel="1">
+      <c r="A21" s="49" t="s">
+        <v>45</v>
+      </c>
+      <c r="B21" s="50" t="s">
+        <v>74</v>
+      </c>
+      <c r="C21" s="51" t="s">
+        <v>75</v>
+      </c>
+      <c r="D21" s="139"/>
+      <c r="E21" s="140"/>
+      <c r="F21" s="51"/>
+      <c r="G21" s="51"/>
+      <c r="H21" s="89"/>
+      <c r="I21" s="51"/>
+      <c r="J21" s="51"/>
+    </row>
+    <row r="22" spans="1:10" s="30" customFormat="1" ht="13.2" outlineLevel="1">
+      <c r="A22" s="49" t="s">
+        <v>47</v>
+      </c>
+      <c r="B22" s="50" t="s">
+        <v>76</v>
+      </c>
+      <c r="C22" s="51" t="s">
+        <v>77</v>
+      </c>
+      <c r="D22" s="139"/>
+      <c r="E22" s="140"/>
+      <c r="F22" s="51"/>
+      <c r="G22" s="51"/>
+      <c r="H22" s="89"/>
+      <c r="I22" s="51"/>
+      <c r="J22" s="51"/>
+    </row>
+    <row r="23" spans="1:10" s="30" customFormat="1" ht="13.2" outlineLevel="1">
+      <c r="A23" s="49" t="s">
+        <v>70</v>
+      </c>
+      <c r="B23" s="50" t="s">
+        <v>65</v>
+      </c>
+      <c r="C23" s="51"/>
+      <c r="D23" s="139"/>
+      <c r="E23" s="140"/>
+      <c r="F23" s="51"/>
+      <c r="G23" s="51"/>
+      <c r="H23" s="89"/>
+      <c r="I23" s="51"/>
+      <c r="J23" s="51"/>
+    </row>
+    <row r="24" spans="1:10" s="30" customFormat="1" ht="13.2" outlineLevel="1">
+      <c r="A24" s="49" t="s">
+        <v>71</v>
+      </c>
+      <c r="B24" s="50" t="s">
+        <v>78</v>
+      </c>
+      <c r="C24" s="51" t="s">
+        <v>79</v>
+      </c>
+      <c r="D24" s="139"/>
+      <c r="E24" s="140"/>
+      <c r="F24" s="51"/>
+      <c r="G24" s="51"/>
+      <c r="H24" s="89"/>
+      <c r="I24" s="51"/>
+      <c r="J24" s="51"/>
+    </row>
+    <row r="25" spans="1:10" s="30" customFormat="1" ht="13.2" outlineLevel="1">
+      <c r="A25" s="49" t="s">
+        <v>72</v>
+      </c>
+      <c r="B25" s="50" t="s">
+        <v>83</v>
+      </c>
+      <c r="C25" s="51" t="s">
+        <v>68</v>
+      </c>
+      <c r="D25" s="139"/>
+      <c r="E25" s="140"/>
+      <c r="F25" s="51"/>
+      <c r="G25" s="51"/>
+      <c r="H25" s="89"/>
+      <c r="I25" s="51"/>
+      <c r="J25" s="51"/>
+    </row>
+    <row r="26" spans="1:10" s="30" customFormat="1" ht="26.4" outlineLevel="1">
+      <c r="A26" s="49" t="s">
+        <v>73</v>
+      </c>
+      <c r="B26" s="50" t="s">
+        <v>81</v>
+      </c>
+      <c r="C26" s="131" t="s">
+        <v>82</v>
+      </c>
+      <c r="D26" s="51"/>
+      <c r="E26" s="51"/>
+      <c r="F26" s="51"/>
+      <c r="G26" s="51"/>
+      <c r="H26" s="89"/>
+      <c r="I26" s="51"/>
+      <c r="J26" s="51"/>
+    </row>
+    <row r="27" spans="1:10" s="30" customFormat="1" ht="18" customHeight="1" outlineLevel="1">
+      <c r="A27" s="132" t="s">
+        <v>80</v>
+      </c>
+      <c r="B27" s="132" t="s">
+        <v>84</v>
+      </c>
+      <c r="C27" s="132" t="s">
+        <v>85</v>
+      </c>
+      <c r="D27" s="139"/>
+      <c r="E27" s="140"/>
+      <c r="F27" s="51"/>
+      <c r="G27" s="51"/>
+      <c r="H27" s="89"/>
+      <c r="I27" s="51"/>
+      <c r="J27" s="51"/>
+    </row>
+    <row r="28" spans="1:10" s="30" customFormat="1" ht="13.2" outlineLevel="1">
+      <c r="A28" s="133" t="s">
+        <v>86</v>
+      </c>
+      <c r="B28" s="119"/>
+      <c r="C28" s="119"/>
+      <c r="D28" s="48"/>
+      <c r="E28" s="48"/>
+      <c r="F28" s="48"/>
+      <c r="G28" s="48"/>
+      <c r="H28" s="48"/>
+      <c r="I28" s="48"/>
+      <c r="J28" s="57"/>
+    </row>
+    <row r="29" spans="1:10" s="30" customFormat="1" ht="26.4" outlineLevel="1">
+      <c r="A29" s="134" t="s">
+        <v>45</v>
+      </c>
+      <c r="B29" s="135" t="s">
+        <v>88</v>
+      </c>
+      <c r="C29" s="136" t="s">
+        <v>90</v>
+      </c>
+      <c r="D29" s="137" t="s">
+        <v>92</v>
+      </c>
+      <c r="F29" s="51"/>
+      <c r="G29" s="51"/>
+      <c r="H29" s="89"/>
+      <c r="I29" s="51"/>
+      <c r="J29" s="51"/>
+    </row>
+    <row r="30" spans="1:10" s="30" customFormat="1" ht="26.4" outlineLevel="1">
+      <c r="A30" s="134" t="s">
+        <v>47</v>
+      </c>
+      <c r="B30" s="135" t="s">
+        <v>89</v>
+      </c>
+      <c r="C30" s="136" t="s">
+        <v>87</v>
+      </c>
+      <c r="D30" s="141" t="s">
+        <v>91</v>
+      </c>
+      <c r="E30" s="142"/>
+      <c r="F30" s="51"/>
+      <c r="G30" s="51"/>
+      <c r="H30" s="89"/>
+      <c r="I30" s="51"/>
+      <c r="J30" s="51"/>
+    </row>
+    <row r="31" spans="1:10" s="30" customFormat="1" ht="26.4" outlineLevel="1">
+      <c r="A31" s="134" t="s">
+        <v>61</v>
+      </c>
+      <c r="B31" s="135" t="s">
+        <v>93</v>
+      </c>
+      <c r="C31" s="138" t="s">
+        <v>94</v>
+      </c>
+      <c r="D31" s="139"/>
+      <c r="E31" s="140"/>
+      <c r="F31" s="51"/>
+      <c r="G31" s="51"/>
+      <c r="H31" s="89"/>
+      <c r="I31" s="51"/>
+      <c r="J31" s="51"/>
+    </row>
+    <row r="32" spans="1:10" s="30" customFormat="1" ht="13.2" outlineLevel="1">
+      <c r="A32" s="134" t="s">
+        <v>62</v>
+      </c>
+      <c r="B32" s="135" t="s">
+        <v>95</v>
+      </c>
+      <c r="C32" s="138" t="s">
+        <v>96</v>
+      </c>
+      <c r="D32" s="139"/>
+      <c r="E32" s="140"/>
+      <c r="F32" s="51"/>
+      <c r="G32" s="51"/>
+      <c r="H32" s="89"/>
+      <c r="I32" s="51"/>
+      <c r="J32" s="51"/>
+    </row>
+    <row r="33" spans="1:10" s="30" customFormat="1" ht="13.2" outlineLevel="1">
+      <c r="A33" s="49"/>
+      <c r="B33" s="50"/>
+      <c r="C33" s="51"/>
+      <c r="D33" s="139"/>
+      <c r="E33" s="140"/>
+      <c r="F33" s="51"/>
+      <c r="G33" s="51"/>
+      <c r="H33" s="89"/>
+      <c r="I33" s="51"/>
+      <c r="J33" s="51"/>
+    </row>
+    <row r="34" spans="1:10" s="30" customFormat="1" ht="13.8" customHeight="1" outlineLevel="1">
+      <c r="A34" s="49"/>
+      <c r="B34" s="50"/>
+      <c r="C34" s="51"/>
+      <c r="D34" s="139"/>
+      <c r="E34" s="140"/>
+      <c r="F34" s="51"/>
+      <c r="G34" s="51"/>
+      <c r="H34" s="89"/>
+      <c r="I34" s="51"/>
+      <c r="J34" s="51"/>
+    </row>
+    <row r="35" spans="1:10" ht="12" customHeight="1"/>
+    <row r="36" spans="1:10" ht="12" customHeight="1"/>
+    <row r="37" spans="1:10" ht="12" customHeight="1"/>
+    <row r="38" spans="1:10" ht="12" customHeight="1"/>
+    <row r="39" spans="1:10" ht="12" customHeight="1"/>
+    <row r="40" spans="1:10" ht="12" customHeight="1"/>
+    <row r="41" spans="1:10" ht="12" customHeight="1"/>
+    <row r="42" spans="1:10" ht="12" customHeight="1"/>
+    <row r="43" spans="1:10" ht="12" customHeight="1"/>
+    <row r="44" spans="1:10" ht="12" customHeight="1"/>
+    <row r="45" spans="1:10" ht="12" customHeight="1"/>
+    <row r="46" spans="1:10" ht="12" customHeight="1"/>
+    <row r="47" spans="1:10" ht="12" customHeight="1"/>
+    <row r="48" spans="1:10" ht="12" customHeight="1"/>
+    <row r="49" ht="12" customHeight="1"/>
+    <row r="50" ht="12" customHeight="1"/>
+    <row r="51" ht="12" customHeight="1"/>
+    <row r="52" ht="12" customHeight="1"/>
+    <row r="53" ht="12" customHeight="1"/>
+    <row r="54" ht="12" customHeight="1"/>
+    <row r="55" ht="12" customHeight="1"/>
+    <row r="56" ht="12" customHeight="1"/>
+    <row r="57" ht="12" customHeight="1"/>
+    <row r="58" ht="12" customHeight="1"/>
+    <row r="59" ht="12" customHeight="1"/>
+    <row r="60" ht="12" customHeight="1"/>
+    <row r="61" ht="12" customHeight="1"/>
+    <row r="62" ht="12" customHeight="1"/>
+    <row r="63" ht="12" customHeight="1"/>
+    <row r="64" ht="12" customHeight="1"/>
+    <row r="65" ht="12" customHeight="1"/>
+    <row r="66" ht="12" customHeight="1"/>
+    <row r="67" ht="12" customHeight="1"/>
+    <row r="68" ht="12" customHeight="1"/>
+    <row r="69" ht="12" customHeight="1"/>
+    <row r="70" ht="12" customHeight="1"/>
+    <row r="71" ht="12" customHeight="1"/>
+    <row r="72" ht="12" customHeight="1"/>
+  </sheetData>
+  <mergeCells count="40">
+    <mergeCell ref="D13:E13"/>
+    <mergeCell ref="D17:E17"/>
+    <mergeCell ref="D16:E16"/>
+    <mergeCell ref="D15:E15"/>
+    <mergeCell ref="D14:E14"/>
+    <mergeCell ref="D18:E18"/>
+    <mergeCell ref="B1:D2"/>
+    <mergeCell ref="D9:F10"/>
+    <mergeCell ref="B3:D3"/>
+    <mergeCell ref="D19:E19"/>
+    <mergeCell ref="A20:C20"/>
+    <mergeCell ref="D27:E27"/>
+    <mergeCell ref="A28:C28"/>
+    <mergeCell ref="D34:E34"/>
+    <mergeCell ref="D21:E21"/>
+    <mergeCell ref="D30:E30"/>
+    <mergeCell ref="D22:E22"/>
+    <mergeCell ref="D23:E23"/>
+    <mergeCell ref="D24:E24"/>
+    <mergeCell ref="D25:E25"/>
+    <mergeCell ref="D31:E31"/>
+    <mergeCell ref="D32:E32"/>
+    <mergeCell ref="D33:E33"/>
+    <mergeCell ref="H6:J6"/>
+    <mergeCell ref="H7:J7"/>
+    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="A11:J11"/>
+    <mergeCell ref="A12:J12"/>
+    <mergeCell ref="A9:A10"/>
+    <mergeCell ref="B9:B10"/>
+    <mergeCell ref="C9:C10"/>
+    <mergeCell ref="G9:G10"/>
+    <mergeCell ref="H9:H10"/>
+    <mergeCell ref="I9:I10"/>
+    <mergeCell ref="J9:J10"/>
+    <mergeCell ref="H3:J3"/>
+    <mergeCell ref="B4:D4"/>
+    <mergeCell ref="H4:J4"/>
+    <mergeCell ref="B5:D5"/>
+    <mergeCell ref="H5:J5"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
+  <headerFooter alignWithMargins="0"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{20690ED2-4B8F-4386-AEC9-67E105CBDE46}">
+  <dimension ref="A1:L71"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="13.8" outlineLevelRow="1"/>
+  <cols>
+    <col min="1" max="1" width="18" customWidth="1"/>
+    <col min="2" max="2" width="18.109375" customWidth="1"/>
+    <col min="3" max="3" width="42.109375" customWidth="1"/>
+    <col min="6" max="6" width="23.6640625" customWidth="1"/>
+    <col min="7" max="7" width="18.44140625" hidden="1" customWidth="1"/>
+    <col min="8" max="8" width="38" customWidth="1"/>
+    <col min="9" max="9" width="17.109375" customWidth="1"/>
+    <col min="10" max="10" width="8.77734375" style="6"/>
+    <col min="11" max="11" width="18" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:12" s="25" customFormat="1" ht="12.75" customHeight="1">
+      <c r="A1" s="31" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="126"/>
+      <c r="C1" s="126"/>
+      <c r="D1" s="126"/>
+      <c r="E1" s="32"/>
+      <c r="F1" s="32"/>
+      <c r="G1" s="32"/>
+      <c r="H1" s="32"/>
+      <c r="I1" s="32"/>
+      <c r="J1" s="52"/>
+      <c r="K1" s="32"/>
+      <c r="L1" s="33"/>
+    </row>
+    <row r="2" spans="1:12" s="25" customFormat="1" ht="11.25" customHeight="1" thickBot="1">
+      <c r="A2" s="33"/>
+      <c r="B2" s="127"/>
+      <c r="C2" s="127"/>
+      <c r="D2" s="127"/>
+      <c r="E2" s="32"/>
+      <c r="F2" s="32"/>
+      <c r="G2" s="32"/>
+      <c r="H2" s="32"/>
+      <c r="I2" s="32"/>
+      <c r="J2" s="52"/>
+      <c r="K2" s="32"/>
+      <c r="L2" s="33"/>
+    </row>
+    <row r="3" spans="1:12" s="26" customFormat="1" ht="15" customHeight="1">
+      <c r="A3" s="34" t="s">
+        <v>18</v>
+      </c>
+      <c r="B3" s="96" t="s">
+        <v>4</v>
+      </c>
+      <c r="C3" s="96"/>
+      <c r="D3" s="97"/>
+      <c r="E3" s="35"/>
+      <c r="F3" s="35"/>
+      <c r="G3" s="35"/>
+      <c r="H3" s="35"/>
+      <c r="I3" s="102"/>
+      <c r="J3" s="102"/>
+      <c r="K3" s="102"/>
+      <c r="L3" s="53"/>
+    </row>
+    <row r="4" spans="1:12" s="26" customFormat="1" ht="13.2">
+      <c r="A4" s="36" t="s">
+        <v>19</v>
+      </c>
+      <c r="B4" s="128" t="s">
+        <v>48</v>
+      </c>
+      <c r="C4" s="129"/>
+      <c r="D4" s="130"/>
+      <c r="E4" s="35"/>
+      <c r="F4" s="35"/>
+      <c r="G4" s="35"/>
+      <c r="H4" s="35"/>
+      <c r="I4" s="102"/>
+      <c r="J4" s="102"/>
+      <c r="K4" s="102"/>
+      <c r="L4" s="53"/>
+    </row>
+    <row r="5" spans="1:12" s="27" customFormat="1" ht="15" customHeight="1">
+      <c r="A5" s="36" t="s">
+        <v>20</v>
+      </c>
+      <c r="B5" s="122" t="s">
+        <v>44</v>
+      </c>
+      <c r="C5" s="123"/>
+      <c r="D5" s="124"/>
+      <c r="E5" s="37"/>
+      <c r="F5" s="37"/>
+      <c r="G5" s="37"/>
+      <c r="H5" s="37"/>
+      <c r="I5" s="125"/>
+      <c r="J5" s="125"/>
+      <c r="K5" s="125"/>
+      <c r="L5" s="54"/>
+    </row>
+    <row r="6" spans="1:12" s="26" customFormat="1" ht="15" customHeight="1">
+      <c r="A6" s="38" t="s">
+        <v>21</v>
+      </c>
+      <c r="B6" s="39">
+        <f>COUNTIF(J12:J33,"Pass")</f>
+        <v>0</v>
+      </c>
+      <c r="C6" s="40" t="s">
+        <v>22</v>
+      </c>
+      <c r="D6" s="41">
+        <f>COUNTIF(J10:J752,"Pending")</f>
+        <v>0</v>
+      </c>
+      <c r="E6" s="42"/>
+      <c r="F6" s="42"/>
+      <c r="G6" s="42"/>
+      <c r="H6" s="42"/>
+      <c r="I6" s="102"/>
+      <c r="J6" s="102"/>
+      <c r="K6" s="102"/>
+      <c r="L6" s="53"/>
+    </row>
+    <row r="7" spans="1:12" s="26" customFormat="1" ht="15" customHeight="1" thickBot="1">
+      <c r="A7" s="43" t="s">
+        <v>23</v>
+      </c>
+      <c r="B7" s="44">
+        <f>COUNTIF(J12:J33,"Fail")</f>
+        <v>0</v>
+      </c>
+      <c r="C7" s="45" t="s">
+        <v>24</v>
+      </c>
+      <c r="D7" s="46">
+        <f>COUNTIF(A12:A33, "TC*")</f>
+        <v>1</v>
+      </c>
+      <c r="E7" s="47"/>
+      <c r="F7" s="47"/>
+      <c r="G7" s="47"/>
+      <c r="H7" s="47"/>
+      <c r="I7" s="102"/>
+      <c r="J7" s="102"/>
+      <c r="K7" s="102"/>
+      <c r="L7" s="53"/>
+    </row>
+    <row r="8" spans="1:12" s="26" customFormat="1" ht="15" customHeight="1">
+      <c r="A8" s="103"/>
+      <c r="B8" s="103"/>
+      <c r="C8" s="103"/>
+      <c r="D8" s="103"/>
+      <c r="E8" s="42"/>
+      <c r="F8" s="42"/>
+      <c r="G8" s="42"/>
+      <c r="H8" s="42"/>
+      <c r="I8" s="42"/>
+      <c r="J8" s="55"/>
+      <c r="K8" s="55"/>
+      <c r="L8" s="53"/>
+    </row>
+    <row r="9" spans="1:12" s="28" customFormat="1" ht="12" customHeight="1">
+      <c r="A9" s="104" t="s">
+        <v>25</v>
+      </c>
+      <c r="B9" s="106" t="s">
+        <v>26</v>
+      </c>
+      <c r="C9" s="104" t="s">
+        <v>27</v>
+      </c>
+      <c r="D9" s="108" t="s">
+        <v>28</v>
+      </c>
+      <c r="E9" s="109"/>
+      <c r="F9" s="109"/>
+      <c r="G9" s="110"/>
+      <c r="H9" s="114" t="s">
+        <v>29</v>
+      </c>
+      <c r="I9" s="115" t="s">
+        <v>30</v>
+      </c>
+      <c r="J9" s="115" t="s">
+        <v>31</v>
+      </c>
+      <c r="K9" s="115" t="s">
+        <v>32</v>
+      </c>
+      <c r="L9" s="56"/>
+    </row>
+    <row r="10" spans="1:12" s="26" customFormat="1" ht="12" customHeight="1">
+      <c r="A10" s="105"/>
+      <c r="B10" s="107"/>
+      <c r="C10" s="105"/>
+      <c r="D10" s="111"/>
+      <c r="E10" s="112"/>
+      <c r="F10" s="112"/>
+      <c r="G10" s="113"/>
+      <c r="H10" s="104"/>
+      <c r="I10" s="104"/>
+      <c r="J10" s="104"/>
+      <c r="K10" s="104"/>
+      <c r="L10" s="53"/>
+    </row>
+    <row r="11" spans="1:12" s="29" customFormat="1" ht="15">
+      <c r="A11" s="116"/>
+      <c r="B11" s="116"/>
+      <c r="C11" s="116"/>
+      <c r="D11" s="116"/>
+      <c r="E11" s="116"/>
+      <c r="F11" s="116"/>
+      <c r="G11" s="116"/>
+      <c r="H11" s="116"/>
+      <c r="I11" s="116"/>
+      <c r="J11" s="116"/>
+      <c r="K11" s="117"/>
+    </row>
+    <row r="12" spans="1:12" s="30" customFormat="1" ht="13.2">
+      <c r="A12" s="118" t="s">
+        <v>33</v>
+      </c>
+      <c r="B12" s="119"/>
+      <c r="C12" s="119"/>
+      <c r="D12" s="119"/>
+      <c r="E12" s="119"/>
+      <c r="F12" s="119"/>
+      <c r="G12" s="119"/>
+      <c r="H12" s="119"/>
+      <c r="I12" s="119"/>
+      <c r="J12" s="119"/>
+      <c r="K12" s="120"/>
+    </row>
+    <row r="13" spans="1:12" s="30" customFormat="1" ht="13.2" outlineLevel="1">
+      <c r="A13" s="49" t="s">
+        <v>45</v>
+      </c>
+      <c r="B13" s="50"/>
+      <c r="C13" s="51"/>
+      <c r="D13" s="121"/>
+      <c r="E13" s="121"/>
+      <c r="F13" s="121"/>
+      <c r="G13" s="51"/>
+      <c r="H13" s="51"/>
+      <c r="I13" s="89"/>
+      <c r="J13" s="51"/>
+      <c r="K13" s="51"/>
+    </row>
+    <row r="14" spans="1:12" s="30" customFormat="1" ht="13.2" outlineLevel="1">
+      <c r="A14" s="49"/>
+      <c r="B14" s="50"/>
+      <c r="C14" s="51"/>
+      <c r="D14" s="99"/>
+      <c r="E14" s="99"/>
+      <c r="F14" s="99"/>
+      <c r="G14" s="51"/>
+      <c r="H14" s="51"/>
+      <c r="I14" s="89"/>
+      <c r="J14" s="51"/>
+      <c r="K14" s="51"/>
+    </row>
+    <row r="15" spans="1:12" s="30" customFormat="1" ht="13.2" outlineLevel="1">
+      <c r="A15" s="49"/>
+      <c r="B15" s="50"/>
+      <c r="C15" s="51"/>
+      <c r="D15" s="99"/>
+      <c r="E15" s="99"/>
+      <c r="F15" s="99"/>
+      <c r="G15" s="51"/>
+      <c r="H15" s="51"/>
+      <c r="I15" s="89"/>
+      <c r="J15" s="51"/>
+      <c r="K15" s="51"/>
+    </row>
+    <row r="16" spans="1:12" s="30" customFormat="1" ht="13.2" outlineLevel="1">
+      <c r="A16" s="49"/>
+      <c r="B16" s="50"/>
+      <c r="C16" s="51"/>
+      <c r="D16" s="99"/>
+      <c r="E16" s="99"/>
+      <c r="F16" s="99"/>
+      <c r="G16" s="51"/>
+      <c r="H16" s="51"/>
+      <c r="I16" s="89"/>
+      <c r="J16" s="51"/>
+      <c r="K16" s="51"/>
+    </row>
+    <row r="17" spans="1:11" s="30" customFormat="1" ht="13.2" outlineLevel="1">
+      <c r="A17" s="49"/>
+      <c r="B17" s="50"/>
+      <c r="C17" s="51"/>
+      <c r="D17" s="99"/>
+      <c r="E17" s="99"/>
+      <c r="F17" s="99"/>
+      <c r="G17" s="51"/>
+      <c r="H17" s="51"/>
+      <c r="I17" s="89"/>
+      <c r="J17" s="51"/>
+      <c r="K17" s="51"/>
+    </row>
+    <row r="18" spans="1:11" s="30" customFormat="1" ht="13.2" outlineLevel="1">
+      <c r="A18" s="49"/>
+      <c r="B18" s="50"/>
+      <c r="C18" s="51"/>
+      <c r="D18" s="99"/>
+      <c r="E18" s="99"/>
+      <c r="F18" s="99"/>
+      <c r="G18" s="51"/>
+      <c r="H18" s="51"/>
+      <c r="I18" s="89"/>
+      <c r="J18" s="51"/>
+      <c r="K18" s="51"/>
+    </row>
+    <row r="19" spans="1:11" s="30" customFormat="1" ht="13.2" outlineLevel="1">
+      <c r="A19" s="49"/>
+      <c r="B19" s="50"/>
+      <c r="C19" s="51"/>
+      <c r="D19" s="99"/>
+      <c r="E19" s="99"/>
+      <c r="F19" s="99"/>
+      <c r="G19" s="51"/>
+      <c r="H19" s="51"/>
+      <c r="I19" s="89"/>
+      <c r="J19" s="51"/>
+      <c r="K19" s="51"/>
+    </row>
+    <row r="20" spans="1:11" s="30" customFormat="1" ht="13.2" outlineLevel="1">
+      <c r="A20" s="100"/>
+      <c r="B20" s="101"/>
+      <c r="C20" s="101"/>
+      <c r="D20" s="48"/>
+      <c r="E20" s="48"/>
+      <c r="F20" s="48"/>
+      <c r="G20" s="48"/>
+      <c r="H20" s="48"/>
+      <c r="I20" s="48"/>
+      <c r="J20" s="48"/>
+      <c r="K20" s="57"/>
+    </row>
+    <row r="21" spans="1:11" s="30" customFormat="1" ht="13.2" outlineLevel="1">
+      <c r="A21" s="49"/>
+      <c r="B21" s="50"/>
+      <c r="C21" s="51"/>
+      <c r="D21" s="99"/>
+      <c r="E21" s="99"/>
+      <c r="F21" s="99"/>
+      <c r="G21" s="51"/>
+      <c r="H21" s="51"/>
+      <c r="I21" s="89"/>
+      <c r="J21" s="51"/>
+      <c r="K21" s="51"/>
+    </row>
+    <row r="22" spans="1:11" s="30" customFormat="1" ht="13.2" outlineLevel="1">
+      <c r="A22" s="49"/>
+      <c r="B22" s="50"/>
+      <c r="C22" s="51"/>
+      <c r="D22" s="99"/>
+      <c r="E22" s="99"/>
+      <c r="F22" s="99"/>
+      <c r="G22" s="51"/>
+      <c r="H22" s="51"/>
+      <c r="I22" s="89"/>
+      <c r="J22" s="51"/>
+      <c r="K22" s="51"/>
+    </row>
+    <row r="23" spans="1:11" s="30" customFormat="1" ht="13.2" outlineLevel="1">
+      <c r="A23" s="49"/>
+      <c r="B23" s="50"/>
+      <c r="C23" s="51"/>
+      <c r="D23" s="99"/>
+      <c r="E23" s="99"/>
+      <c r="F23" s="99"/>
+      <c r="G23" s="51"/>
+      <c r="H23" s="51"/>
+      <c r="I23" s="89"/>
+      <c r="J23" s="51"/>
+      <c r="K23" s="51"/>
+    </row>
+    <row r="24" spans="1:11" s="30" customFormat="1" ht="13.2" outlineLevel="1">
+      <c r="A24" s="49"/>
+      <c r="B24" s="50"/>
+      <c r="C24" s="51"/>
+      <c r="D24" s="99"/>
+      <c r="E24" s="99"/>
+      <c r="F24" s="99"/>
+      <c r="G24" s="51"/>
+      <c r="H24" s="51"/>
+      <c r="I24" s="89"/>
+      <c r="J24" s="51"/>
+      <c r="K24" s="51"/>
+    </row>
+    <row r="25" spans="1:11" s="30" customFormat="1" ht="13.2" outlineLevel="1">
+      <c r="A25" s="49"/>
+      <c r="B25" s="50"/>
+      <c r="C25" s="51"/>
+      <c r="D25" s="99"/>
+      <c r="E25" s="99"/>
+      <c r="F25" s="99"/>
+      <c r="G25" s="51"/>
+      <c r="H25" s="51"/>
+      <c r="I25" s="89"/>
+      <c r="J25" s="51"/>
+      <c r="K25" s="51"/>
+    </row>
+    <row r="26" spans="1:11" s="30" customFormat="1" ht="18" customHeight="1" outlineLevel="1">
+      <c r="A26" s="49"/>
+      <c r="B26" s="50"/>
+      <c r="C26" s="51"/>
+      <c r="D26" s="99"/>
+      <c r="E26" s="99"/>
+      <c r="F26" s="99"/>
+      <c r="G26" s="51"/>
+      <c r="H26" s="51"/>
+      <c r="I26" s="89"/>
+      <c r="J26" s="51"/>
+      <c r="K26" s="51"/>
+    </row>
+    <row r="27" spans="1:11" s="30" customFormat="1" ht="13.2" outlineLevel="1">
+      <c r="A27" s="100"/>
+      <c r="B27" s="101"/>
+      <c r="C27" s="101"/>
+      <c r="D27" s="48"/>
+      <c r="E27" s="48"/>
+      <c r="F27" s="48"/>
+      <c r="G27" s="48"/>
+      <c r="H27" s="48"/>
+      <c r="I27" s="48"/>
+      <c r="J27" s="48"/>
+      <c r="K27" s="57"/>
+    </row>
+    <row r="28" spans="1:11" s="30" customFormat="1" ht="13.2" outlineLevel="1">
+      <c r="A28" s="49"/>
+      <c r="B28" s="50"/>
+      <c r="C28" s="51"/>
+      <c r="D28" s="99"/>
+      <c r="E28" s="99"/>
+      <c r="F28" s="99"/>
+      <c r="G28" s="51"/>
+      <c r="H28" s="51"/>
+      <c r="I28" s="89"/>
+      <c r="J28" s="51"/>
+      <c r="K28" s="51"/>
+    </row>
+    <row r="29" spans="1:11" s="30" customFormat="1" ht="13.2" outlineLevel="1">
+      <c r="A29" s="49"/>
+      <c r="B29" s="50"/>
+      <c r="C29" s="51"/>
+      <c r="D29" s="99"/>
+      <c r="E29" s="99"/>
+      <c r="F29" s="99"/>
+      <c r="G29" s="51"/>
+      <c r="H29" s="51"/>
+      <c r="I29" s="89"/>
+      <c r="J29" s="51"/>
+      <c r="K29" s="51"/>
+    </row>
+    <row r="30" spans="1:11" s="30" customFormat="1" ht="13.2" outlineLevel="1">
+      <c r="A30" s="49"/>
+      <c r="B30" s="50"/>
+      <c r="C30" s="51"/>
+      <c r="D30" s="99"/>
+      <c r="E30" s="99"/>
+      <c r="F30" s="99"/>
+      <c r="G30" s="51"/>
+      <c r="H30" s="51"/>
+      <c r="I30" s="89"/>
+      <c r="J30" s="51"/>
+      <c r="K30" s="51"/>
+    </row>
+    <row r="31" spans="1:11" s="30" customFormat="1" ht="13.2" outlineLevel="1">
+      <c r="A31" s="49"/>
+      <c r="B31" s="50"/>
+      <c r="C31" s="51"/>
+      <c r="D31" s="99"/>
+      <c r="E31" s="99"/>
+      <c r="F31" s="99"/>
+      <c r="G31" s="51"/>
+      <c r="H31" s="51"/>
+      <c r="I31" s="89"/>
+      <c r="J31" s="51"/>
+      <c r="K31" s="51"/>
+    </row>
+    <row r="32" spans="1:11" s="30" customFormat="1" ht="13.2" outlineLevel="1">
+      <c r="A32" s="49"/>
+      <c r="B32" s="50"/>
+      <c r="C32" s="51"/>
+      <c r="D32" s="99"/>
+      <c r="E32" s="99"/>
+      <c r="F32" s="99"/>
+      <c r="G32" s="51"/>
+      <c r="H32" s="51"/>
+      <c r="I32" s="89"/>
+      <c r="J32" s="51"/>
+      <c r="K32" s="51"/>
+    </row>
+    <row r="33" spans="1:11" s="30" customFormat="1" ht="13.8" customHeight="1" outlineLevel="1">
+      <c r="A33" s="49"/>
+      <c r="B33" s="50"/>
+      <c r="C33" s="51"/>
+      <c r="D33" s="99"/>
+      <c r="E33" s="99"/>
+      <c r="F33" s="99"/>
       <c r="G33" s="51"/>
       <c r="H33" s="51"/>
       <c r="I33" s="89"/>
@@ -2436,1203 +3937,6 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <sheetPr>
-    <outlinePr summaryBelow="0" summaryRight="0"/>
-  </sheetPr>
-  <dimension ref="A1:L71"/>
-  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="13.8" outlineLevelRow="1"/>
-  <cols>
-    <col min="1" max="1" width="18" customWidth="1"/>
-    <col min="2" max="2" width="18.109375" customWidth="1"/>
-    <col min="3" max="3" width="42.109375" customWidth="1"/>
-    <col min="6" max="6" width="23.6640625" customWidth="1"/>
-    <col min="7" max="7" width="18.44140625" hidden="1" customWidth="1"/>
-    <col min="8" max="8" width="38" customWidth="1"/>
-    <col min="9" max="9" width="17.109375" customWidth="1"/>
-    <col min="10" max="10" width="9" style="6"/>
-    <col min="11" max="11" width="18" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:12" s="25" customFormat="1" ht="12.75" customHeight="1">
-      <c r="A1" s="31" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="103"/>
-      <c r="C1" s="103"/>
-      <c r="D1" s="103"/>
-      <c r="E1" s="32"/>
-      <c r="F1" s="32"/>
-      <c r="G1" s="32"/>
-      <c r="H1" s="32"/>
-      <c r="I1" s="32"/>
-      <c r="J1" s="52"/>
-      <c r="K1" s="32"/>
-      <c r="L1" s="33"/>
-    </row>
-    <row r="2" spans="1:12" s="25" customFormat="1" ht="11.25" customHeight="1">
-      <c r="A2" s="33"/>
-      <c r="B2" s="104"/>
-      <c r="C2" s="104"/>
-      <c r="D2" s="104"/>
-      <c r="E2" s="32"/>
-      <c r="F2" s="32"/>
-      <c r="G2" s="32"/>
-      <c r="H2" s="32"/>
-      <c r="I2" s="32"/>
-      <c r="J2" s="52"/>
-      <c r="K2" s="32"/>
-      <c r="L2" s="33"/>
-    </row>
-    <row r="3" spans="1:12" s="26" customFormat="1" ht="15" customHeight="1">
-      <c r="A3" s="34" t="s">
-        <v>18</v>
-      </c>
-      <c r="B3" s="96" t="s">
-        <v>4</v>
-      </c>
-      <c r="C3" s="96"/>
-      <c r="D3" s="97"/>
-      <c r="E3" s="35"/>
-      <c r="F3" s="35"/>
-      <c r="G3" s="35"/>
-      <c r="H3" s="35"/>
-      <c r="I3" s="105"/>
-      <c r="J3" s="105"/>
-      <c r="K3" s="105"/>
-      <c r="L3" s="53"/>
-    </row>
-    <row r="4" spans="1:12" s="26" customFormat="1" ht="13.2">
-      <c r="A4" s="36" t="s">
-        <v>19</v>
-      </c>
-      <c r="B4" s="106" t="s">
-        <v>50</v>
-      </c>
-      <c r="C4" s="107"/>
-      <c r="D4" s="108"/>
-      <c r="E4" s="35"/>
-      <c r="F4" s="35"/>
-      <c r="G4" s="35"/>
-      <c r="H4" s="35"/>
-      <c r="I4" s="105"/>
-      <c r="J4" s="105"/>
-      <c r="K4" s="105"/>
-      <c r="L4" s="53"/>
-    </row>
-    <row r="5" spans="1:12" s="27" customFormat="1" ht="15" customHeight="1">
-      <c r="A5" s="36" t="s">
-        <v>20</v>
-      </c>
-      <c r="B5" s="99" t="s">
-        <v>44</v>
-      </c>
-      <c r="C5" s="100"/>
-      <c r="D5" s="101"/>
-      <c r="E5" s="37"/>
-      <c r="F5" s="37"/>
-      <c r="G5" s="37"/>
-      <c r="H5" s="37"/>
-      <c r="I5" s="102"/>
-      <c r="J5" s="102"/>
-      <c r="K5" s="102"/>
-      <c r="L5" s="54"/>
-    </row>
-    <row r="6" spans="1:12" s="26" customFormat="1" ht="15" customHeight="1">
-      <c r="A6" s="38" t="s">
-        <v>21</v>
-      </c>
-      <c r="B6" s="39">
-        <f>COUNTIF(J12:J33,"Pass")</f>
-        <v>0</v>
-      </c>
-      <c r="C6" s="40" t="s">
-        <v>22</v>
-      </c>
-      <c r="D6" s="41">
-        <f>COUNTIF(J10:J752,"Pending")</f>
-        <v>0</v>
-      </c>
-      <c r="E6" s="42"/>
-      <c r="F6" s="42"/>
-      <c r="G6" s="42"/>
-      <c r="H6" s="42"/>
-      <c r="I6" s="105"/>
-      <c r="J6" s="105"/>
-      <c r="K6" s="105"/>
-      <c r="L6" s="53"/>
-    </row>
-    <row r="7" spans="1:12" s="26" customFormat="1" ht="15" customHeight="1">
-      <c r="A7" s="43" t="s">
-        <v>23</v>
-      </c>
-      <c r="B7" s="44">
-        <f>COUNTIF(J12:J33,"Fail")</f>
-        <v>0</v>
-      </c>
-      <c r="C7" s="45" t="s">
-        <v>24</v>
-      </c>
-      <c r="D7" s="46">
-        <f>COUNTIF(A12:A33, "TC*")</f>
-        <v>2</v>
-      </c>
-      <c r="E7" s="47"/>
-      <c r="F7" s="47"/>
-      <c r="G7" s="47"/>
-      <c r="H7" s="47"/>
-      <c r="I7" s="105"/>
-      <c r="J7" s="105"/>
-      <c r="K7" s="105"/>
-      <c r="L7" s="53"/>
-    </row>
-    <row r="8" spans="1:12" s="26" customFormat="1" ht="15" customHeight="1">
-      <c r="A8" s="110"/>
-      <c r="B8" s="110"/>
-      <c r="C8" s="110"/>
-      <c r="D8" s="110"/>
-      <c r="E8" s="42"/>
-      <c r="F8" s="42"/>
-      <c r="G8" s="42"/>
-      <c r="H8" s="42"/>
-      <c r="I8" s="42"/>
-      <c r="J8" s="55"/>
-      <c r="K8" s="55"/>
-      <c r="L8" s="53"/>
-    </row>
-    <row r="9" spans="1:12" s="28" customFormat="1" ht="12" customHeight="1">
-      <c r="A9" s="111" t="s">
-        <v>25</v>
-      </c>
-      <c r="B9" s="113" t="s">
-        <v>26</v>
-      </c>
-      <c r="C9" s="111" t="s">
-        <v>27</v>
-      </c>
-      <c r="D9" s="115" t="s">
-        <v>28</v>
-      </c>
-      <c r="E9" s="116"/>
-      <c r="F9" s="116"/>
-      <c r="G9" s="117"/>
-      <c r="H9" s="121" t="s">
-        <v>29</v>
-      </c>
-      <c r="I9" s="122" t="s">
-        <v>30</v>
-      </c>
-      <c r="J9" s="122" t="s">
-        <v>31</v>
-      </c>
-      <c r="K9" s="122" t="s">
-        <v>32</v>
-      </c>
-      <c r="L9" s="56"/>
-    </row>
-    <row r="10" spans="1:12" s="26" customFormat="1" ht="12" customHeight="1">
-      <c r="A10" s="112"/>
-      <c r="B10" s="114"/>
-      <c r="C10" s="112"/>
-      <c r="D10" s="118"/>
-      <c r="E10" s="119"/>
-      <c r="F10" s="119"/>
-      <c r="G10" s="120"/>
-      <c r="H10" s="111"/>
-      <c r="I10" s="111"/>
-      <c r="J10" s="111"/>
-      <c r="K10" s="111"/>
-      <c r="L10" s="53"/>
-    </row>
-    <row r="11" spans="1:12" s="29" customFormat="1" ht="15">
-      <c r="A11" s="123"/>
-      <c r="B11" s="123"/>
-      <c r="C11" s="123"/>
-      <c r="D11" s="123"/>
-      <c r="E11" s="123"/>
-      <c r="F11" s="123"/>
-      <c r="G11" s="123"/>
-      <c r="H11" s="123"/>
-      <c r="I11" s="123"/>
-      <c r="J11" s="123"/>
-      <c r="K11" s="124"/>
-    </row>
-    <row r="12" spans="1:12" s="30" customFormat="1" ht="13.2">
-      <c r="A12" s="125" t="s">
-        <v>33</v>
-      </c>
-      <c r="B12" s="126"/>
-      <c r="C12" s="126"/>
-      <c r="D12" s="126"/>
-      <c r="E12" s="126"/>
-      <c r="F12" s="126"/>
-      <c r="G12" s="126"/>
-      <c r="H12" s="126"/>
-      <c r="I12" s="126"/>
-      <c r="J12" s="126"/>
-      <c r="K12" s="127"/>
-    </row>
-    <row r="13" spans="1:12" s="30" customFormat="1" ht="13.2" outlineLevel="1">
-      <c r="A13" s="49" t="s">
-        <v>45</v>
-      </c>
-      <c r="B13" s="50"/>
-      <c r="C13" s="51"/>
-      <c r="D13" s="128"/>
-      <c r="E13" s="128"/>
-      <c r="F13" s="128"/>
-      <c r="G13" s="51"/>
-      <c r="H13" s="51"/>
-      <c r="I13" s="89"/>
-      <c r="J13" s="51"/>
-      <c r="K13" s="51"/>
-    </row>
-    <row r="14" spans="1:12" s="30" customFormat="1" ht="13.2" outlineLevel="1">
-      <c r="A14" s="49" t="s">
-        <v>47</v>
-      </c>
-      <c r="B14" s="50"/>
-      <c r="C14" s="51"/>
-      <c r="D14" s="109"/>
-      <c r="E14" s="109"/>
-      <c r="F14" s="109"/>
-      <c r="G14" s="51"/>
-      <c r="H14" s="51"/>
-      <c r="I14" s="89"/>
-      <c r="J14" s="51"/>
-      <c r="K14" s="51"/>
-    </row>
-    <row r="15" spans="1:12" s="30" customFormat="1" ht="13.2" outlineLevel="1">
-      <c r="A15" s="49"/>
-      <c r="B15" s="50"/>
-      <c r="C15" s="51"/>
-      <c r="D15" s="109"/>
-      <c r="E15" s="109"/>
-      <c r="F15" s="109"/>
-      <c r="G15" s="51"/>
-      <c r="H15" s="51"/>
-      <c r="I15" s="89"/>
-      <c r="J15" s="51"/>
-      <c r="K15" s="51"/>
-    </row>
-    <row r="16" spans="1:12" s="30" customFormat="1" ht="13.2" outlineLevel="1">
-      <c r="A16" s="49"/>
-      <c r="B16" s="50"/>
-      <c r="C16" s="51"/>
-      <c r="D16" s="109"/>
-      <c r="E16" s="109"/>
-      <c r="F16" s="109"/>
-      <c r="G16" s="51"/>
-      <c r="H16" s="51"/>
-      <c r="I16" s="89"/>
-      <c r="J16" s="51"/>
-      <c r="K16" s="51"/>
-    </row>
-    <row r="17" spans="1:11" s="30" customFormat="1" ht="13.2" outlineLevel="1">
-      <c r="A17" s="49"/>
-      <c r="B17" s="50"/>
-      <c r="C17" s="51"/>
-      <c r="D17" s="109"/>
-      <c r="E17" s="109"/>
-      <c r="F17" s="109"/>
-      <c r="G17" s="51"/>
-      <c r="H17" s="51"/>
-      <c r="I17" s="89"/>
-      <c r="J17" s="51"/>
-      <c r="K17" s="51"/>
-    </row>
-    <row r="18" spans="1:11" s="30" customFormat="1" ht="13.2" outlineLevel="1">
-      <c r="A18" s="49"/>
-      <c r="B18" s="50"/>
-      <c r="C18" s="51"/>
-      <c r="D18" s="109"/>
-      <c r="E18" s="109"/>
-      <c r="F18" s="109"/>
-      <c r="G18" s="51"/>
-      <c r="H18" s="51"/>
-      <c r="I18" s="89"/>
-      <c r="J18" s="51"/>
-      <c r="K18" s="51"/>
-    </row>
-    <row r="19" spans="1:11" s="30" customFormat="1" ht="13.2" outlineLevel="1">
-      <c r="A19" s="49"/>
-      <c r="B19" s="50"/>
-      <c r="C19" s="51"/>
-      <c r="D19" s="109"/>
-      <c r="E19" s="109"/>
-      <c r="F19" s="109"/>
-      <c r="G19" s="51"/>
-      <c r="H19" s="51"/>
-      <c r="I19" s="89"/>
-      <c r="J19" s="51"/>
-      <c r="K19" s="51"/>
-    </row>
-    <row r="20" spans="1:11" s="30" customFormat="1" ht="13.2" outlineLevel="1">
-      <c r="A20" s="129"/>
-      <c r="B20" s="130"/>
-      <c r="C20" s="130"/>
-      <c r="D20" s="48"/>
-      <c r="E20" s="48"/>
-      <c r="F20" s="48"/>
-      <c r="G20" s="48"/>
-      <c r="H20" s="48"/>
-      <c r="I20" s="48"/>
-      <c r="J20" s="48"/>
-      <c r="K20" s="57"/>
-    </row>
-    <row r="21" spans="1:11" s="30" customFormat="1" ht="13.2" outlineLevel="1">
-      <c r="A21" s="49"/>
-      <c r="B21" s="50"/>
-      <c r="C21" s="51"/>
-      <c r="D21" s="109"/>
-      <c r="E21" s="109"/>
-      <c r="F21" s="109"/>
-      <c r="G21" s="51"/>
-      <c r="H21" s="51"/>
-      <c r="I21" s="89"/>
-      <c r="J21" s="51"/>
-      <c r="K21" s="51"/>
-    </row>
-    <row r="22" spans="1:11" s="30" customFormat="1" ht="13.2" outlineLevel="1">
-      <c r="A22" s="49"/>
-      <c r="B22" s="50"/>
-      <c r="C22" s="51"/>
-      <c r="D22" s="109"/>
-      <c r="E22" s="109"/>
-      <c r="F22" s="109"/>
-      <c r="G22" s="51"/>
-      <c r="H22" s="51"/>
-      <c r="I22" s="89"/>
-      <c r="J22" s="51"/>
-      <c r="K22" s="51"/>
-    </row>
-    <row r="23" spans="1:11" s="30" customFormat="1" ht="13.2" outlineLevel="1">
-      <c r="A23" s="49"/>
-      <c r="B23" s="50"/>
-      <c r="C23" s="51"/>
-      <c r="D23" s="109"/>
-      <c r="E23" s="109"/>
-      <c r="F23" s="109"/>
-      <c r="G23" s="51"/>
-      <c r="H23" s="51"/>
-      <c r="I23" s="89"/>
-      <c r="J23" s="51"/>
-      <c r="K23" s="51"/>
-    </row>
-    <row r="24" spans="1:11" s="30" customFormat="1" ht="13.2" outlineLevel="1">
-      <c r="A24" s="49"/>
-      <c r="B24" s="50"/>
-      <c r="C24" s="51"/>
-      <c r="D24" s="109"/>
-      <c r="E24" s="109"/>
-      <c r="F24" s="109"/>
-      <c r="G24" s="51"/>
-      <c r="H24" s="51"/>
-      <c r="I24" s="89"/>
-      <c r="J24" s="51"/>
-      <c r="K24" s="51"/>
-    </row>
-    <row r="25" spans="1:11" s="30" customFormat="1" ht="13.2" outlineLevel="1">
-      <c r="A25" s="49"/>
-      <c r="B25" s="50"/>
-      <c r="C25" s="51"/>
-      <c r="D25" s="109"/>
-      <c r="E25" s="109"/>
-      <c r="F25" s="109"/>
-      <c r="G25" s="51"/>
-      <c r="H25" s="51"/>
-      <c r="I25" s="89"/>
-      <c r="J25" s="51"/>
-      <c r="K25" s="51"/>
-    </row>
-    <row r="26" spans="1:11" s="30" customFormat="1" ht="18" customHeight="1" outlineLevel="1">
-      <c r="A26" s="49"/>
-      <c r="B26" s="50"/>
-      <c r="C26" s="51"/>
-      <c r="D26" s="109"/>
-      <c r="E26" s="109"/>
-      <c r="F26" s="109"/>
-      <c r="G26" s="51"/>
-      <c r="H26" s="51"/>
-      <c r="I26" s="89"/>
-      <c r="J26" s="51"/>
-      <c r="K26" s="51"/>
-    </row>
-    <row r="27" spans="1:11" s="30" customFormat="1" ht="13.2" outlineLevel="1">
-      <c r="A27" s="129"/>
-      <c r="B27" s="130"/>
-      <c r="C27" s="130"/>
-      <c r="D27" s="48"/>
-      <c r="E27" s="48"/>
-      <c r="F27" s="48"/>
-      <c r="G27" s="48"/>
-      <c r="H27" s="48"/>
-      <c r="I27" s="48"/>
-      <c r="J27" s="48"/>
-      <c r="K27" s="57"/>
-    </row>
-    <row r="28" spans="1:11" s="30" customFormat="1" ht="13.2" outlineLevel="1">
-      <c r="A28" s="49"/>
-      <c r="B28" s="50"/>
-      <c r="C28" s="51"/>
-      <c r="D28" s="109"/>
-      <c r="E28" s="109"/>
-      <c r="F28" s="109"/>
-      <c r="G28" s="51"/>
-      <c r="H28" s="51"/>
-      <c r="I28" s="89"/>
-      <c r="J28" s="51"/>
-      <c r="K28" s="51"/>
-    </row>
-    <row r="29" spans="1:11" s="30" customFormat="1" ht="13.2" outlineLevel="1">
-      <c r="A29" s="49"/>
-      <c r="B29" s="50"/>
-      <c r="C29" s="51"/>
-      <c r="D29" s="109"/>
-      <c r="E29" s="109"/>
-      <c r="F29" s="109"/>
-      <c r="G29" s="51"/>
-      <c r="H29" s="51"/>
-      <c r="I29" s="89"/>
-      <c r="J29" s="51"/>
-      <c r="K29" s="51"/>
-    </row>
-    <row r="30" spans="1:11" s="30" customFormat="1" ht="13.2" outlineLevel="1">
-      <c r="A30" s="49"/>
-      <c r="B30" s="50"/>
-      <c r="C30" s="51"/>
-      <c r="D30" s="109"/>
-      <c r="E30" s="109"/>
-      <c r="F30" s="109"/>
-      <c r="G30" s="51"/>
-      <c r="H30" s="51"/>
-      <c r="I30" s="89"/>
-      <c r="J30" s="51"/>
-      <c r="K30" s="51"/>
-    </row>
-    <row r="31" spans="1:11" s="30" customFormat="1" ht="13.2" outlineLevel="1">
-      <c r="A31" s="49"/>
-      <c r="B31" s="50"/>
-      <c r="C31" s="51"/>
-      <c r="D31" s="109"/>
-      <c r="E31" s="109"/>
-      <c r="F31" s="109"/>
-      <c r="G31" s="51"/>
-      <c r="H31" s="51"/>
-      <c r="I31" s="89"/>
-      <c r="J31" s="51"/>
-      <c r="K31" s="51"/>
-    </row>
-    <row r="32" spans="1:11" s="30" customFormat="1" ht="13.2" outlineLevel="1">
-      <c r="A32" s="49"/>
-      <c r="B32" s="50"/>
-      <c r="C32" s="51"/>
-      <c r="D32" s="109"/>
-      <c r="E32" s="109"/>
-      <c r="F32" s="109"/>
-      <c r="G32" s="51"/>
-      <c r="H32" s="51"/>
-      <c r="I32" s="89"/>
-      <c r="J32" s="51"/>
-      <c r="K32" s="51"/>
-    </row>
-    <row r="33" spans="1:11" s="30" customFormat="1" ht="13.8" customHeight="1" outlineLevel="1">
-      <c r="A33" s="49"/>
-      <c r="B33" s="50"/>
-      <c r="C33" s="51"/>
-      <c r="D33" s="109"/>
-      <c r="E33" s="109"/>
-      <c r="F33" s="109"/>
-      <c r="G33" s="51"/>
-      <c r="H33" s="51"/>
-      <c r="I33" s="89"/>
-      <c r="J33" s="51"/>
-      <c r="K33" s="51"/>
-    </row>
-    <row r="34" spans="1:11" ht="12" customHeight="1"/>
-    <row r="35" spans="1:11" ht="12" customHeight="1"/>
-    <row r="36" spans="1:11" ht="12" customHeight="1"/>
-    <row r="37" spans="1:11" ht="12" customHeight="1"/>
-    <row r="38" spans="1:11" ht="12" customHeight="1"/>
-    <row r="39" spans="1:11" ht="12" customHeight="1"/>
-    <row r="40" spans="1:11" ht="12" customHeight="1"/>
-    <row r="41" spans="1:11" ht="12" customHeight="1"/>
-    <row r="42" spans="1:11" ht="12" customHeight="1"/>
-    <row r="43" spans="1:11" ht="12" customHeight="1"/>
-    <row r="44" spans="1:11" ht="12" customHeight="1"/>
-    <row r="45" spans="1:11" ht="12" customHeight="1"/>
-    <row r="46" spans="1:11" ht="12" customHeight="1"/>
-    <row r="47" spans="1:11" ht="12" customHeight="1"/>
-    <row r="48" spans="1:11" ht="12" customHeight="1"/>
-    <row r="49" ht="12" customHeight="1"/>
-    <row r="50" ht="12" customHeight="1"/>
-    <row r="51" ht="12" customHeight="1"/>
-    <row r="52" ht="12" customHeight="1"/>
-    <row r="53" ht="12" customHeight="1"/>
-    <row r="54" ht="12" customHeight="1"/>
-    <row r="55" ht="12" customHeight="1"/>
-    <row r="56" ht="12" customHeight="1"/>
-    <row r="57" ht="12" customHeight="1"/>
-    <row r="58" ht="12" customHeight="1"/>
-    <row r="59" ht="12" customHeight="1"/>
-    <row r="60" ht="12" customHeight="1"/>
-    <row r="61" ht="12" customHeight="1"/>
-    <row r="62" ht="12" customHeight="1"/>
-    <row r="63" ht="12" customHeight="1"/>
-    <row r="64" ht="12" customHeight="1"/>
-    <row r="65" ht="12" customHeight="1"/>
-    <row r="66" ht="12" customHeight="1"/>
-    <row r="67" ht="12" customHeight="1"/>
-    <row r="68" ht="12" customHeight="1"/>
-    <row r="69" ht="12" customHeight="1"/>
-    <row r="70" ht="12" customHeight="1"/>
-    <row r="71" ht="12" customHeight="1"/>
-  </sheetData>
-  <mergeCells count="41">
-    <mergeCell ref="I3:K3"/>
-    <mergeCell ref="B4:D4"/>
-    <mergeCell ref="I4:K4"/>
-    <mergeCell ref="B5:D5"/>
-    <mergeCell ref="I5:K5"/>
-    <mergeCell ref="I6:K6"/>
-    <mergeCell ref="I7:K7"/>
-    <mergeCell ref="A8:D8"/>
-    <mergeCell ref="A11:K11"/>
-    <mergeCell ref="A12:K12"/>
-    <mergeCell ref="A9:A10"/>
-    <mergeCell ref="B9:B10"/>
-    <mergeCell ref="C9:C10"/>
-    <mergeCell ref="H9:H10"/>
-    <mergeCell ref="I9:I10"/>
-    <mergeCell ref="J9:J10"/>
-    <mergeCell ref="K9:K10"/>
-    <mergeCell ref="D19:F19"/>
-    <mergeCell ref="A20:C20"/>
-    <mergeCell ref="D26:F26"/>
-    <mergeCell ref="A27:C27"/>
-    <mergeCell ref="D33:F33"/>
-    <mergeCell ref="D21:F21"/>
-    <mergeCell ref="D28:F28"/>
-    <mergeCell ref="D22:F22"/>
-    <mergeCell ref="D23:F23"/>
-    <mergeCell ref="D24:F24"/>
-    <mergeCell ref="D25:F25"/>
-    <mergeCell ref="D29:F29"/>
-    <mergeCell ref="D30:F30"/>
-    <mergeCell ref="D31:F31"/>
-    <mergeCell ref="D32:F32"/>
-    <mergeCell ref="B1:D2"/>
-    <mergeCell ref="D9:G10"/>
-    <mergeCell ref="D13:F13"/>
-    <mergeCell ref="D18:F18"/>
-    <mergeCell ref="D14:F14"/>
-    <mergeCell ref="D15:F15"/>
-    <mergeCell ref="D16:F16"/>
-    <mergeCell ref="D17:F17"/>
-    <mergeCell ref="B3:D3"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
-  <headerFooter alignWithMargins="0"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{20690ED2-4B8F-4386-AEC9-67E105CBDE46}">
-  <dimension ref="A1:L71"/>
-  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="13.8" outlineLevelRow="1"/>
-  <cols>
-    <col min="1" max="1" width="18" customWidth="1"/>
-    <col min="2" max="2" width="18.109375" customWidth="1"/>
-    <col min="3" max="3" width="42.109375" customWidth="1"/>
-    <col min="6" max="6" width="23.6640625" customWidth="1"/>
-    <col min="7" max="7" width="18.44140625" hidden="1" customWidth="1"/>
-    <col min="8" max="8" width="38" customWidth="1"/>
-    <col min="9" max="9" width="17.109375" customWidth="1"/>
-    <col min="10" max="10" width="8.77734375" style="6"/>
-    <col min="11" max="11" width="18" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:12" s="25" customFormat="1" ht="12.75" customHeight="1">
-      <c r="A1" s="31" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="103"/>
-      <c r="C1" s="103"/>
-      <c r="D1" s="103"/>
-      <c r="E1" s="32"/>
-      <c r="F1" s="32"/>
-      <c r="G1" s="32"/>
-      <c r="H1" s="32"/>
-      <c r="I1" s="32"/>
-      <c r="J1" s="52"/>
-      <c r="K1" s="32"/>
-      <c r="L1" s="33"/>
-    </row>
-    <row r="2" spans="1:12" s="25" customFormat="1" ht="11.25" customHeight="1" thickBot="1">
-      <c r="A2" s="33"/>
-      <c r="B2" s="104"/>
-      <c r="C2" s="104"/>
-      <c r="D2" s="104"/>
-      <c r="E2" s="32"/>
-      <c r="F2" s="32"/>
-      <c r="G2" s="32"/>
-      <c r="H2" s="32"/>
-      <c r="I2" s="32"/>
-      <c r="J2" s="52"/>
-      <c r="K2" s="32"/>
-      <c r="L2" s="33"/>
-    </row>
-    <row r="3" spans="1:12" s="26" customFormat="1" ht="15" customHeight="1">
-      <c r="A3" s="34" t="s">
-        <v>18</v>
-      </c>
-      <c r="B3" s="96" t="s">
-        <v>4</v>
-      </c>
-      <c r="C3" s="96"/>
-      <c r="D3" s="97"/>
-      <c r="E3" s="35"/>
-      <c r="F3" s="35"/>
-      <c r="G3" s="35"/>
-      <c r="H3" s="35"/>
-      <c r="I3" s="105"/>
-      <c r="J3" s="105"/>
-      <c r="K3" s="105"/>
-      <c r="L3" s="53"/>
-    </row>
-    <row r="4" spans="1:12" s="26" customFormat="1" ht="13.2">
-      <c r="A4" s="36" t="s">
-        <v>19</v>
-      </c>
-      <c r="B4" s="106" t="s">
-        <v>48</v>
-      </c>
-      <c r="C4" s="107"/>
-      <c r="D4" s="108"/>
-      <c r="E4" s="35"/>
-      <c r="F4" s="35"/>
-      <c r="G4" s="35"/>
-      <c r="H4" s="35"/>
-      <c r="I4" s="105"/>
-      <c r="J4" s="105"/>
-      <c r="K4" s="105"/>
-      <c r="L4" s="53"/>
-    </row>
-    <row r="5" spans="1:12" s="27" customFormat="1" ht="15" customHeight="1">
-      <c r="A5" s="36" t="s">
-        <v>20</v>
-      </c>
-      <c r="B5" s="99" t="s">
-        <v>44</v>
-      </c>
-      <c r="C5" s="100"/>
-      <c r="D5" s="101"/>
-      <c r="E5" s="37"/>
-      <c r="F5" s="37"/>
-      <c r="G5" s="37"/>
-      <c r="H5" s="37"/>
-      <c r="I5" s="102"/>
-      <c r="J5" s="102"/>
-      <c r="K5" s="102"/>
-      <c r="L5" s="54"/>
-    </row>
-    <row r="6" spans="1:12" s="26" customFormat="1" ht="15" customHeight="1">
-      <c r="A6" s="38" t="s">
-        <v>21</v>
-      </c>
-      <c r="B6" s="39">
-        <f>COUNTIF(J12:J33,"Pass")</f>
-        <v>0</v>
-      </c>
-      <c r="C6" s="40" t="s">
-        <v>22</v>
-      </c>
-      <c r="D6" s="41">
-        <f>COUNTIF(J10:J752,"Pending")</f>
-        <v>0</v>
-      </c>
-      <c r="E6" s="42"/>
-      <c r="F6" s="42"/>
-      <c r="G6" s="42"/>
-      <c r="H6" s="42"/>
-      <c r="I6" s="105"/>
-      <c r="J6" s="105"/>
-      <c r="K6" s="105"/>
-      <c r="L6" s="53"/>
-    </row>
-    <row r="7" spans="1:12" s="26" customFormat="1" ht="15" customHeight="1" thickBot="1">
-      <c r="A7" s="43" t="s">
-        <v>23</v>
-      </c>
-      <c r="B7" s="44">
-        <f>COUNTIF(J12:J33,"Fail")</f>
-        <v>0</v>
-      </c>
-      <c r="C7" s="45" t="s">
-        <v>24</v>
-      </c>
-      <c r="D7" s="46">
-        <f>COUNTIF(A12:A33, "TC*")</f>
-        <v>1</v>
-      </c>
-      <c r="E7" s="47"/>
-      <c r="F7" s="47"/>
-      <c r="G7" s="47"/>
-      <c r="H7" s="47"/>
-      <c r="I7" s="105"/>
-      <c r="J7" s="105"/>
-      <c r="K7" s="105"/>
-      <c r="L7" s="53"/>
-    </row>
-    <row r="8" spans="1:12" s="26" customFormat="1" ht="15" customHeight="1">
-      <c r="A8" s="110"/>
-      <c r="B8" s="110"/>
-      <c r="C8" s="110"/>
-      <c r="D8" s="110"/>
-      <c r="E8" s="42"/>
-      <c r="F8" s="42"/>
-      <c r="G8" s="42"/>
-      <c r="H8" s="42"/>
-      <c r="I8" s="42"/>
-      <c r="J8" s="55"/>
-      <c r="K8" s="55"/>
-      <c r="L8" s="53"/>
-    </row>
-    <row r="9" spans="1:12" s="28" customFormat="1" ht="12" customHeight="1">
-      <c r="A9" s="111" t="s">
-        <v>25</v>
-      </c>
-      <c r="B9" s="113" t="s">
-        <v>26</v>
-      </c>
-      <c r="C9" s="111" t="s">
-        <v>27</v>
-      </c>
-      <c r="D9" s="115" t="s">
-        <v>28</v>
-      </c>
-      <c r="E9" s="116"/>
-      <c r="F9" s="116"/>
-      <c r="G9" s="117"/>
-      <c r="H9" s="121" t="s">
-        <v>29</v>
-      </c>
-      <c r="I9" s="122" t="s">
-        <v>30</v>
-      </c>
-      <c r="J9" s="122" t="s">
-        <v>31</v>
-      </c>
-      <c r="K9" s="122" t="s">
-        <v>32</v>
-      </c>
-      <c r="L9" s="56"/>
-    </row>
-    <row r="10" spans="1:12" s="26" customFormat="1" ht="12" customHeight="1">
-      <c r="A10" s="112"/>
-      <c r="B10" s="114"/>
-      <c r="C10" s="112"/>
-      <c r="D10" s="118"/>
-      <c r="E10" s="119"/>
-      <c r="F10" s="119"/>
-      <c r="G10" s="120"/>
-      <c r="H10" s="111"/>
-      <c r="I10" s="111"/>
-      <c r="J10" s="111"/>
-      <c r="K10" s="111"/>
-      <c r="L10" s="53"/>
-    </row>
-    <row r="11" spans="1:12" s="29" customFormat="1" ht="15">
-      <c r="A11" s="123"/>
-      <c r="B11" s="123"/>
-      <c r="C11" s="123"/>
-      <c r="D11" s="123"/>
-      <c r="E11" s="123"/>
-      <c r="F11" s="123"/>
-      <c r="G11" s="123"/>
-      <c r="H11" s="123"/>
-      <c r="I11" s="123"/>
-      <c r="J11" s="123"/>
-      <c r="K11" s="124"/>
-    </row>
-    <row r="12" spans="1:12" s="30" customFormat="1" ht="13.2">
-      <c r="A12" s="125" t="s">
-        <v>33</v>
-      </c>
-      <c r="B12" s="126"/>
-      <c r="C12" s="126"/>
-      <c r="D12" s="126"/>
-      <c r="E12" s="126"/>
-      <c r="F12" s="126"/>
-      <c r="G12" s="126"/>
-      <c r="H12" s="126"/>
-      <c r="I12" s="126"/>
-      <c r="J12" s="126"/>
-      <c r="K12" s="127"/>
-    </row>
-    <row r="13" spans="1:12" s="30" customFormat="1" ht="13.2" outlineLevel="1">
-      <c r="A13" s="49" t="s">
-        <v>45</v>
-      </c>
-      <c r="B13" s="50"/>
-      <c r="C13" s="51"/>
-      <c r="D13" s="128"/>
-      <c r="E13" s="128"/>
-      <c r="F13" s="128"/>
-      <c r="G13" s="51"/>
-      <c r="H13" s="51"/>
-      <c r="I13" s="89"/>
-      <c r="J13" s="51"/>
-      <c r="K13" s="51"/>
-    </row>
-    <row r="14" spans="1:12" s="30" customFormat="1" ht="13.2" outlineLevel="1">
-      <c r="A14" s="49"/>
-      <c r="B14" s="50"/>
-      <c r="C14" s="51"/>
-      <c r="D14" s="109"/>
-      <c r="E14" s="109"/>
-      <c r="F14" s="109"/>
-      <c r="G14" s="51"/>
-      <c r="H14" s="51"/>
-      <c r="I14" s="89"/>
-      <c r="J14" s="51"/>
-      <c r="K14" s="51"/>
-    </row>
-    <row r="15" spans="1:12" s="30" customFormat="1" ht="13.2" outlineLevel="1">
-      <c r="A15" s="49"/>
-      <c r="B15" s="50"/>
-      <c r="C15" s="51"/>
-      <c r="D15" s="109"/>
-      <c r="E15" s="109"/>
-      <c r="F15" s="109"/>
-      <c r="G15" s="51"/>
-      <c r="H15" s="51"/>
-      <c r="I15" s="89"/>
-      <c r="J15" s="51"/>
-      <c r="K15" s="51"/>
-    </row>
-    <row r="16" spans="1:12" s="30" customFormat="1" ht="13.2" outlineLevel="1">
-      <c r="A16" s="49"/>
-      <c r="B16" s="50"/>
-      <c r="C16" s="51"/>
-      <c r="D16" s="109"/>
-      <c r="E16" s="109"/>
-      <c r="F16" s="109"/>
-      <c r="G16" s="51"/>
-      <c r="H16" s="51"/>
-      <c r="I16" s="89"/>
-      <c r="J16" s="51"/>
-      <c r="K16" s="51"/>
-    </row>
-    <row r="17" spans="1:11" s="30" customFormat="1" ht="13.2" outlineLevel="1">
-      <c r="A17" s="49"/>
-      <c r="B17" s="50"/>
-      <c r="C17" s="51"/>
-      <c r="D17" s="109"/>
-      <c r="E17" s="109"/>
-      <c r="F17" s="109"/>
-      <c r="G17" s="51"/>
-      <c r="H17" s="51"/>
-      <c r="I17" s="89"/>
-      <c r="J17" s="51"/>
-      <c r="K17" s="51"/>
-    </row>
-    <row r="18" spans="1:11" s="30" customFormat="1" ht="13.2" outlineLevel="1">
-      <c r="A18" s="49"/>
-      <c r="B18" s="50"/>
-      <c r="C18" s="51"/>
-      <c r="D18" s="109"/>
-      <c r="E18" s="109"/>
-      <c r="F18" s="109"/>
-      <c r="G18" s="51"/>
-      <c r="H18" s="51"/>
-      <c r="I18" s="89"/>
-      <c r="J18" s="51"/>
-      <c r="K18" s="51"/>
-    </row>
-    <row r="19" spans="1:11" s="30" customFormat="1" ht="13.2" outlineLevel="1">
-      <c r="A19" s="49"/>
-      <c r="B19" s="50"/>
-      <c r="C19" s="51"/>
-      <c r="D19" s="109"/>
-      <c r="E19" s="109"/>
-      <c r="F19" s="109"/>
-      <c r="G19" s="51"/>
-      <c r="H19" s="51"/>
-      <c r="I19" s="89"/>
-      <c r="J19" s="51"/>
-      <c r="K19" s="51"/>
-    </row>
-    <row r="20" spans="1:11" s="30" customFormat="1" ht="13.2" outlineLevel="1">
-      <c r="A20" s="129"/>
-      <c r="B20" s="130"/>
-      <c r="C20" s="130"/>
-      <c r="D20" s="48"/>
-      <c r="E20" s="48"/>
-      <c r="F20" s="48"/>
-      <c r="G20" s="48"/>
-      <c r="H20" s="48"/>
-      <c r="I20" s="48"/>
-      <c r="J20" s="48"/>
-      <c r="K20" s="57"/>
-    </row>
-    <row r="21" spans="1:11" s="30" customFormat="1" ht="13.2" outlineLevel="1">
-      <c r="A21" s="49"/>
-      <c r="B21" s="50"/>
-      <c r="C21" s="51"/>
-      <c r="D21" s="109"/>
-      <c r="E21" s="109"/>
-      <c r="F21" s="109"/>
-      <c r="G21" s="51"/>
-      <c r="H21" s="51"/>
-      <c r="I21" s="89"/>
-      <c r="J21" s="51"/>
-      <c r="K21" s="51"/>
-    </row>
-    <row r="22" spans="1:11" s="30" customFormat="1" ht="13.2" outlineLevel="1">
-      <c r="A22" s="49"/>
-      <c r="B22" s="50"/>
-      <c r="C22" s="51"/>
-      <c r="D22" s="109"/>
-      <c r="E22" s="109"/>
-      <c r="F22" s="109"/>
-      <c r="G22" s="51"/>
-      <c r="H22" s="51"/>
-      <c r="I22" s="89"/>
-      <c r="J22" s="51"/>
-      <c r="K22" s="51"/>
-    </row>
-    <row r="23" spans="1:11" s="30" customFormat="1" ht="13.2" outlineLevel="1">
-      <c r="A23" s="49"/>
-      <c r="B23" s="50"/>
-      <c r="C23" s="51"/>
-      <c r="D23" s="109"/>
-      <c r="E23" s="109"/>
-      <c r="F23" s="109"/>
-      <c r="G23" s="51"/>
-      <c r="H23" s="51"/>
-      <c r="I23" s="89"/>
-      <c r="J23" s="51"/>
-      <c r="K23" s="51"/>
-    </row>
-    <row r="24" spans="1:11" s="30" customFormat="1" ht="13.2" outlineLevel="1">
-      <c r="A24" s="49"/>
-      <c r="B24" s="50"/>
-      <c r="C24" s="51"/>
-      <c r="D24" s="109"/>
-      <c r="E24" s="109"/>
-      <c r="F24" s="109"/>
-      <c r="G24" s="51"/>
-      <c r="H24" s="51"/>
-      <c r="I24" s="89"/>
-      <c r="J24" s="51"/>
-      <c r="K24" s="51"/>
-    </row>
-    <row r="25" spans="1:11" s="30" customFormat="1" ht="13.2" outlineLevel="1">
-      <c r="A25" s="49"/>
-      <c r="B25" s="50"/>
-      <c r="C25" s="51"/>
-      <c r="D25" s="109"/>
-      <c r="E25" s="109"/>
-      <c r="F25" s="109"/>
-      <c r="G25" s="51"/>
-      <c r="H25" s="51"/>
-      <c r="I25" s="89"/>
-      <c r="J25" s="51"/>
-      <c r="K25" s="51"/>
-    </row>
-    <row r="26" spans="1:11" s="30" customFormat="1" ht="18" customHeight="1" outlineLevel="1">
-      <c r="A26" s="49"/>
-      <c r="B26" s="50"/>
-      <c r="C26" s="51"/>
-      <c r="D26" s="109"/>
-      <c r="E26" s="109"/>
-      <c r="F26" s="109"/>
-      <c r="G26" s="51"/>
-      <c r="H26" s="51"/>
-      <c r="I26" s="89"/>
-      <c r="J26" s="51"/>
-      <c r="K26" s="51"/>
-    </row>
-    <row r="27" spans="1:11" s="30" customFormat="1" ht="13.2" outlineLevel="1">
-      <c r="A27" s="129"/>
-      <c r="B27" s="130"/>
-      <c r="C27" s="130"/>
-      <c r="D27" s="48"/>
-      <c r="E27" s="48"/>
-      <c r="F27" s="48"/>
-      <c r="G27" s="48"/>
-      <c r="H27" s="48"/>
-      <c r="I27" s="48"/>
-      <c r="J27" s="48"/>
-      <c r="K27" s="57"/>
-    </row>
-    <row r="28" spans="1:11" s="30" customFormat="1" ht="13.2" outlineLevel="1">
-      <c r="A28" s="49"/>
-      <c r="B28" s="50"/>
-      <c r="C28" s="51"/>
-      <c r="D28" s="109"/>
-      <c r="E28" s="109"/>
-      <c r="F28" s="109"/>
-      <c r="G28" s="51"/>
-      <c r="H28" s="51"/>
-      <c r="I28" s="89"/>
-      <c r="J28" s="51"/>
-      <c r="K28" s="51"/>
-    </row>
-    <row r="29" spans="1:11" s="30" customFormat="1" ht="13.2" outlineLevel="1">
-      <c r="A29" s="49"/>
-      <c r="B29" s="50"/>
-      <c r="C29" s="51"/>
-      <c r="D29" s="109"/>
-      <c r="E29" s="109"/>
-      <c r="F29" s="109"/>
-      <c r="G29" s="51"/>
-      <c r="H29" s="51"/>
-      <c r="I29" s="89"/>
-      <c r="J29" s="51"/>
-      <c r="K29" s="51"/>
-    </row>
-    <row r="30" spans="1:11" s="30" customFormat="1" ht="13.2" outlineLevel="1">
-      <c r="A30" s="49"/>
-      <c r="B30" s="50"/>
-      <c r="C30" s="51"/>
-      <c r="D30" s="109"/>
-      <c r="E30" s="109"/>
-      <c r="F30" s="109"/>
-      <c r="G30" s="51"/>
-      <c r="H30" s="51"/>
-      <c r="I30" s="89"/>
-      <c r="J30" s="51"/>
-      <c r="K30" s="51"/>
-    </row>
-    <row r="31" spans="1:11" s="30" customFormat="1" ht="13.2" outlineLevel="1">
-      <c r="A31" s="49"/>
-      <c r="B31" s="50"/>
-      <c r="C31" s="51"/>
-      <c r="D31" s="109"/>
-      <c r="E31" s="109"/>
-      <c r="F31" s="109"/>
-      <c r="G31" s="51"/>
-      <c r="H31" s="51"/>
-      <c r="I31" s="89"/>
-      <c r="J31" s="51"/>
-      <c r="K31" s="51"/>
-    </row>
-    <row r="32" spans="1:11" s="30" customFormat="1" ht="13.2" outlineLevel="1">
-      <c r="A32" s="49"/>
-      <c r="B32" s="50"/>
-      <c r="C32" s="51"/>
-      <c r="D32" s="109"/>
-      <c r="E32" s="109"/>
-      <c r="F32" s="109"/>
-      <c r="G32" s="51"/>
-      <c r="H32" s="51"/>
-      <c r="I32" s="89"/>
-      <c r="J32" s="51"/>
-      <c r="K32" s="51"/>
-    </row>
-    <row r="33" spans="1:11" s="30" customFormat="1" ht="13.8" customHeight="1" outlineLevel="1">
-      <c r="A33" s="49"/>
-      <c r="B33" s="50"/>
-      <c r="C33" s="51"/>
-      <c r="D33" s="109"/>
-      <c r="E33" s="109"/>
-      <c r="F33" s="109"/>
-      <c r="G33" s="51"/>
-      <c r="H33" s="51"/>
-      <c r="I33" s="89"/>
-      <c r="J33" s="51"/>
-      <c r="K33" s="51"/>
-    </row>
-    <row r="34" spans="1:11" ht="12" customHeight="1"/>
-    <row r="35" spans="1:11" ht="12" customHeight="1"/>
-    <row r="36" spans="1:11" ht="12" customHeight="1"/>
-    <row r="37" spans="1:11" ht="12" customHeight="1"/>
-    <row r="38" spans="1:11" ht="12" customHeight="1"/>
-    <row r="39" spans="1:11" ht="12" customHeight="1"/>
-    <row r="40" spans="1:11" ht="12" customHeight="1"/>
-    <row r="41" spans="1:11" ht="12" customHeight="1"/>
-    <row r="42" spans="1:11" ht="12" customHeight="1"/>
-    <row r="43" spans="1:11" ht="12" customHeight="1"/>
-    <row r="44" spans="1:11" ht="12" customHeight="1"/>
-    <row r="45" spans="1:11" ht="12" customHeight="1"/>
-    <row r="46" spans="1:11" ht="12" customHeight="1"/>
-    <row r="47" spans="1:11" ht="12" customHeight="1"/>
-    <row r="48" spans="1:11" ht="12" customHeight="1"/>
-    <row r="49" ht="12" customHeight="1"/>
-    <row r="50" ht="12" customHeight="1"/>
-    <row r="51" ht="12" customHeight="1"/>
-    <row r="52" ht="12" customHeight="1"/>
-    <row r="53" ht="12" customHeight="1"/>
-    <row r="54" ht="12" customHeight="1"/>
-    <row r="55" ht="12" customHeight="1"/>
-    <row r="56" ht="12" customHeight="1"/>
-    <row r="57" ht="12" customHeight="1"/>
-    <row r="58" ht="12" customHeight="1"/>
-    <row r="59" ht="12" customHeight="1"/>
-    <row r="60" ht="12" customHeight="1"/>
-    <row r="61" ht="12" customHeight="1"/>
-    <row r="62" ht="12" customHeight="1"/>
-    <row r="63" ht="12" customHeight="1"/>
-    <row r="64" ht="12" customHeight="1"/>
-    <row r="65" ht="12" customHeight="1"/>
-    <row r="66" ht="12" customHeight="1"/>
-    <row r="67" ht="12" customHeight="1"/>
-    <row r="68" ht="12" customHeight="1"/>
-    <row r="69" ht="12" customHeight="1"/>
-    <row r="70" ht="12" customHeight="1"/>
-    <row r="71" ht="12" customHeight="1"/>
-  </sheetData>
-  <mergeCells count="41">
-    <mergeCell ref="B5:D5"/>
-    <mergeCell ref="I5:K5"/>
-    <mergeCell ref="B1:D2"/>
-    <mergeCell ref="B3:D3"/>
-    <mergeCell ref="I3:K3"/>
-    <mergeCell ref="B4:D4"/>
-    <mergeCell ref="I4:K4"/>
-    <mergeCell ref="D15:F15"/>
-    <mergeCell ref="I6:K6"/>
-    <mergeCell ref="I7:K7"/>
-    <mergeCell ref="A8:D8"/>
-    <mergeCell ref="A9:A10"/>
-    <mergeCell ref="B9:B10"/>
-    <mergeCell ref="C9:C10"/>
-    <mergeCell ref="D9:G10"/>
-    <mergeCell ref="H9:H10"/>
-    <mergeCell ref="I9:I10"/>
-    <mergeCell ref="J9:J10"/>
-    <mergeCell ref="K9:K10"/>
-    <mergeCell ref="A11:K11"/>
-    <mergeCell ref="A12:K12"/>
-    <mergeCell ref="D13:F13"/>
-    <mergeCell ref="D14:F14"/>
-    <mergeCell ref="A27:C27"/>
-    <mergeCell ref="D16:F16"/>
-    <mergeCell ref="D17:F17"/>
-    <mergeCell ref="D18:F18"/>
-    <mergeCell ref="D19:F19"/>
-    <mergeCell ref="A20:C20"/>
-    <mergeCell ref="D21:F21"/>
-    <mergeCell ref="D33:F33"/>
-    <mergeCell ref="D22:F22"/>
-    <mergeCell ref="D23:F23"/>
-    <mergeCell ref="D24:F24"/>
-    <mergeCell ref="D25:F25"/>
-    <mergeCell ref="D26:F26"/>
-    <mergeCell ref="D28:F28"/>
-    <mergeCell ref="D29:F29"/>
-    <mergeCell ref="D30:F30"/>
-    <mergeCell ref="D31:F31"/>
-    <mergeCell ref="D32:F32"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:G22"/>
@@ -3770,7 +4074,7 @@
       </c>
       <c r="G9" s="15">
         <f>User!D7</f>
-        <v>2</v>
+        <v>18</v>
       </c>
     </row>
     <row r="10" spans="1:7" s="1" customFormat="1" ht="13.8">
@@ -3891,7 +4195,7 @@
       </c>
       <c r="G19" s="19">
         <f>SUM(G6:G18)</f>
-        <v>4</v>
+        <v>20</v>
       </c>
     </row>
     <row r="20" spans="1:7" ht="13.8">

--- a/docs/docs_tester_cinema.xlsx
+++ b/docs/docs_tester_cinema.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Project\CineFlow\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{02A811D3-E4BE-4D4D-B712-1223E1AE8537}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D11FA951-D7FB-4EA0-B3E3-F4DC249DA293}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="821" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1306,119 +1306,11 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="12" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="13" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="12" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="15" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="16" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="24" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="18" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="24" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="18" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="25" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="3" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="26" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="28" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="29" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="30" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="27" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="32" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="15" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="16" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="31" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="15" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="16" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="17" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="15" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="16" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="17" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="7" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="6" borderId="15" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="165" fontId="22" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -1434,22 +1326,130 @@
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="25" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="3" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="26" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="28" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="29" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="30" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="12" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="13" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="15" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="16" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="6" borderId="15" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="31" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="24" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="18" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="24" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="18" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="27" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="32" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="15" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="16" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="17" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="15" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="16" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="17" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="12" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="15" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="16" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="5">
@@ -1851,11 +1851,11 @@
       <c r="B6" s="63" t="s">
         <v>3</v>
       </c>
-      <c r="C6" s="96" t="s">
+      <c r="C6" s="115" t="s">
         <v>4</v>
       </c>
-      <c r="D6" s="96"/>
-      <c r="E6" s="97"/>
+      <c r="D6" s="115"/>
+      <c r="E6" s="116"/>
       <c r="F6" s="61"/>
       <c r="G6" s="61"/>
     </row>
@@ -1864,11 +1864,11 @@
       <c r="B7" s="63" t="s">
         <v>5</v>
       </c>
-      <c r="C7" s="98" t="s">
+      <c r="C7" s="140" t="s">
         <v>46</v>
       </c>
-      <c r="D7" s="96"/>
-      <c r="E7" s="97"/>
+      <c r="D7" s="115"/>
+      <c r="E7" s="116"/>
       <c r="F7" s="61"/>
       <c r="G7" s="61"/>
     </row>
@@ -2071,9 +2071,9 @@
       <c r="A1" s="31" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="126"/>
-      <c r="C1" s="126"/>
-      <c r="D1" s="126"/>
+      <c r="B1" s="107"/>
+      <c r="C1" s="107"/>
+      <c r="D1" s="107"/>
       <c r="E1" s="32"/>
       <c r="F1" s="32"/>
       <c r="G1" s="32"/>
@@ -2085,9 +2085,9 @@
     </row>
     <row r="2" spans="1:12" s="25" customFormat="1" ht="11.25" customHeight="1" thickBot="1">
       <c r="A2" s="33"/>
-      <c r="B2" s="127"/>
-      <c r="C2" s="127"/>
-      <c r="D2" s="127"/>
+      <c r="B2" s="108"/>
+      <c r="C2" s="108"/>
+      <c r="D2" s="108"/>
       <c r="E2" s="32"/>
       <c r="F2" s="32"/>
       <c r="G2" s="32"/>
@@ -2101,54 +2101,54 @@
       <c r="A3" s="34" t="s">
         <v>18</v>
       </c>
-      <c r="B3" s="96" t="s">
+      <c r="B3" s="115" t="s">
         <v>4</v>
       </c>
-      <c r="C3" s="96"/>
-      <c r="D3" s="97"/>
+      <c r="C3" s="115"/>
+      <c r="D3" s="116"/>
       <c r="E3" s="35"/>
       <c r="F3" s="35"/>
       <c r="G3" s="35"/>
       <c r="H3" s="35"/>
-      <c r="I3" s="102"/>
-      <c r="J3" s="102"/>
-      <c r="K3" s="102"/>
+      <c r="I3" s="122"/>
+      <c r="J3" s="122"/>
+      <c r="K3" s="122"/>
       <c r="L3" s="53"/>
     </row>
     <row r="4" spans="1:12" s="26" customFormat="1" ht="13.2">
       <c r="A4" s="36" t="s">
         <v>19</v>
       </c>
-      <c r="B4" s="128" t="s">
+      <c r="B4" s="133" t="s">
         <v>49</v>
       </c>
-      <c r="C4" s="129"/>
-      <c r="D4" s="130"/>
+      <c r="C4" s="134"/>
+      <c r="D4" s="135"/>
       <c r="E4" s="35"/>
       <c r="F4" s="35"/>
       <c r="G4" s="35"/>
       <c r="H4" s="35"/>
-      <c r="I4" s="102"/>
-      <c r="J4" s="102"/>
-      <c r="K4" s="102"/>
+      <c r="I4" s="122"/>
+      <c r="J4" s="122"/>
+      <c r="K4" s="122"/>
       <c r="L4" s="53"/>
     </row>
     <row r="5" spans="1:12" s="27" customFormat="1" ht="15" customHeight="1">
       <c r="A5" s="36" t="s">
         <v>20</v>
       </c>
-      <c r="B5" s="122" t="s">
+      <c r="B5" s="136" t="s">
         <v>44</v>
       </c>
-      <c r="C5" s="123"/>
-      <c r="D5" s="124"/>
+      <c r="C5" s="137"/>
+      <c r="D5" s="138"/>
       <c r="E5" s="37"/>
       <c r="F5" s="37"/>
       <c r="G5" s="37"/>
       <c r="H5" s="37"/>
-      <c r="I5" s="125"/>
-      <c r="J5" s="125"/>
-      <c r="K5" s="125"/>
+      <c r="I5" s="139"/>
+      <c r="J5" s="139"/>
+      <c r="K5" s="139"/>
       <c r="L5" s="54"/>
     </row>
     <row r="6" spans="1:12" s="26" customFormat="1" ht="15" customHeight="1">
@@ -2170,9 +2170,9 @@
       <c r="F6" s="42"/>
       <c r="G6" s="42"/>
       <c r="H6" s="42"/>
-      <c r="I6" s="102"/>
-      <c r="J6" s="102"/>
-      <c r="K6" s="102"/>
+      <c r="I6" s="122"/>
+      <c r="J6" s="122"/>
+      <c r="K6" s="122"/>
       <c r="L6" s="53"/>
     </row>
     <row r="7" spans="1:12" s="26" customFormat="1" ht="15" customHeight="1" thickBot="1">
@@ -2194,16 +2194,16 @@
       <c r="F7" s="47"/>
       <c r="G7" s="47"/>
       <c r="H7" s="47"/>
-      <c r="I7" s="102"/>
-      <c r="J7" s="102"/>
-      <c r="K7" s="102"/>
+      <c r="I7" s="122"/>
+      <c r="J7" s="122"/>
+      <c r="K7" s="122"/>
       <c r="L7" s="53"/>
     </row>
     <row r="8" spans="1:12" s="26" customFormat="1" ht="15" customHeight="1">
-      <c r="A8" s="103"/>
-      <c r="B8" s="103"/>
-      <c r="C8" s="103"/>
-      <c r="D8" s="103"/>
+      <c r="A8" s="123"/>
+      <c r="B8" s="123"/>
+      <c r="C8" s="123"/>
+      <c r="D8" s="123"/>
       <c r="E8" s="42"/>
       <c r="F8" s="42"/>
       <c r="G8" s="42"/>
@@ -2214,76 +2214,76 @@
       <c r="L8" s="53"/>
     </row>
     <row r="9" spans="1:12" s="28" customFormat="1" ht="12" customHeight="1">
-      <c r="A9" s="104" t="s">
+      <c r="A9" s="127" t="s">
         <v>25</v>
       </c>
-      <c r="B9" s="106" t="s">
+      <c r="B9" s="129" t="s">
         <v>26</v>
       </c>
-      <c r="C9" s="104" t="s">
+      <c r="C9" s="127" t="s">
         <v>27</v>
       </c>
-      <c r="D9" s="108" t="s">
+      <c r="D9" s="109" t="s">
         <v>28</v>
       </c>
-      <c r="E9" s="109"/>
-      <c r="F9" s="109"/>
-      <c r="G9" s="110"/>
-      <c r="H9" s="114" t="s">
+      <c r="E9" s="110"/>
+      <c r="F9" s="110"/>
+      <c r="G9" s="111"/>
+      <c r="H9" s="131" t="s">
         <v>29</v>
       </c>
-      <c r="I9" s="115" t="s">
+      <c r="I9" s="132" t="s">
         <v>30</v>
       </c>
-      <c r="J9" s="115" t="s">
+      <c r="J9" s="132" t="s">
         <v>31</v>
       </c>
-      <c r="K9" s="115" t="s">
+      <c r="K9" s="132" t="s">
         <v>32</v>
       </c>
       <c r="L9" s="56"/>
     </row>
     <row r="10" spans="1:12" s="26" customFormat="1" ht="12" customHeight="1">
-      <c r="A10" s="105"/>
-      <c r="B10" s="107"/>
-      <c r="C10" s="105"/>
-      <c r="D10" s="111"/>
-      <c r="E10" s="112"/>
-      <c r="F10" s="112"/>
-      <c r="G10" s="113"/>
-      <c r="H10" s="104"/>
-      <c r="I10" s="104"/>
-      <c r="J10" s="104"/>
-      <c r="K10" s="104"/>
+      <c r="A10" s="128"/>
+      <c r="B10" s="130"/>
+      <c r="C10" s="128"/>
+      <c r="D10" s="112"/>
+      <c r="E10" s="113"/>
+      <c r="F10" s="113"/>
+      <c r="G10" s="114"/>
+      <c r="H10" s="127"/>
+      <c r="I10" s="127"/>
+      <c r="J10" s="127"/>
+      <c r="K10" s="127"/>
       <c r="L10" s="53"/>
     </row>
     <row r="11" spans="1:12" s="29" customFormat="1" ht="15">
-      <c r="A11" s="116"/>
-      <c r="B11" s="116"/>
-      <c r="C11" s="116"/>
-      <c r="D11" s="116"/>
-      <c r="E11" s="116"/>
-      <c r="F11" s="116"/>
-      <c r="G11" s="116"/>
-      <c r="H11" s="116"/>
-      <c r="I11" s="116"/>
-      <c r="J11" s="116"/>
-      <c r="K11" s="117"/>
+      <c r="A11" s="124"/>
+      <c r="B11" s="124"/>
+      <c r="C11" s="124"/>
+      <c r="D11" s="124"/>
+      <c r="E11" s="124"/>
+      <c r="F11" s="124"/>
+      <c r="G11" s="124"/>
+      <c r="H11" s="124"/>
+      <c r="I11" s="124"/>
+      <c r="J11" s="124"/>
+      <c r="K11" s="125"/>
     </row>
     <row r="12" spans="1:12" s="30" customFormat="1" ht="13.2">
-      <c r="A12" s="118" t="s">
+      <c r="A12" s="117" t="s">
         <v>33</v>
       </c>
-      <c r="B12" s="119"/>
-      <c r="C12" s="119"/>
-      <c r="D12" s="119"/>
-      <c r="E12" s="119"/>
-      <c r="F12" s="119"/>
-      <c r="G12" s="119"/>
-      <c r="H12" s="119"/>
-      <c r="I12" s="119"/>
-      <c r="J12" s="119"/>
-      <c r="K12" s="120"/>
+      <c r="B12" s="118"/>
+      <c r="C12" s="118"/>
+      <c r="D12" s="118"/>
+      <c r="E12" s="118"/>
+      <c r="F12" s="118"/>
+      <c r="G12" s="118"/>
+      <c r="H12" s="118"/>
+      <c r="I12" s="118"/>
+      <c r="J12" s="118"/>
+      <c r="K12" s="126"/>
     </row>
     <row r="13" spans="1:12" s="30" customFormat="1" ht="13.2" outlineLevel="1">
       <c r="A13" s="49" t="s">
@@ -2291,9 +2291,9 @@
       </c>
       <c r="B13" s="50"/>
       <c r="C13" s="51"/>
-      <c r="D13" s="121"/>
-      <c r="E13" s="121"/>
-      <c r="F13" s="121"/>
+      <c r="D13" s="142"/>
+      <c r="E13" s="142"/>
+      <c r="F13" s="142"/>
       <c r="G13" s="51"/>
       <c r="H13" s="51"/>
       <c r="I13" s="89"/>
@@ -2304,9 +2304,9 @@
       <c r="A14" s="49"/>
       <c r="B14" s="50"/>
       <c r="C14" s="51"/>
-      <c r="D14" s="99"/>
-      <c r="E14" s="99"/>
-      <c r="F14" s="99"/>
+      <c r="D14" s="141"/>
+      <c r="E14" s="141"/>
+      <c r="F14" s="141"/>
       <c r="G14" s="51"/>
       <c r="H14" s="51"/>
       <c r="I14" s="89"/>
@@ -2317,9 +2317,9 @@
       <c r="A15" s="49"/>
       <c r="B15" s="50"/>
       <c r="C15" s="51"/>
-      <c r="D15" s="99"/>
-      <c r="E15" s="99"/>
-      <c r="F15" s="99"/>
+      <c r="D15" s="141"/>
+      <c r="E15" s="141"/>
+      <c r="F15" s="141"/>
       <c r="G15" s="51"/>
       <c r="H15" s="51"/>
       <c r="I15" s="89"/>
@@ -2330,9 +2330,9 @@
       <c r="A16" s="49"/>
       <c r="B16" s="50"/>
       <c r="C16" s="51"/>
-      <c r="D16" s="99"/>
-      <c r="E16" s="99"/>
-      <c r="F16" s="99"/>
+      <c r="D16" s="141"/>
+      <c r="E16" s="141"/>
+      <c r="F16" s="141"/>
       <c r="G16" s="51"/>
       <c r="H16" s="51"/>
       <c r="I16" s="89"/>
@@ -2343,9 +2343,9 @@
       <c r="A17" s="49"/>
       <c r="B17" s="50"/>
       <c r="C17" s="51"/>
-      <c r="D17" s="99"/>
-      <c r="E17" s="99"/>
-      <c r="F17" s="99"/>
+      <c r="D17" s="141"/>
+      <c r="E17" s="141"/>
+      <c r="F17" s="141"/>
       <c r="G17" s="51"/>
       <c r="H17" s="51"/>
       <c r="I17" s="89"/>
@@ -2356,9 +2356,9 @@
       <c r="A18" s="49"/>
       <c r="B18" s="50"/>
       <c r="C18" s="51"/>
-      <c r="D18" s="99"/>
-      <c r="E18" s="99"/>
-      <c r="F18" s="99"/>
+      <c r="D18" s="141"/>
+      <c r="E18" s="141"/>
+      <c r="F18" s="141"/>
       <c r="G18" s="51"/>
       <c r="H18" s="51"/>
       <c r="I18" s="89"/>
@@ -2369,9 +2369,9 @@
       <c r="A19" s="49"/>
       <c r="B19" s="50"/>
       <c r="C19" s="51"/>
-      <c r="D19" s="99"/>
-      <c r="E19" s="99"/>
-      <c r="F19" s="99"/>
+      <c r="D19" s="141"/>
+      <c r="E19" s="141"/>
+      <c r="F19" s="141"/>
       <c r="G19" s="51"/>
       <c r="H19" s="51"/>
       <c r="I19" s="89"/>
@@ -2379,9 +2379,9 @@
       <c r="K19" s="51"/>
     </row>
     <row r="20" spans="1:11" s="30" customFormat="1" ht="13.2" outlineLevel="1">
-      <c r="A20" s="100"/>
-      <c r="B20" s="101"/>
-      <c r="C20" s="101"/>
+      <c r="A20" s="143"/>
+      <c r="B20" s="144"/>
+      <c r="C20" s="144"/>
       <c r="D20" s="48"/>
       <c r="E20" s="48"/>
       <c r="F20" s="48"/>
@@ -2395,9 +2395,9 @@
       <c r="A21" s="49"/>
       <c r="B21" s="50"/>
       <c r="C21" s="51"/>
-      <c r="D21" s="99"/>
-      <c r="E21" s="99"/>
-      <c r="F21" s="99"/>
+      <c r="D21" s="141"/>
+      <c r="E21" s="141"/>
+      <c r="F21" s="141"/>
       <c r="G21" s="51"/>
       <c r="H21" s="51"/>
       <c r="I21" s="89"/>
@@ -2408,9 +2408,9 @@
       <c r="A22" s="49"/>
       <c r="B22" s="50"/>
       <c r="C22" s="51"/>
-      <c r="D22" s="99"/>
-      <c r="E22" s="99"/>
-      <c r="F22" s="99"/>
+      <c r="D22" s="141"/>
+      <c r="E22" s="141"/>
+      <c r="F22" s="141"/>
       <c r="G22" s="51"/>
       <c r="H22" s="51"/>
       <c r="I22" s="89"/>
@@ -2421,9 +2421,9 @@
       <c r="A23" s="49"/>
       <c r="B23" s="50"/>
       <c r="C23" s="51"/>
-      <c r="D23" s="99"/>
-      <c r="E23" s="99"/>
-      <c r="F23" s="99"/>
+      <c r="D23" s="141"/>
+      <c r="E23" s="141"/>
+      <c r="F23" s="141"/>
       <c r="G23" s="51"/>
       <c r="H23" s="51"/>
       <c r="I23" s="89"/>
@@ -2434,9 +2434,9 @@
       <c r="A24" s="49"/>
       <c r="B24" s="50"/>
       <c r="C24" s="51"/>
-      <c r="D24" s="99"/>
-      <c r="E24" s="99"/>
-      <c r="F24" s="99"/>
+      <c r="D24" s="141"/>
+      <c r="E24" s="141"/>
+      <c r="F24" s="141"/>
       <c r="G24" s="51"/>
       <c r="H24" s="51"/>
       <c r="I24" s="89"/>
@@ -2447,9 +2447,9 @@
       <c r="A25" s="49"/>
       <c r="B25" s="50"/>
       <c r="C25" s="51"/>
-      <c r="D25" s="99"/>
-      <c r="E25" s="99"/>
-      <c r="F25" s="99"/>
+      <c r="D25" s="141"/>
+      <c r="E25" s="141"/>
+      <c r="F25" s="141"/>
       <c r="G25" s="51"/>
       <c r="H25" s="51"/>
       <c r="I25" s="89"/>
@@ -2460,9 +2460,9 @@
       <c r="A26" s="49"/>
       <c r="B26" s="50"/>
       <c r="C26" s="51"/>
-      <c r="D26" s="99"/>
-      <c r="E26" s="99"/>
-      <c r="F26" s="99"/>
+      <c r="D26" s="141"/>
+      <c r="E26" s="141"/>
+      <c r="F26" s="141"/>
       <c r="G26" s="51"/>
       <c r="H26" s="51"/>
       <c r="I26" s="89"/>
@@ -2470,9 +2470,9 @@
       <c r="K26" s="51"/>
     </row>
     <row r="27" spans="1:11" s="30" customFormat="1" ht="13.2" outlineLevel="1">
-      <c r="A27" s="100"/>
-      <c r="B27" s="101"/>
-      <c r="C27" s="101"/>
+      <c r="A27" s="143"/>
+      <c r="B27" s="144"/>
+      <c r="C27" s="144"/>
       <c r="D27" s="48"/>
       <c r="E27" s="48"/>
       <c r="F27" s="48"/>
@@ -2486,9 +2486,9 @@
       <c r="A28" s="49"/>
       <c r="B28" s="50"/>
       <c r="C28" s="51"/>
-      <c r="D28" s="99"/>
-      <c r="E28" s="99"/>
-      <c r="F28" s="99"/>
+      <c r="D28" s="141"/>
+      <c r="E28" s="141"/>
+      <c r="F28" s="141"/>
       <c r="G28" s="51"/>
       <c r="H28" s="51"/>
       <c r="I28" s="89"/>
@@ -2499,9 +2499,9 @@
       <c r="A29" s="49"/>
       <c r="B29" s="50"/>
       <c r="C29" s="51"/>
-      <c r="D29" s="99"/>
-      <c r="E29" s="99"/>
-      <c r="F29" s="99"/>
+      <c r="D29" s="141"/>
+      <c r="E29" s="141"/>
+      <c r="F29" s="141"/>
       <c r="G29" s="51"/>
       <c r="H29" s="51"/>
       <c r="I29" s="89"/>
@@ -2512,9 +2512,9 @@
       <c r="A30" s="49"/>
       <c r="B30" s="50"/>
       <c r="C30" s="51"/>
-      <c r="D30" s="99"/>
-      <c r="E30" s="99"/>
-      <c r="F30" s="99"/>
+      <c r="D30" s="141"/>
+      <c r="E30" s="141"/>
+      <c r="F30" s="141"/>
       <c r="G30" s="51"/>
       <c r="H30" s="51"/>
       <c r="I30" s="89"/>
@@ -2525,9 +2525,9 @@
       <c r="A31" s="49"/>
       <c r="B31" s="50"/>
       <c r="C31" s="51"/>
-      <c r="D31" s="99"/>
-      <c r="E31" s="99"/>
-      <c r="F31" s="99"/>
+      <c r="D31" s="141"/>
+      <c r="E31" s="141"/>
+      <c r="F31" s="141"/>
       <c r="G31" s="51"/>
       <c r="H31" s="51"/>
       <c r="I31" s="89"/>
@@ -2538,9 +2538,9 @@
       <c r="A32" s="49"/>
       <c r="B32" s="50"/>
       <c r="C32" s="51"/>
-      <c r="D32" s="99"/>
-      <c r="E32" s="99"/>
-      <c r="F32" s="99"/>
+      <c r="D32" s="141"/>
+      <c r="E32" s="141"/>
+      <c r="F32" s="141"/>
       <c r="G32" s="51"/>
       <c r="H32" s="51"/>
       <c r="I32" s="89"/>
@@ -2551,9 +2551,1300 @@
       <c r="A33" s="49"/>
       <c r="B33" s="50"/>
       <c r="C33" s="51"/>
-      <c r="D33" s="99"/>
-      <c r="E33" s="99"/>
-      <c r="F33" s="99"/>
+      <c r="D33" s="141"/>
+      <c r="E33" s="141"/>
+      <c r="F33" s="141"/>
+      <c r="G33" s="51"/>
+      <c r="H33" s="51"/>
+      <c r="I33" s="89"/>
+      <c r="J33" s="51"/>
+      <c r="K33" s="51"/>
+    </row>
+    <row r="34" spans="1:11" ht="12" customHeight="1"/>
+    <row r="35" spans="1:11" ht="12" customHeight="1"/>
+    <row r="36" spans="1:11" ht="12" customHeight="1"/>
+    <row r="37" spans="1:11" ht="12" customHeight="1"/>
+    <row r="38" spans="1:11" ht="12" customHeight="1"/>
+    <row r="39" spans="1:11" ht="12" customHeight="1"/>
+    <row r="40" spans="1:11" ht="12" customHeight="1"/>
+    <row r="41" spans="1:11" ht="12" customHeight="1"/>
+    <row r="42" spans="1:11" ht="12" customHeight="1"/>
+    <row r="43" spans="1:11" ht="12" customHeight="1"/>
+    <row r="44" spans="1:11" ht="12" customHeight="1"/>
+    <row r="45" spans="1:11" ht="12" customHeight="1"/>
+    <row r="46" spans="1:11" ht="12" customHeight="1"/>
+    <row r="47" spans="1:11" ht="12" customHeight="1"/>
+    <row r="48" spans="1:11" ht="12" customHeight="1"/>
+    <row r="49" ht="12" customHeight="1"/>
+    <row r="50" ht="12" customHeight="1"/>
+    <row r="51" ht="12" customHeight="1"/>
+    <row r="52" ht="12" customHeight="1"/>
+    <row r="53" ht="12" customHeight="1"/>
+    <row r="54" ht="12" customHeight="1"/>
+    <row r="55" ht="12" customHeight="1"/>
+    <row r="56" ht="12" customHeight="1"/>
+    <row r="57" ht="12" customHeight="1"/>
+    <row r="58" ht="12" customHeight="1"/>
+    <row r="59" ht="12" customHeight="1"/>
+    <row r="60" ht="12" customHeight="1"/>
+    <row r="61" ht="12" customHeight="1"/>
+    <row r="62" ht="12" customHeight="1"/>
+    <row r="63" ht="12" customHeight="1"/>
+    <row r="64" ht="12" customHeight="1"/>
+    <row r="65" ht="12" customHeight="1"/>
+    <row r="66" ht="12" customHeight="1"/>
+    <row r="67" ht="12" customHeight="1"/>
+    <row r="68" ht="12" customHeight="1"/>
+    <row r="69" ht="12" customHeight="1"/>
+    <row r="70" ht="12" customHeight="1"/>
+    <row r="71" ht="12" customHeight="1"/>
+  </sheetData>
+  <mergeCells count="41">
+    <mergeCell ref="D33:F33"/>
+    <mergeCell ref="D22:F22"/>
+    <mergeCell ref="D23:F23"/>
+    <mergeCell ref="D24:F24"/>
+    <mergeCell ref="D25:F25"/>
+    <mergeCell ref="D26:F26"/>
+    <mergeCell ref="D28:F28"/>
+    <mergeCell ref="D29:F29"/>
+    <mergeCell ref="D30:F30"/>
+    <mergeCell ref="D31:F31"/>
+    <mergeCell ref="D32:F32"/>
+    <mergeCell ref="A27:C27"/>
+    <mergeCell ref="D16:F16"/>
+    <mergeCell ref="D17:F17"/>
+    <mergeCell ref="D18:F18"/>
+    <mergeCell ref="D19:F19"/>
+    <mergeCell ref="A20:C20"/>
+    <mergeCell ref="D21:F21"/>
+    <mergeCell ref="D15:F15"/>
+    <mergeCell ref="I6:K6"/>
+    <mergeCell ref="I7:K7"/>
+    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="A9:A10"/>
+    <mergeCell ref="B9:B10"/>
+    <mergeCell ref="C9:C10"/>
+    <mergeCell ref="D9:G10"/>
+    <mergeCell ref="H9:H10"/>
+    <mergeCell ref="I9:I10"/>
+    <mergeCell ref="J9:J10"/>
+    <mergeCell ref="K9:K10"/>
+    <mergeCell ref="A11:K11"/>
+    <mergeCell ref="A12:K12"/>
+    <mergeCell ref="D13:F13"/>
+    <mergeCell ref="D14:F14"/>
+    <mergeCell ref="B5:D5"/>
+    <mergeCell ref="I5:K5"/>
+    <mergeCell ref="B1:D2"/>
+    <mergeCell ref="B3:D3"/>
+    <mergeCell ref="I3:K3"/>
+    <mergeCell ref="B4:D4"/>
+    <mergeCell ref="I4:K4"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <sheetPr>
+    <outlinePr summaryBelow="0" summaryRight="0"/>
+  </sheetPr>
+  <dimension ref="A1:K72"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="13.8" outlineLevelRow="1"/>
+  <cols>
+    <col min="1" max="1" width="18" customWidth="1"/>
+    <col min="2" max="2" width="18.109375" customWidth="1"/>
+    <col min="3" max="3" width="42.109375" customWidth="1"/>
+    <col min="4" max="4" width="28.109375" customWidth="1"/>
+    <col min="5" max="5" width="13.109375" customWidth="1"/>
+    <col min="6" max="6" width="18.44140625" hidden="1" customWidth="1"/>
+    <col min="7" max="7" width="38" customWidth="1"/>
+    <col min="8" max="8" width="17.109375" customWidth="1"/>
+    <col min="9" max="9" width="9" style="6"/>
+    <col min="10" max="10" width="18" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:11" s="25" customFormat="1" ht="12.75" customHeight="1">
+      <c r="A1" s="31" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="107"/>
+      <c r="C1" s="107"/>
+      <c r="D1" s="107"/>
+      <c r="E1" s="32"/>
+      <c r="F1" s="32"/>
+      <c r="G1" s="32"/>
+      <c r="H1" s="32"/>
+      <c r="I1" s="52"/>
+      <c r="J1" s="32"/>
+      <c r="K1" s="33"/>
+    </row>
+    <row r="2" spans="1:11" s="25" customFormat="1" ht="11.25" customHeight="1" thickBot="1">
+      <c r="A2" s="33"/>
+      <c r="B2" s="108"/>
+      <c r="C2" s="108"/>
+      <c r="D2" s="108"/>
+      <c r="E2" s="32"/>
+      <c r="F2" s="32"/>
+      <c r="G2" s="32"/>
+      <c r="H2" s="32"/>
+      <c r="I2" s="52"/>
+      <c r="J2" s="32"/>
+      <c r="K2" s="33"/>
+    </row>
+    <row r="3" spans="1:11" s="26" customFormat="1" ht="15" customHeight="1">
+      <c r="A3" s="34" t="s">
+        <v>18</v>
+      </c>
+      <c r="B3" s="115" t="s">
+        <v>4</v>
+      </c>
+      <c r="C3" s="115"/>
+      <c r="D3" s="116"/>
+      <c r="E3" s="35"/>
+      <c r="F3" s="35"/>
+      <c r="G3" s="35"/>
+      <c r="H3" s="122"/>
+      <c r="I3" s="122"/>
+      <c r="J3" s="122"/>
+      <c r="K3" s="53"/>
+    </row>
+    <row r="4" spans="1:11" s="26" customFormat="1" ht="13.2">
+      <c r="A4" s="36" t="s">
+        <v>19</v>
+      </c>
+      <c r="B4" s="133" t="s">
+        <v>50</v>
+      </c>
+      <c r="C4" s="134"/>
+      <c r="D4" s="135"/>
+      <c r="E4" s="35"/>
+      <c r="F4" s="35"/>
+      <c r="G4" s="35"/>
+      <c r="H4" s="122"/>
+      <c r="I4" s="122"/>
+      <c r="J4" s="122"/>
+      <c r="K4" s="53"/>
+    </row>
+    <row r="5" spans="1:11" s="27" customFormat="1" ht="15" customHeight="1">
+      <c r="A5" s="36" t="s">
+        <v>20</v>
+      </c>
+      <c r="B5" s="136" t="s">
+        <v>44</v>
+      </c>
+      <c r="C5" s="137"/>
+      <c r="D5" s="138"/>
+      <c r="E5" s="37"/>
+      <c r="F5" s="37"/>
+      <c r="G5" s="37"/>
+      <c r="H5" s="139"/>
+      <c r="I5" s="139"/>
+      <c r="J5" s="139"/>
+      <c r="K5" s="54"/>
+    </row>
+    <row r="6" spans="1:11" s="26" customFormat="1" ht="15" customHeight="1">
+      <c r="A6" s="38" t="s">
+        <v>21</v>
+      </c>
+      <c r="B6" s="39">
+        <f>COUNTIF(I12:I34,"Pass")</f>
+        <v>0</v>
+      </c>
+      <c r="C6" s="40" t="s">
+        <v>22</v>
+      </c>
+      <c r="D6" s="41">
+        <f>COUNTIF(I10:I753,"Pending")</f>
+        <v>0</v>
+      </c>
+      <c r="E6" s="42"/>
+      <c r="F6" s="42"/>
+      <c r="G6" s="42"/>
+      <c r="H6" s="122"/>
+      <c r="I6" s="122"/>
+      <c r="J6" s="122"/>
+      <c r="K6" s="53"/>
+    </row>
+    <row r="7" spans="1:11" s="26" customFormat="1" ht="15" customHeight="1" thickBot="1">
+      <c r="A7" s="43" t="s">
+        <v>23</v>
+      </c>
+      <c r="B7" s="44">
+        <f>COUNTIF(I12:I34,"Fail")</f>
+        <v>0</v>
+      </c>
+      <c r="C7" s="45" t="s">
+        <v>24</v>
+      </c>
+      <c r="D7" s="46">
+        <f>COUNTIF(A12:A34, "TC*")</f>
+        <v>18</v>
+      </c>
+      <c r="E7" s="47"/>
+      <c r="F7" s="47"/>
+      <c r="G7" s="47"/>
+      <c r="H7" s="122"/>
+      <c r="I7" s="122"/>
+      <c r="J7" s="122"/>
+      <c r="K7" s="53"/>
+    </row>
+    <row r="8" spans="1:11" s="26" customFormat="1" ht="15" customHeight="1">
+      <c r="A8" s="123"/>
+      <c r="B8" s="123"/>
+      <c r="C8" s="123"/>
+      <c r="D8" s="123"/>
+      <c r="E8" s="42"/>
+      <c r="F8" s="42"/>
+      <c r="G8" s="42"/>
+      <c r="H8" s="42"/>
+      <c r="I8" s="55"/>
+      <c r="J8" s="55"/>
+      <c r="K8" s="53"/>
+    </row>
+    <row r="9" spans="1:11" s="28" customFormat="1" ht="12" customHeight="1">
+      <c r="A9" s="127" t="s">
+        <v>25</v>
+      </c>
+      <c r="B9" s="129" t="s">
+        <v>26</v>
+      </c>
+      <c r="C9" s="127" t="s">
+        <v>27</v>
+      </c>
+      <c r="D9" s="109" t="s">
+        <v>28</v>
+      </c>
+      <c r="E9" s="110"/>
+      <c r="F9" s="111"/>
+      <c r="G9" s="131" t="s">
+        <v>29</v>
+      </c>
+      <c r="H9" s="132" t="s">
+        <v>30</v>
+      </c>
+      <c r="I9" s="132" t="s">
+        <v>31</v>
+      </c>
+      <c r="J9" s="132" t="s">
+        <v>32</v>
+      </c>
+      <c r="K9" s="56"/>
+    </row>
+    <row r="10" spans="1:11" s="26" customFormat="1" ht="12" customHeight="1">
+      <c r="A10" s="128"/>
+      <c r="B10" s="130"/>
+      <c r="C10" s="128"/>
+      <c r="D10" s="112"/>
+      <c r="E10" s="113"/>
+      <c r="F10" s="114"/>
+      <c r="G10" s="127"/>
+      <c r="H10" s="127"/>
+      <c r="I10" s="127"/>
+      <c r="J10" s="127"/>
+      <c r="K10" s="53"/>
+    </row>
+    <row r="11" spans="1:11" s="29" customFormat="1" ht="15">
+      <c r="A11" s="124"/>
+      <c r="B11" s="124"/>
+      <c r="C11" s="124"/>
+      <c r="D11" s="124"/>
+      <c r="E11" s="124"/>
+      <c r="F11" s="124"/>
+      <c r="G11" s="124"/>
+      <c r="H11" s="124"/>
+      <c r="I11" s="124"/>
+      <c r="J11" s="125"/>
+    </row>
+    <row r="12" spans="1:11" s="30" customFormat="1" ht="13.2">
+      <c r="A12" s="117" t="s">
+        <v>51</v>
+      </c>
+      <c r="B12" s="118"/>
+      <c r="C12" s="118"/>
+      <c r="D12" s="118"/>
+      <c r="E12" s="118"/>
+      <c r="F12" s="118"/>
+      <c r="G12" s="118"/>
+      <c r="H12" s="118"/>
+      <c r="I12" s="118"/>
+      <c r="J12" s="126"/>
+    </row>
+    <row r="13" spans="1:11" s="30" customFormat="1" ht="26.4" outlineLevel="1">
+      <c r="A13" s="49" t="s">
+        <v>45</v>
+      </c>
+      <c r="B13" s="50" t="s">
+        <v>52</v>
+      </c>
+      <c r="C13" s="51" t="s">
+        <v>53</v>
+      </c>
+      <c r="D13" s="103" t="s">
+        <v>54</v>
+      </c>
+      <c r="E13" s="104"/>
+      <c r="F13" s="51"/>
+      <c r="G13" s="51"/>
+      <c r="H13" s="89"/>
+      <c r="I13" s="51"/>
+      <c r="J13" s="51"/>
+    </row>
+    <row r="14" spans="1:11" s="30" customFormat="1" ht="13.2" outlineLevel="1">
+      <c r="A14" s="49" t="s">
+        <v>47</v>
+      </c>
+      <c r="B14" s="50" t="s">
+        <v>55</v>
+      </c>
+      <c r="C14" s="51" t="s">
+        <v>56</v>
+      </c>
+      <c r="D14" s="105" t="s">
+        <v>57</v>
+      </c>
+      <c r="E14" s="106"/>
+      <c r="F14" s="51"/>
+      <c r="G14" s="51"/>
+      <c r="H14" s="89"/>
+      <c r="I14" s="51"/>
+      <c r="J14" s="51"/>
+    </row>
+    <row r="15" spans="1:11" s="30" customFormat="1" ht="26.4" outlineLevel="1">
+      <c r="A15" s="49" t="s">
+        <v>70</v>
+      </c>
+      <c r="B15" s="50" t="s">
+        <v>58</v>
+      </c>
+      <c r="C15" s="51" t="s">
+        <v>59</v>
+      </c>
+      <c r="D15" s="105" t="s">
+        <v>60</v>
+      </c>
+      <c r="E15" s="106"/>
+      <c r="F15" s="51"/>
+      <c r="G15" s="51"/>
+      <c r="H15" s="89"/>
+      <c r="I15" s="51"/>
+      <c r="J15" s="51"/>
+    </row>
+    <row r="16" spans="1:11" s="30" customFormat="1" ht="13.2" outlineLevel="1">
+      <c r="A16" s="49" t="s">
+        <v>71</v>
+      </c>
+      <c r="B16" s="50" t="s">
+        <v>63</v>
+      </c>
+      <c r="C16" s="51" t="s">
+        <v>64</v>
+      </c>
+      <c r="D16" s="105"/>
+      <c r="E16" s="106"/>
+      <c r="F16" s="51"/>
+      <c r="G16" s="51"/>
+      <c r="H16" s="89"/>
+      <c r="I16" s="51"/>
+      <c r="J16" s="51"/>
+    </row>
+    <row r="17" spans="1:10" s="30" customFormat="1" ht="13.2" outlineLevel="1">
+      <c r="A17" s="49" t="s">
+        <v>72</v>
+      </c>
+      <c r="B17" s="50" t="s">
+        <v>65</v>
+      </c>
+      <c r="C17" s="51" t="s">
+        <v>66</v>
+      </c>
+      <c r="D17" s="105"/>
+      <c r="E17" s="106"/>
+      <c r="F17" s="51"/>
+      <c r="G17" s="51"/>
+      <c r="H17" s="89"/>
+      <c r="I17" s="51"/>
+      <c r="J17" s="51"/>
+    </row>
+    <row r="18" spans="1:10" s="30" customFormat="1" ht="26.4" outlineLevel="1">
+      <c r="A18" s="49" t="s">
+        <v>73</v>
+      </c>
+      <c r="B18" s="50" t="s">
+        <v>67</v>
+      </c>
+      <c r="C18" s="51" t="s">
+        <v>68</v>
+      </c>
+      <c r="D18" s="105"/>
+      <c r="E18" s="106"/>
+      <c r="F18" s="51"/>
+      <c r="G18" s="51"/>
+      <c r="H18" s="89"/>
+      <c r="I18" s="51"/>
+      <c r="J18" s="51"/>
+    </row>
+    <row r="19" spans="1:10" s="30" customFormat="1" ht="26.4" outlineLevel="1">
+      <c r="A19" s="49" t="s">
+        <v>80</v>
+      </c>
+      <c r="B19" s="50" t="s">
+        <v>81</v>
+      </c>
+      <c r="C19" s="96" t="s">
+        <v>82</v>
+      </c>
+      <c r="D19" s="105"/>
+      <c r="E19" s="106"/>
+      <c r="F19" s="51"/>
+      <c r="G19" s="51"/>
+      <c r="H19" s="89"/>
+      <c r="I19" s="51"/>
+      <c r="J19" s="51"/>
+    </row>
+    <row r="20" spans="1:10" s="30" customFormat="1" ht="13.2" outlineLevel="1">
+      <c r="A20" s="117" t="s">
+        <v>69</v>
+      </c>
+      <c r="B20" s="118"/>
+      <c r="C20" s="118"/>
+      <c r="D20" s="48"/>
+      <c r="E20" s="48"/>
+      <c r="F20" s="48"/>
+      <c r="G20" s="48"/>
+      <c r="H20" s="48"/>
+      <c r="I20" s="48"/>
+      <c r="J20" s="57"/>
+    </row>
+    <row r="21" spans="1:10" s="30" customFormat="1" ht="13.2" outlineLevel="1">
+      <c r="A21" s="49" t="s">
+        <v>45</v>
+      </c>
+      <c r="B21" s="50" t="s">
+        <v>74</v>
+      </c>
+      <c r="C21" s="51" t="s">
+        <v>75</v>
+      </c>
+      <c r="D21" s="105"/>
+      <c r="E21" s="106"/>
+      <c r="F21" s="51"/>
+      <c r="G21" s="51"/>
+      <c r="H21" s="89"/>
+      <c r="I21" s="51"/>
+      <c r="J21" s="51"/>
+    </row>
+    <row r="22" spans="1:10" s="30" customFormat="1" ht="13.2" outlineLevel="1">
+      <c r="A22" s="49" t="s">
+        <v>47</v>
+      </c>
+      <c r="B22" s="50" t="s">
+        <v>76</v>
+      </c>
+      <c r="C22" s="51" t="s">
+        <v>77</v>
+      </c>
+      <c r="D22" s="105"/>
+      <c r="E22" s="106"/>
+      <c r="F22" s="51"/>
+      <c r="G22" s="51"/>
+      <c r="H22" s="89"/>
+      <c r="I22" s="51"/>
+      <c r="J22" s="51"/>
+    </row>
+    <row r="23" spans="1:10" s="30" customFormat="1" ht="13.2" outlineLevel="1">
+      <c r="A23" s="49" t="s">
+        <v>70</v>
+      </c>
+      <c r="B23" s="50" t="s">
+        <v>65</v>
+      </c>
+      <c r="C23" s="51"/>
+      <c r="D23" s="105"/>
+      <c r="E23" s="106"/>
+      <c r="F23" s="51"/>
+      <c r="G23" s="51"/>
+      <c r="H23" s="89"/>
+      <c r="I23" s="51"/>
+      <c r="J23" s="51"/>
+    </row>
+    <row r="24" spans="1:10" s="30" customFormat="1" ht="13.2" outlineLevel="1">
+      <c r="A24" s="49" t="s">
+        <v>71</v>
+      </c>
+      <c r="B24" s="50" t="s">
+        <v>78</v>
+      </c>
+      <c r="C24" s="51" t="s">
+        <v>79</v>
+      </c>
+      <c r="D24" s="105"/>
+      <c r="E24" s="106"/>
+      <c r="F24" s="51"/>
+      <c r="G24" s="51"/>
+      <c r="H24" s="89"/>
+      <c r="I24" s="51"/>
+      <c r="J24" s="51"/>
+    </row>
+    <row r="25" spans="1:10" s="30" customFormat="1" ht="13.2" outlineLevel="1">
+      <c r="A25" s="49" t="s">
+        <v>72</v>
+      </c>
+      <c r="B25" s="50" t="s">
+        <v>83</v>
+      </c>
+      <c r="C25" s="51" t="s">
+        <v>68</v>
+      </c>
+      <c r="D25" s="105"/>
+      <c r="E25" s="106"/>
+      <c r="F25" s="51"/>
+      <c r="G25" s="51"/>
+      <c r="H25" s="89"/>
+      <c r="I25" s="51"/>
+      <c r="J25" s="51"/>
+    </row>
+    <row r="26" spans="1:10" s="30" customFormat="1" ht="26.4" outlineLevel="1">
+      <c r="A26" s="49" t="s">
+        <v>73</v>
+      </c>
+      <c r="B26" s="50" t="s">
+        <v>81</v>
+      </c>
+      <c r="C26" s="96" t="s">
+        <v>82</v>
+      </c>
+      <c r="D26" s="51"/>
+      <c r="E26" s="51"/>
+      <c r="F26" s="51"/>
+      <c r="G26" s="51"/>
+      <c r="H26" s="89"/>
+      <c r="I26" s="51"/>
+      <c r="J26" s="51"/>
+    </row>
+    <row r="27" spans="1:10" s="30" customFormat="1" ht="18" customHeight="1" outlineLevel="1">
+      <c r="A27" s="97" t="s">
+        <v>80</v>
+      </c>
+      <c r="B27" s="97" t="s">
+        <v>84</v>
+      </c>
+      <c r="C27" s="97" t="s">
+        <v>85</v>
+      </c>
+      <c r="D27" s="105"/>
+      <c r="E27" s="106"/>
+      <c r="F27" s="51"/>
+      <c r="G27" s="51"/>
+      <c r="H27" s="89"/>
+      <c r="I27" s="51"/>
+      <c r="J27" s="51"/>
+    </row>
+    <row r="28" spans="1:10" s="30" customFormat="1" ht="13.2" outlineLevel="1">
+      <c r="A28" s="119" t="s">
+        <v>86</v>
+      </c>
+      <c r="B28" s="118"/>
+      <c r="C28" s="118"/>
+      <c r="D28" s="48"/>
+      <c r="E28" s="48"/>
+      <c r="F28" s="48"/>
+      <c r="G28" s="48"/>
+      <c r="H28" s="48"/>
+      <c r="I28" s="48"/>
+      <c r="J28" s="57"/>
+    </row>
+    <row r="29" spans="1:10" s="30" customFormat="1" ht="26.4" outlineLevel="1">
+      <c r="A29" s="98" t="s">
+        <v>45</v>
+      </c>
+      <c r="B29" s="99" t="s">
+        <v>88</v>
+      </c>
+      <c r="C29" s="100" t="s">
+        <v>90</v>
+      </c>
+      <c r="D29" s="101" t="s">
+        <v>92</v>
+      </c>
+      <c r="F29" s="51"/>
+      <c r="G29" s="51"/>
+      <c r="H29" s="89"/>
+      <c r="I29" s="51"/>
+      <c r="J29" s="51"/>
+    </row>
+    <row r="30" spans="1:10" s="30" customFormat="1" ht="26.4" outlineLevel="1">
+      <c r="A30" s="98" t="s">
+        <v>47</v>
+      </c>
+      <c r="B30" s="99" t="s">
+        <v>89</v>
+      </c>
+      <c r="C30" s="100" t="s">
+        <v>87</v>
+      </c>
+      <c r="D30" s="120" t="s">
+        <v>91</v>
+      </c>
+      <c r="E30" s="121"/>
+      <c r="F30" s="51"/>
+      <c r="G30" s="51"/>
+      <c r="H30" s="89"/>
+      <c r="I30" s="51"/>
+      <c r="J30" s="51"/>
+    </row>
+    <row r="31" spans="1:10" s="30" customFormat="1" ht="26.4" outlineLevel="1">
+      <c r="A31" s="98" t="s">
+        <v>61</v>
+      </c>
+      <c r="B31" s="99" t="s">
+        <v>93</v>
+      </c>
+      <c r="C31" s="102" t="s">
+        <v>94</v>
+      </c>
+      <c r="D31" s="105"/>
+      <c r="E31" s="106"/>
+      <c r="F31" s="51"/>
+      <c r="G31" s="51"/>
+      <c r="H31" s="89"/>
+      <c r="I31" s="51"/>
+      <c r="J31" s="51"/>
+    </row>
+    <row r="32" spans="1:10" s="30" customFormat="1" ht="13.2" outlineLevel="1">
+      <c r="A32" s="98" t="s">
+        <v>62</v>
+      </c>
+      <c r="B32" s="99" t="s">
+        <v>95</v>
+      </c>
+      <c r="C32" s="102" t="s">
+        <v>96</v>
+      </c>
+      <c r="D32" s="105"/>
+      <c r="E32" s="106"/>
+      <c r="F32" s="51"/>
+      <c r="G32" s="51"/>
+      <c r="H32" s="89"/>
+      <c r="I32" s="51"/>
+      <c r="J32" s="51"/>
+    </row>
+    <row r="33" spans="1:10" s="30" customFormat="1" ht="13.2" outlineLevel="1">
+      <c r="A33" s="49"/>
+      <c r="B33" s="50"/>
+      <c r="C33" s="51"/>
+      <c r="D33" s="105"/>
+      <c r="E33" s="106"/>
+      <c r="F33" s="51"/>
+      <c r="G33" s="51"/>
+      <c r="H33" s="89"/>
+      <c r="I33" s="51"/>
+      <c r="J33" s="51"/>
+    </row>
+    <row r="34" spans="1:10" s="30" customFormat="1" ht="13.8" customHeight="1" outlineLevel="1">
+      <c r="A34" s="49"/>
+      <c r="B34" s="50"/>
+      <c r="C34" s="51"/>
+      <c r="D34" s="105"/>
+      <c r="E34" s="106"/>
+      <c r="F34" s="51"/>
+      <c r="G34" s="51"/>
+      <c r="H34" s="89"/>
+      <c r="I34" s="51"/>
+      <c r="J34" s="51"/>
+    </row>
+    <row r="35" spans="1:10" ht="12" customHeight="1"/>
+    <row r="36" spans="1:10" ht="12" customHeight="1"/>
+    <row r="37" spans="1:10" ht="12" customHeight="1"/>
+    <row r="38" spans="1:10" ht="12" customHeight="1"/>
+    <row r="39" spans="1:10" ht="12" customHeight="1"/>
+    <row r="40" spans="1:10" ht="12" customHeight="1"/>
+    <row r="41" spans="1:10" ht="12" customHeight="1"/>
+    <row r="42" spans="1:10" ht="12" customHeight="1"/>
+    <row r="43" spans="1:10" ht="12" customHeight="1"/>
+    <row r="44" spans="1:10" ht="12" customHeight="1"/>
+    <row r="45" spans="1:10" ht="12" customHeight="1"/>
+    <row r="46" spans="1:10" ht="12" customHeight="1"/>
+    <row r="47" spans="1:10" ht="12" customHeight="1"/>
+    <row r="48" spans="1:10" ht="12" customHeight="1"/>
+    <row r="49" ht="12" customHeight="1"/>
+    <row r="50" ht="12" customHeight="1"/>
+    <row r="51" ht="12" customHeight="1"/>
+    <row r="52" ht="12" customHeight="1"/>
+    <row r="53" ht="12" customHeight="1"/>
+    <row r="54" ht="12" customHeight="1"/>
+    <row r="55" ht="12" customHeight="1"/>
+    <row r="56" ht="12" customHeight="1"/>
+    <row r="57" ht="12" customHeight="1"/>
+    <row r="58" ht="12" customHeight="1"/>
+    <row r="59" ht="12" customHeight="1"/>
+    <row r="60" ht="12" customHeight="1"/>
+    <row r="61" ht="12" customHeight="1"/>
+    <row r="62" ht="12" customHeight="1"/>
+    <row r="63" ht="12" customHeight="1"/>
+    <row r="64" ht="12" customHeight="1"/>
+    <row r="65" ht="12" customHeight="1"/>
+    <row r="66" ht="12" customHeight="1"/>
+    <row r="67" ht="12" customHeight="1"/>
+    <row r="68" ht="12" customHeight="1"/>
+    <row r="69" ht="12" customHeight="1"/>
+    <row r="70" ht="12" customHeight="1"/>
+    <row r="71" ht="12" customHeight="1"/>
+    <row r="72" ht="12" customHeight="1"/>
+  </sheetData>
+  <mergeCells count="40">
+    <mergeCell ref="H3:J3"/>
+    <mergeCell ref="B4:D4"/>
+    <mergeCell ref="H4:J4"/>
+    <mergeCell ref="B5:D5"/>
+    <mergeCell ref="H5:J5"/>
+    <mergeCell ref="H6:J6"/>
+    <mergeCell ref="H7:J7"/>
+    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="A11:J11"/>
+    <mergeCell ref="A12:J12"/>
+    <mergeCell ref="A9:A10"/>
+    <mergeCell ref="B9:B10"/>
+    <mergeCell ref="C9:C10"/>
+    <mergeCell ref="G9:G10"/>
+    <mergeCell ref="H9:H10"/>
+    <mergeCell ref="I9:I10"/>
+    <mergeCell ref="J9:J10"/>
+    <mergeCell ref="A20:C20"/>
+    <mergeCell ref="D27:E27"/>
+    <mergeCell ref="A28:C28"/>
+    <mergeCell ref="D34:E34"/>
+    <mergeCell ref="D21:E21"/>
+    <mergeCell ref="D30:E30"/>
+    <mergeCell ref="D22:E22"/>
+    <mergeCell ref="D23:E23"/>
+    <mergeCell ref="D24:E24"/>
+    <mergeCell ref="D25:E25"/>
+    <mergeCell ref="D31:E31"/>
+    <mergeCell ref="D32:E32"/>
+    <mergeCell ref="D33:E33"/>
+    <mergeCell ref="D18:E18"/>
+    <mergeCell ref="B1:D2"/>
+    <mergeCell ref="D9:F10"/>
+    <mergeCell ref="B3:D3"/>
+    <mergeCell ref="D19:E19"/>
+    <mergeCell ref="D13:E13"/>
+    <mergeCell ref="D17:E17"/>
+    <mergeCell ref="D16:E16"/>
+    <mergeCell ref="D15:E15"/>
+    <mergeCell ref="D14:E14"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
+  <headerFooter alignWithMargins="0"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{20690ED2-4B8F-4386-AEC9-67E105CBDE46}">
+  <dimension ref="A1:L71"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="13.8" outlineLevelRow="1"/>
+  <cols>
+    <col min="1" max="1" width="18" customWidth="1"/>
+    <col min="2" max="2" width="18.109375" customWidth="1"/>
+    <col min="3" max="3" width="42.109375" customWidth="1"/>
+    <col min="6" max="6" width="23.6640625" customWidth="1"/>
+    <col min="7" max="7" width="18.44140625" hidden="1" customWidth="1"/>
+    <col min="8" max="8" width="38" customWidth="1"/>
+    <col min="9" max="9" width="17.109375" customWidth="1"/>
+    <col min="10" max="10" width="8.77734375" style="6"/>
+    <col min="11" max="11" width="18" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:12" s="25" customFormat="1" ht="12.75" customHeight="1">
+      <c r="A1" s="31" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="107"/>
+      <c r="C1" s="107"/>
+      <c r="D1" s="107"/>
+      <c r="E1" s="32"/>
+      <c r="F1" s="32"/>
+      <c r="G1" s="32"/>
+      <c r="H1" s="32"/>
+      <c r="I1" s="32"/>
+      <c r="J1" s="52"/>
+      <c r="K1" s="32"/>
+      <c r="L1" s="33"/>
+    </row>
+    <row r="2" spans="1:12" s="25" customFormat="1" ht="11.25" customHeight="1" thickBot="1">
+      <c r="A2" s="33"/>
+      <c r="B2" s="108"/>
+      <c r="C2" s="108"/>
+      <c r="D2" s="108"/>
+      <c r="E2" s="32"/>
+      <c r="F2" s="32"/>
+      <c r="G2" s="32"/>
+      <c r="H2" s="32"/>
+      <c r="I2" s="32"/>
+      <c r="J2" s="52"/>
+      <c r="K2" s="32"/>
+      <c r="L2" s="33"/>
+    </row>
+    <row r="3" spans="1:12" s="26" customFormat="1" ht="15" customHeight="1">
+      <c r="A3" s="34" t="s">
+        <v>18</v>
+      </c>
+      <c r="B3" s="115" t="s">
+        <v>4</v>
+      </c>
+      <c r="C3" s="115"/>
+      <c r="D3" s="116"/>
+      <c r="E3" s="35"/>
+      <c r="F3" s="35"/>
+      <c r="G3" s="35"/>
+      <c r="H3" s="35"/>
+      <c r="I3" s="122"/>
+      <c r="J3" s="122"/>
+      <c r="K3" s="122"/>
+      <c r="L3" s="53"/>
+    </row>
+    <row r="4" spans="1:12" s="26" customFormat="1" ht="13.2">
+      <c r="A4" s="36" t="s">
+        <v>19</v>
+      </c>
+      <c r="B4" s="133" t="s">
+        <v>48</v>
+      </c>
+      <c r="C4" s="134"/>
+      <c r="D4" s="135"/>
+      <c r="E4" s="35"/>
+      <c r="F4" s="35"/>
+      <c r="G4" s="35"/>
+      <c r="H4" s="35"/>
+      <c r="I4" s="122"/>
+      <c r="J4" s="122"/>
+      <c r="K4" s="122"/>
+      <c r="L4" s="53"/>
+    </row>
+    <row r="5" spans="1:12" s="27" customFormat="1" ht="15" customHeight="1">
+      <c r="A5" s="36" t="s">
+        <v>20</v>
+      </c>
+      <c r="B5" s="136" t="s">
+        <v>44</v>
+      </c>
+      <c r="C5" s="137"/>
+      <c r="D5" s="138"/>
+      <c r="E5" s="37"/>
+      <c r="F5" s="37"/>
+      <c r="G5" s="37"/>
+      <c r="H5" s="37"/>
+      <c r="I5" s="139"/>
+      <c r="J5" s="139"/>
+      <c r="K5" s="139"/>
+      <c r="L5" s="54"/>
+    </row>
+    <row r="6" spans="1:12" s="26" customFormat="1" ht="15" customHeight="1">
+      <c r="A6" s="38" t="s">
+        <v>21</v>
+      </c>
+      <c r="B6" s="39">
+        <f>COUNTIF(J12:J33,"Pass")</f>
+        <v>0</v>
+      </c>
+      <c r="C6" s="40" t="s">
+        <v>22</v>
+      </c>
+      <c r="D6" s="41">
+        <f>COUNTIF(J10:J752,"Pending")</f>
+        <v>0</v>
+      </c>
+      <c r="E6" s="42"/>
+      <c r="F6" s="42"/>
+      <c r="G6" s="42"/>
+      <c r="H6" s="42"/>
+      <c r="I6" s="122"/>
+      <c r="J6" s="122"/>
+      <c r="K6" s="122"/>
+      <c r="L6" s="53"/>
+    </row>
+    <row r="7" spans="1:12" s="26" customFormat="1" ht="15" customHeight="1" thickBot="1">
+      <c r="A7" s="43" t="s">
+        <v>23</v>
+      </c>
+      <c r="B7" s="44">
+        <f>COUNTIF(J12:J33,"Fail")</f>
+        <v>0</v>
+      </c>
+      <c r="C7" s="45" t="s">
+        <v>24</v>
+      </c>
+      <c r="D7" s="46">
+        <f>COUNTIF(A12:A33, "TC*")</f>
+        <v>1</v>
+      </c>
+      <c r="E7" s="47"/>
+      <c r="F7" s="47"/>
+      <c r="G7" s="47"/>
+      <c r="H7" s="47"/>
+      <c r="I7" s="122"/>
+      <c r="J7" s="122"/>
+      <c r="K7" s="122"/>
+      <c r="L7" s="53"/>
+    </row>
+    <row r="8" spans="1:12" s="26" customFormat="1" ht="15" customHeight="1">
+      <c r="A8" s="123"/>
+      <c r="B8" s="123"/>
+      <c r="C8" s="123"/>
+      <c r="D8" s="123"/>
+      <c r="E8" s="42"/>
+      <c r="F8" s="42"/>
+      <c r="G8" s="42"/>
+      <c r="H8" s="42"/>
+      <c r="I8" s="42"/>
+      <c r="J8" s="55"/>
+      <c r="K8" s="55"/>
+      <c r="L8" s="53"/>
+    </row>
+    <row r="9" spans="1:12" s="28" customFormat="1" ht="12" customHeight="1">
+      <c r="A9" s="127" t="s">
+        <v>25</v>
+      </c>
+      <c r="B9" s="129" t="s">
+        <v>26</v>
+      </c>
+      <c r="C9" s="127" t="s">
+        <v>27</v>
+      </c>
+      <c r="D9" s="109" t="s">
+        <v>28</v>
+      </c>
+      <c r="E9" s="110"/>
+      <c r="F9" s="110"/>
+      <c r="G9" s="111"/>
+      <c r="H9" s="131" t="s">
+        <v>29</v>
+      </c>
+      <c r="I9" s="132" t="s">
+        <v>30</v>
+      </c>
+      <c r="J9" s="132" t="s">
+        <v>31</v>
+      </c>
+      <c r="K9" s="132" t="s">
+        <v>32</v>
+      </c>
+      <c r="L9" s="56"/>
+    </row>
+    <row r="10" spans="1:12" s="26" customFormat="1" ht="12" customHeight="1">
+      <c r="A10" s="128"/>
+      <c r="B10" s="130"/>
+      <c r="C10" s="128"/>
+      <c r="D10" s="112"/>
+      <c r="E10" s="113"/>
+      <c r="F10" s="113"/>
+      <c r="G10" s="114"/>
+      <c r="H10" s="127"/>
+      <c r="I10" s="127"/>
+      <c r="J10" s="127"/>
+      <c r="K10" s="127"/>
+      <c r="L10" s="53"/>
+    </row>
+    <row r="11" spans="1:12" s="29" customFormat="1" ht="15">
+      <c r="A11" s="124"/>
+      <c r="B11" s="124"/>
+      <c r="C11" s="124"/>
+      <c r="D11" s="124"/>
+      <c r="E11" s="124"/>
+      <c r="F11" s="124"/>
+      <c r="G11" s="124"/>
+      <c r="H11" s="124"/>
+      <c r="I11" s="124"/>
+      <c r="J11" s="124"/>
+      <c r="K11" s="125"/>
+    </row>
+    <row r="12" spans="1:12" s="30" customFormat="1" ht="13.2">
+      <c r="A12" s="117" t="s">
+        <v>33</v>
+      </c>
+      <c r="B12" s="118"/>
+      <c r="C12" s="118"/>
+      <c r="D12" s="118"/>
+      <c r="E12" s="118"/>
+      <c r="F12" s="118"/>
+      <c r="G12" s="118"/>
+      <c r="H12" s="118"/>
+      <c r="I12" s="118"/>
+      <c r="J12" s="118"/>
+      <c r="K12" s="126"/>
+    </row>
+    <row r="13" spans="1:12" s="30" customFormat="1" ht="13.2" outlineLevel="1">
+      <c r="A13" s="49" t="s">
+        <v>45</v>
+      </c>
+      <c r="B13" s="50"/>
+      <c r="C13" s="51"/>
+      <c r="D13" s="142"/>
+      <c r="E13" s="142"/>
+      <c r="F13" s="142"/>
+      <c r="G13" s="51"/>
+      <c r="H13" s="51"/>
+      <c r="I13" s="89"/>
+      <c r="J13" s="51"/>
+      <c r="K13" s="51"/>
+    </row>
+    <row r="14" spans="1:12" s="30" customFormat="1" ht="13.2" outlineLevel="1">
+      <c r="A14" s="49"/>
+      <c r="B14" s="50"/>
+      <c r="C14" s="51"/>
+      <c r="D14" s="141"/>
+      <c r="E14" s="141"/>
+      <c r="F14" s="141"/>
+      <c r="G14" s="51"/>
+      <c r="H14" s="51"/>
+      <c r="I14" s="89"/>
+      <c r="J14" s="51"/>
+      <c r="K14" s="51"/>
+    </row>
+    <row r="15" spans="1:12" s="30" customFormat="1" ht="13.2" outlineLevel="1">
+      <c r="A15" s="49"/>
+      <c r="B15" s="50"/>
+      <c r="C15" s="51"/>
+      <c r="D15" s="141"/>
+      <c r="E15" s="141"/>
+      <c r="F15" s="141"/>
+      <c r="G15" s="51"/>
+      <c r="H15" s="51"/>
+      <c r="I15" s="89"/>
+      <c r="J15" s="51"/>
+      <c r="K15" s="51"/>
+    </row>
+    <row r="16" spans="1:12" s="30" customFormat="1" ht="13.2" outlineLevel="1">
+      <c r="A16" s="49"/>
+      <c r="B16" s="50"/>
+      <c r="C16" s="51"/>
+      <c r="D16" s="141"/>
+      <c r="E16" s="141"/>
+      <c r="F16" s="141"/>
+      <c r="G16" s="51"/>
+      <c r="H16" s="51"/>
+      <c r="I16" s="89"/>
+      <c r="J16" s="51"/>
+      <c r="K16" s="51"/>
+    </row>
+    <row r="17" spans="1:11" s="30" customFormat="1" ht="13.2" outlineLevel="1">
+      <c r="A17" s="49"/>
+      <c r="B17" s="50"/>
+      <c r="C17" s="51"/>
+      <c r="D17" s="141"/>
+      <c r="E17" s="141"/>
+      <c r="F17" s="141"/>
+      <c r="G17" s="51"/>
+      <c r="H17" s="51"/>
+      <c r="I17" s="89"/>
+      <c r="J17" s="51"/>
+      <c r="K17" s="51"/>
+    </row>
+    <row r="18" spans="1:11" s="30" customFormat="1" ht="13.2" outlineLevel="1">
+      <c r="A18" s="49"/>
+      <c r="B18" s="50"/>
+      <c r="C18" s="51"/>
+      <c r="D18" s="141"/>
+      <c r="E18" s="141"/>
+      <c r="F18" s="141"/>
+      <c r="G18" s="51"/>
+      <c r="H18" s="51"/>
+      <c r="I18" s="89"/>
+      <c r="J18" s="51"/>
+      <c r="K18" s="51"/>
+    </row>
+    <row r="19" spans="1:11" s="30" customFormat="1" ht="13.2" outlineLevel="1">
+      <c r="A19" s="49"/>
+      <c r="B19" s="50"/>
+      <c r="C19" s="51"/>
+      <c r="D19" s="141"/>
+      <c r="E19" s="141"/>
+      <c r="F19" s="141"/>
+      <c r="G19" s="51"/>
+      <c r="H19" s="51"/>
+      <c r="I19" s="89"/>
+      <c r="J19" s="51"/>
+      <c r="K19" s="51"/>
+    </row>
+    <row r="20" spans="1:11" s="30" customFormat="1" ht="13.2" outlineLevel="1">
+      <c r="A20" s="143"/>
+      <c r="B20" s="144"/>
+      <c r="C20" s="144"/>
+      <c r="D20" s="48"/>
+      <c r="E20" s="48"/>
+      <c r="F20" s="48"/>
+      <c r="G20" s="48"/>
+      <c r="H20" s="48"/>
+      <c r="I20" s="48"/>
+      <c r="J20" s="48"/>
+      <c r="K20" s="57"/>
+    </row>
+    <row r="21" spans="1:11" s="30" customFormat="1" ht="13.2" outlineLevel="1">
+      <c r="A21" s="49"/>
+      <c r="B21" s="50"/>
+      <c r="C21" s="51"/>
+      <c r="D21" s="141"/>
+      <c r="E21" s="141"/>
+      <c r="F21" s="141"/>
+      <c r="G21" s="51"/>
+      <c r="H21" s="51"/>
+      <c r="I21" s="89"/>
+      <c r="J21" s="51"/>
+      <c r="K21" s="51"/>
+    </row>
+    <row r="22" spans="1:11" s="30" customFormat="1" ht="13.2" outlineLevel="1">
+      <c r="A22" s="49"/>
+      <c r="B22" s="50"/>
+      <c r="C22" s="51"/>
+      <c r="D22" s="141"/>
+      <c r="E22" s="141"/>
+      <c r="F22" s="141"/>
+      <c r="G22" s="51"/>
+      <c r="H22" s="51"/>
+      <c r="I22" s="89"/>
+      <c r="J22" s="51"/>
+      <c r="K22" s="51"/>
+    </row>
+    <row r="23" spans="1:11" s="30" customFormat="1" ht="13.2" outlineLevel="1">
+      <c r="A23" s="49"/>
+      <c r="B23" s="50"/>
+      <c r="C23" s="51"/>
+      <c r="D23" s="141"/>
+      <c r="E23" s="141"/>
+      <c r="F23" s="141"/>
+      <c r="G23" s="51"/>
+      <c r="H23" s="51"/>
+      <c r="I23" s="89"/>
+      <c r="J23" s="51"/>
+      <c r="K23" s="51"/>
+    </row>
+    <row r="24" spans="1:11" s="30" customFormat="1" ht="13.2" outlineLevel="1">
+      <c r="A24" s="49"/>
+      <c r="B24" s="50"/>
+      <c r="C24" s="51"/>
+      <c r="D24" s="141"/>
+      <c r="E24" s="141"/>
+      <c r="F24" s="141"/>
+      <c r="G24" s="51"/>
+      <c r="H24" s="51"/>
+      <c r="I24" s="89"/>
+      <c r="J24" s="51"/>
+      <c r="K24" s="51"/>
+    </row>
+    <row r="25" spans="1:11" s="30" customFormat="1" ht="13.2" outlineLevel="1">
+      <c r="A25" s="49"/>
+      <c r="B25" s="50"/>
+      <c r="C25" s="51"/>
+      <c r="D25" s="141"/>
+      <c r="E25" s="141"/>
+      <c r="F25" s="141"/>
+      <c r="G25" s="51"/>
+      <c r="H25" s="51"/>
+      <c r="I25" s="89"/>
+      <c r="J25" s="51"/>
+      <c r="K25" s="51"/>
+    </row>
+    <row r="26" spans="1:11" s="30" customFormat="1" ht="18" customHeight="1" outlineLevel="1">
+      <c r="A26" s="49"/>
+      <c r="B26" s="50"/>
+      <c r="C26" s="51"/>
+      <c r="D26" s="141"/>
+      <c r="E26" s="141"/>
+      <c r="F26" s="141"/>
+      <c r="G26" s="51"/>
+      <c r="H26" s="51"/>
+      <c r="I26" s="89"/>
+      <c r="J26" s="51"/>
+      <c r="K26" s="51"/>
+    </row>
+    <row r="27" spans="1:11" s="30" customFormat="1" ht="13.2" outlineLevel="1">
+      <c r="A27" s="143"/>
+      <c r="B27" s="144"/>
+      <c r="C27" s="144"/>
+      <c r="D27" s="48"/>
+      <c r="E27" s="48"/>
+      <c r="F27" s="48"/>
+      <c r="G27" s="48"/>
+      <c r="H27" s="48"/>
+      <c r="I27" s="48"/>
+      <c r="J27" s="48"/>
+      <c r="K27" s="57"/>
+    </row>
+    <row r="28" spans="1:11" s="30" customFormat="1" ht="13.2" outlineLevel="1">
+      <c r="A28" s="49"/>
+      <c r="B28" s="50"/>
+      <c r="C28" s="51"/>
+      <c r="D28" s="141"/>
+      <c r="E28" s="141"/>
+      <c r="F28" s="141"/>
+      <c r="G28" s="51"/>
+      <c r="H28" s="51"/>
+      <c r="I28" s="89"/>
+      <c r="J28" s="51"/>
+      <c r="K28" s="51"/>
+    </row>
+    <row r="29" spans="1:11" s="30" customFormat="1" ht="13.2" outlineLevel="1">
+      <c r="A29" s="49"/>
+      <c r="B29" s="50"/>
+      <c r="C29" s="51"/>
+      <c r="D29" s="141"/>
+      <c r="E29" s="141"/>
+      <c r="F29" s="141"/>
+      <c r="G29" s="51"/>
+      <c r="H29" s="51"/>
+      <c r="I29" s="89"/>
+      <c r="J29" s="51"/>
+      <c r="K29" s="51"/>
+    </row>
+    <row r="30" spans="1:11" s="30" customFormat="1" ht="13.2" outlineLevel="1">
+      <c r="A30" s="49"/>
+      <c r="B30" s="50"/>
+      <c r="C30" s="51"/>
+      <c r="D30" s="141"/>
+      <c r="E30" s="141"/>
+      <c r="F30" s="141"/>
+      <c r="G30" s="51"/>
+      <c r="H30" s="51"/>
+      <c r="I30" s="89"/>
+      <c r="J30" s="51"/>
+      <c r="K30" s="51"/>
+    </row>
+    <row r="31" spans="1:11" s="30" customFormat="1" ht="13.2" outlineLevel="1">
+      <c r="A31" s="49"/>
+      <c r="B31" s="50"/>
+      <c r="C31" s="51"/>
+      <c r="D31" s="141"/>
+      <c r="E31" s="141"/>
+      <c r="F31" s="141"/>
+      <c r="G31" s="51"/>
+      <c r="H31" s="51"/>
+      <c r="I31" s="89"/>
+      <c r="J31" s="51"/>
+      <c r="K31" s="51"/>
+    </row>
+    <row r="32" spans="1:11" s="30" customFormat="1" ht="13.2" outlineLevel="1">
+      <c r="A32" s="49"/>
+      <c r="B32" s="50"/>
+      <c r="C32" s="51"/>
+      <c r="D32" s="141"/>
+      <c r="E32" s="141"/>
+      <c r="F32" s="141"/>
+      <c r="G32" s="51"/>
+      <c r="H32" s="51"/>
+      <c r="I32" s="89"/>
+      <c r="J32" s="51"/>
+      <c r="K32" s="51"/>
+    </row>
+    <row r="33" spans="1:11" s="30" customFormat="1" ht="13.8" customHeight="1" outlineLevel="1">
+      <c r="A33" s="49"/>
+      <c r="B33" s="50"/>
+      <c r="C33" s="51"/>
+      <c r="D33" s="141"/>
+      <c r="E33" s="141"/>
+      <c r="F33" s="141"/>
       <c r="G33" s="51"/>
       <c r="H33" s="51"/>
       <c r="I33" s="89"/>
@@ -2646,1297 +3937,6 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <sheetPr>
-    <outlinePr summaryBelow="0" summaryRight="0"/>
-  </sheetPr>
-  <dimension ref="A1:K72"/>
-  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="13.8" outlineLevelRow="1"/>
-  <cols>
-    <col min="1" max="1" width="18" customWidth="1"/>
-    <col min="2" max="2" width="18.109375" customWidth="1"/>
-    <col min="3" max="3" width="42.109375" customWidth="1"/>
-    <col min="4" max="4" width="28.109375" customWidth="1"/>
-    <col min="5" max="5" width="13.109375" customWidth="1"/>
-    <col min="6" max="6" width="18.44140625" hidden="1" customWidth="1"/>
-    <col min="7" max="7" width="38" customWidth="1"/>
-    <col min="8" max="8" width="17.109375" customWidth="1"/>
-    <col min="9" max="9" width="9" style="6"/>
-    <col min="10" max="10" width="18" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:11" s="25" customFormat="1" ht="12.75" customHeight="1">
-      <c r="A1" s="31" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="126"/>
-      <c r="C1" s="126"/>
-      <c r="D1" s="126"/>
-      <c r="E1" s="32"/>
-      <c r="F1" s="32"/>
-      <c r="G1" s="32"/>
-      <c r="H1" s="32"/>
-      <c r="I1" s="52"/>
-      <c r="J1" s="32"/>
-      <c r="K1" s="33"/>
-    </row>
-    <row r="2" spans="1:11" s="25" customFormat="1" ht="11.25" customHeight="1" thickBot="1">
-      <c r="A2" s="33"/>
-      <c r="B2" s="127"/>
-      <c r="C2" s="127"/>
-      <c r="D2" s="127"/>
-      <c r="E2" s="32"/>
-      <c r="F2" s="32"/>
-      <c r="G2" s="32"/>
-      <c r="H2" s="32"/>
-      <c r="I2" s="52"/>
-      <c r="J2" s="32"/>
-      <c r="K2" s="33"/>
-    </row>
-    <row r="3" spans="1:11" s="26" customFormat="1" ht="15" customHeight="1">
-      <c r="A3" s="34" t="s">
-        <v>18</v>
-      </c>
-      <c r="B3" s="96" t="s">
-        <v>4</v>
-      </c>
-      <c r="C3" s="96"/>
-      <c r="D3" s="97"/>
-      <c r="E3" s="35"/>
-      <c r="F3" s="35"/>
-      <c r="G3" s="35"/>
-      <c r="H3" s="102"/>
-      <c r="I3" s="102"/>
-      <c r="J3" s="102"/>
-      <c r="K3" s="53"/>
-    </row>
-    <row r="4" spans="1:11" s="26" customFormat="1" ht="13.2">
-      <c r="A4" s="36" t="s">
-        <v>19</v>
-      </c>
-      <c r="B4" s="128" t="s">
-        <v>50</v>
-      </c>
-      <c r="C4" s="129"/>
-      <c r="D4" s="130"/>
-      <c r="E4" s="35"/>
-      <c r="F4" s="35"/>
-      <c r="G4" s="35"/>
-      <c r="H4" s="102"/>
-      <c r="I4" s="102"/>
-      <c r="J4" s="102"/>
-      <c r="K4" s="53"/>
-    </row>
-    <row r="5" spans="1:11" s="27" customFormat="1" ht="15" customHeight="1">
-      <c r="A5" s="36" t="s">
-        <v>20</v>
-      </c>
-      <c r="B5" s="122" t="s">
-        <v>44</v>
-      </c>
-      <c r="C5" s="123"/>
-      <c r="D5" s="124"/>
-      <c r="E5" s="37"/>
-      <c r="F5" s="37"/>
-      <c r="G5" s="37"/>
-      <c r="H5" s="125"/>
-      <c r="I5" s="125"/>
-      <c r="J5" s="125"/>
-      <c r="K5" s="54"/>
-    </row>
-    <row r="6" spans="1:11" s="26" customFormat="1" ht="15" customHeight="1">
-      <c r="A6" s="38" t="s">
-        <v>21</v>
-      </c>
-      <c r="B6" s="39">
-        <f>COUNTIF(I12:I34,"Pass")</f>
-        <v>0</v>
-      </c>
-      <c r="C6" s="40" t="s">
-        <v>22</v>
-      </c>
-      <c r="D6" s="41">
-        <f>COUNTIF(I10:I753,"Pending")</f>
-        <v>0</v>
-      </c>
-      <c r="E6" s="42"/>
-      <c r="F6" s="42"/>
-      <c r="G6" s="42"/>
-      <c r="H6" s="102"/>
-      <c r="I6" s="102"/>
-      <c r="J6" s="102"/>
-      <c r="K6" s="53"/>
-    </row>
-    <row r="7" spans="1:11" s="26" customFormat="1" ht="15" customHeight="1" thickBot="1">
-      <c r="A7" s="43" t="s">
-        <v>23</v>
-      </c>
-      <c r="B7" s="44">
-        <f>COUNTIF(I12:I34,"Fail")</f>
-        <v>0</v>
-      </c>
-      <c r="C7" s="45" t="s">
-        <v>24</v>
-      </c>
-      <c r="D7" s="46">
-        <f>COUNTIF(A12:A34, "TC*")</f>
-        <v>18</v>
-      </c>
-      <c r="E7" s="47"/>
-      <c r="F7" s="47"/>
-      <c r="G7" s="47"/>
-      <c r="H7" s="102"/>
-      <c r="I7" s="102"/>
-      <c r="J7" s="102"/>
-      <c r="K7" s="53"/>
-    </row>
-    <row r="8" spans="1:11" s="26" customFormat="1" ht="15" customHeight="1">
-      <c r="A8" s="103"/>
-      <c r="B8" s="103"/>
-      <c r="C8" s="103"/>
-      <c r="D8" s="103"/>
-      <c r="E8" s="42"/>
-      <c r="F8" s="42"/>
-      <c r="G8" s="42"/>
-      <c r="H8" s="42"/>
-      <c r="I8" s="55"/>
-      <c r="J8" s="55"/>
-      <c r="K8" s="53"/>
-    </row>
-    <row r="9" spans="1:11" s="28" customFormat="1" ht="12" customHeight="1">
-      <c r="A9" s="104" t="s">
-        <v>25</v>
-      </c>
-      <c r="B9" s="106" t="s">
-        <v>26</v>
-      </c>
-      <c r="C9" s="104" t="s">
-        <v>27</v>
-      </c>
-      <c r="D9" s="108" t="s">
-        <v>28</v>
-      </c>
-      <c r="E9" s="109"/>
-      <c r="F9" s="110"/>
-      <c r="G9" s="114" t="s">
-        <v>29</v>
-      </c>
-      <c r="H9" s="115" t="s">
-        <v>30</v>
-      </c>
-      <c r="I9" s="115" t="s">
-        <v>31</v>
-      </c>
-      <c r="J9" s="115" t="s">
-        <v>32</v>
-      </c>
-      <c r="K9" s="56"/>
-    </row>
-    <row r="10" spans="1:11" s="26" customFormat="1" ht="12" customHeight="1">
-      <c r="A10" s="105"/>
-      <c r="B10" s="107"/>
-      <c r="C10" s="105"/>
-      <c r="D10" s="111"/>
-      <c r="E10" s="112"/>
-      <c r="F10" s="113"/>
-      <c r="G10" s="104"/>
-      <c r="H10" s="104"/>
-      <c r="I10" s="104"/>
-      <c r="J10" s="104"/>
-      <c r="K10" s="53"/>
-    </row>
-    <row r="11" spans="1:11" s="29" customFormat="1" ht="15">
-      <c r="A11" s="116"/>
-      <c r="B11" s="116"/>
-      <c r="C11" s="116"/>
-      <c r="D11" s="116"/>
-      <c r="E11" s="116"/>
-      <c r="F11" s="116"/>
-      <c r="G11" s="116"/>
-      <c r="H11" s="116"/>
-      <c r="I11" s="116"/>
-      <c r="J11" s="117"/>
-    </row>
-    <row r="12" spans="1:11" s="30" customFormat="1" ht="13.2">
-      <c r="A12" s="118" t="s">
-        <v>51</v>
-      </c>
-      <c r="B12" s="119"/>
-      <c r="C12" s="119"/>
-      <c r="D12" s="119"/>
-      <c r="E12" s="119"/>
-      <c r="F12" s="119"/>
-      <c r="G12" s="119"/>
-      <c r="H12" s="119"/>
-      <c r="I12" s="119"/>
-      <c r="J12" s="120"/>
-    </row>
-    <row r="13" spans="1:11" s="30" customFormat="1" ht="26.4" outlineLevel="1">
-      <c r="A13" s="49" t="s">
-        <v>45</v>
-      </c>
-      <c r="B13" s="50" t="s">
-        <v>52</v>
-      </c>
-      <c r="C13" s="51" t="s">
-        <v>53</v>
-      </c>
-      <c r="D13" s="143" t="s">
-        <v>54</v>
-      </c>
-      <c r="E13" s="144"/>
-      <c r="F13" s="51"/>
-      <c r="G13" s="51"/>
-      <c r="H13" s="89"/>
-      <c r="I13" s="51"/>
-      <c r="J13" s="51"/>
-    </row>
-    <row r="14" spans="1:11" s="30" customFormat="1" ht="13.2" outlineLevel="1">
-      <c r="A14" s="49" t="s">
-        <v>47</v>
-      </c>
-      <c r="B14" s="50" t="s">
-        <v>55</v>
-      </c>
-      <c r="C14" s="51" t="s">
-        <v>56</v>
-      </c>
-      <c r="D14" s="139" t="s">
-        <v>57</v>
-      </c>
-      <c r="E14" s="140"/>
-      <c r="F14" s="51"/>
-      <c r="G14" s="51"/>
-      <c r="H14" s="89"/>
-      <c r="I14" s="51"/>
-      <c r="J14" s="51"/>
-    </row>
-    <row r="15" spans="1:11" s="30" customFormat="1" ht="26.4" outlineLevel="1">
-      <c r="A15" s="49" t="s">
-        <v>70</v>
-      </c>
-      <c r="B15" s="50" t="s">
-        <v>58</v>
-      </c>
-      <c r="C15" s="51" t="s">
-        <v>59</v>
-      </c>
-      <c r="D15" s="139" t="s">
-        <v>60</v>
-      </c>
-      <c r="E15" s="140"/>
-      <c r="F15" s="51"/>
-      <c r="G15" s="51"/>
-      <c r="H15" s="89"/>
-      <c r="I15" s="51"/>
-      <c r="J15" s="51"/>
-    </row>
-    <row r="16" spans="1:11" s="30" customFormat="1" ht="13.2" outlineLevel="1">
-      <c r="A16" s="49" t="s">
-        <v>71</v>
-      </c>
-      <c r="B16" s="50" t="s">
-        <v>63</v>
-      </c>
-      <c r="C16" s="51" t="s">
-        <v>64</v>
-      </c>
-      <c r="D16" s="139"/>
-      <c r="E16" s="140"/>
-      <c r="F16" s="51"/>
-      <c r="G16" s="51"/>
-      <c r="H16" s="89"/>
-      <c r="I16" s="51"/>
-      <c r="J16" s="51"/>
-    </row>
-    <row r="17" spans="1:10" s="30" customFormat="1" ht="13.2" outlineLevel="1">
-      <c r="A17" s="49" t="s">
-        <v>72</v>
-      </c>
-      <c r="B17" s="50" t="s">
-        <v>65</v>
-      </c>
-      <c r="C17" s="51" t="s">
-        <v>66</v>
-      </c>
-      <c r="D17" s="139"/>
-      <c r="E17" s="140"/>
-      <c r="F17" s="51"/>
-      <c r="G17" s="51"/>
-      <c r="H17" s="89"/>
-      <c r="I17" s="51"/>
-      <c r="J17" s="51"/>
-    </row>
-    <row r="18" spans="1:10" s="30" customFormat="1" ht="26.4" outlineLevel="1">
-      <c r="A18" s="49" t="s">
-        <v>73</v>
-      </c>
-      <c r="B18" s="50" t="s">
-        <v>67</v>
-      </c>
-      <c r="C18" s="51" t="s">
-        <v>68</v>
-      </c>
-      <c r="D18" s="139"/>
-      <c r="E18" s="140"/>
-      <c r="F18" s="51"/>
-      <c r="G18" s="51"/>
-      <c r="H18" s="89"/>
-      <c r="I18" s="51"/>
-      <c r="J18" s="51"/>
-    </row>
-    <row r="19" spans="1:10" s="30" customFormat="1" ht="26.4" outlineLevel="1">
-      <c r="A19" s="49" t="s">
-        <v>80</v>
-      </c>
-      <c r="B19" s="50" t="s">
-        <v>81</v>
-      </c>
-      <c r="C19" s="131" t="s">
-        <v>82</v>
-      </c>
-      <c r="D19" s="139"/>
-      <c r="E19" s="140"/>
-      <c r="F19" s="51"/>
-      <c r="G19" s="51"/>
-      <c r="H19" s="89"/>
-      <c r="I19" s="51"/>
-      <c r="J19" s="51"/>
-    </row>
-    <row r="20" spans="1:10" s="30" customFormat="1" ht="13.2" outlineLevel="1">
-      <c r="A20" s="118" t="s">
-        <v>69</v>
-      </c>
-      <c r="B20" s="119"/>
-      <c r="C20" s="119"/>
-      <c r="D20" s="48"/>
-      <c r="E20" s="48"/>
-      <c r="F20" s="48"/>
-      <c r="G20" s="48"/>
-      <c r="H20" s="48"/>
-      <c r="I20" s="48"/>
-      <c r="J20" s="57"/>
-    </row>
-    <row r="21" spans="1:10" s="30" customFormat="1" ht="13.2" outlineLevel="1">
-      <c r="A21" s="49" t="s">
-        <v>45</v>
-      </c>
-      <c r="B21" s="50" t="s">
-        <v>74</v>
-      </c>
-      <c r="C21" s="51" t="s">
-        <v>75</v>
-      </c>
-      <c r="D21" s="139"/>
-      <c r="E21" s="140"/>
-      <c r="F21" s="51"/>
-      <c r="G21" s="51"/>
-      <c r="H21" s="89"/>
-      <c r="I21" s="51"/>
-      <c r="J21" s="51"/>
-    </row>
-    <row r="22" spans="1:10" s="30" customFormat="1" ht="13.2" outlineLevel="1">
-      <c r="A22" s="49" t="s">
-        <v>47</v>
-      </c>
-      <c r="B22" s="50" t="s">
-        <v>76</v>
-      </c>
-      <c r="C22" s="51" t="s">
-        <v>77</v>
-      </c>
-      <c r="D22" s="139"/>
-      <c r="E22" s="140"/>
-      <c r="F22" s="51"/>
-      <c r="G22" s="51"/>
-      <c r="H22" s="89"/>
-      <c r="I22" s="51"/>
-      <c r="J22" s="51"/>
-    </row>
-    <row r="23" spans="1:10" s="30" customFormat="1" ht="13.2" outlineLevel="1">
-      <c r="A23" s="49" t="s">
-        <v>70</v>
-      </c>
-      <c r="B23" s="50" t="s">
-        <v>65</v>
-      </c>
-      <c r="C23" s="51"/>
-      <c r="D23" s="139"/>
-      <c r="E23" s="140"/>
-      <c r="F23" s="51"/>
-      <c r="G23" s="51"/>
-      <c r="H23" s="89"/>
-      <c r="I23" s="51"/>
-      <c r="J23" s="51"/>
-    </row>
-    <row r="24" spans="1:10" s="30" customFormat="1" ht="13.2" outlineLevel="1">
-      <c r="A24" s="49" t="s">
-        <v>71</v>
-      </c>
-      <c r="B24" s="50" t="s">
-        <v>78</v>
-      </c>
-      <c r="C24" s="51" t="s">
-        <v>79</v>
-      </c>
-      <c r="D24" s="139"/>
-      <c r="E24" s="140"/>
-      <c r="F24" s="51"/>
-      <c r="G24" s="51"/>
-      <c r="H24" s="89"/>
-      <c r="I24" s="51"/>
-      <c r="J24" s="51"/>
-    </row>
-    <row r="25" spans="1:10" s="30" customFormat="1" ht="13.2" outlineLevel="1">
-      <c r="A25" s="49" t="s">
-        <v>72</v>
-      </c>
-      <c r="B25" s="50" t="s">
-        <v>83</v>
-      </c>
-      <c r="C25" s="51" t="s">
-        <v>68</v>
-      </c>
-      <c r="D25" s="139"/>
-      <c r="E25" s="140"/>
-      <c r="F25" s="51"/>
-      <c r="G25" s="51"/>
-      <c r="H25" s="89"/>
-      <c r="I25" s="51"/>
-      <c r="J25" s="51"/>
-    </row>
-    <row r="26" spans="1:10" s="30" customFormat="1" ht="26.4" outlineLevel="1">
-      <c r="A26" s="49" t="s">
-        <v>73</v>
-      </c>
-      <c r="B26" s="50" t="s">
-        <v>81</v>
-      </c>
-      <c r="C26" s="131" t="s">
-        <v>82</v>
-      </c>
-      <c r="D26" s="51"/>
-      <c r="E26" s="51"/>
-      <c r="F26" s="51"/>
-      <c r="G26" s="51"/>
-      <c r="H26" s="89"/>
-      <c r="I26" s="51"/>
-      <c r="J26" s="51"/>
-    </row>
-    <row r="27" spans="1:10" s="30" customFormat="1" ht="18" customHeight="1" outlineLevel="1">
-      <c r="A27" s="132" t="s">
-        <v>80</v>
-      </c>
-      <c r="B27" s="132" t="s">
-        <v>84</v>
-      </c>
-      <c r="C27" s="132" t="s">
-        <v>85</v>
-      </c>
-      <c r="D27" s="139"/>
-      <c r="E27" s="140"/>
-      <c r="F27" s="51"/>
-      <c r="G27" s="51"/>
-      <c r="H27" s="89"/>
-      <c r="I27" s="51"/>
-      <c r="J27" s="51"/>
-    </row>
-    <row r="28" spans="1:10" s="30" customFormat="1" ht="13.2" outlineLevel="1">
-      <c r="A28" s="133" t="s">
-        <v>86</v>
-      </c>
-      <c r="B28" s="119"/>
-      <c r="C28" s="119"/>
-      <c r="D28" s="48"/>
-      <c r="E28" s="48"/>
-      <c r="F28" s="48"/>
-      <c r="G28" s="48"/>
-      <c r="H28" s="48"/>
-      <c r="I28" s="48"/>
-      <c r="J28" s="57"/>
-    </row>
-    <row r="29" spans="1:10" s="30" customFormat="1" ht="26.4" outlineLevel="1">
-      <c r="A29" s="134" t="s">
-        <v>45</v>
-      </c>
-      <c r="B29" s="135" t="s">
-        <v>88</v>
-      </c>
-      <c r="C29" s="136" t="s">
-        <v>90</v>
-      </c>
-      <c r="D29" s="137" t="s">
-        <v>92</v>
-      </c>
-      <c r="F29" s="51"/>
-      <c r="G29" s="51"/>
-      <c r="H29" s="89"/>
-      <c r="I29" s="51"/>
-      <c r="J29" s="51"/>
-    </row>
-    <row r="30" spans="1:10" s="30" customFormat="1" ht="26.4" outlineLevel="1">
-      <c r="A30" s="134" t="s">
-        <v>47</v>
-      </c>
-      <c r="B30" s="135" t="s">
-        <v>89</v>
-      </c>
-      <c r="C30" s="136" t="s">
-        <v>87</v>
-      </c>
-      <c r="D30" s="141" t="s">
-        <v>91</v>
-      </c>
-      <c r="E30" s="142"/>
-      <c r="F30" s="51"/>
-      <c r="G30" s="51"/>
-      <c r="H30" s="89"/>
-      <c r="I30" s="51"/>
-      <c r="J30" s="51"/>
-    </row>
-    <row r="31" spans="1:10" s="30" customFormat="1" ht="26.4" outlineLevel="1">
-      <c r="A31" s="134" t="s">
-        <v>61</v>
-      </c>
-      <c r="B31" s="135" t="s">
-        <v>93</v>
-      </c>
-      <c r="C31" s="138" t="s">
-        <v>94</v>
-      </c>
-      <c r="D31" s="139"/>
-      <c r="E31" s="140"/>
-      <c r="F31" s="51"/>
-      <c r="G31" s="51"/>
-      <c r="H31" s="89"/>
-      <c r="I31" s="51"/>
-      <c r="J31" s="51"/>
-    </row>
-    <row r="32" spans="1:10" s="30" customFormat="1" ht="13.2" outlineLevel="1">
-      <c r="A32" s="134" t="s">
-        <v>62</v>
-      </c>
-      <c r="B32" s="135" t="s">
-        <v>95</v>
-      </c>
-      <c r="C32" s="138" t="s">
-        <v>96</v>
-      </c>
-      <c r="D32" s="139"/>
-      <c r="E32" s="140"/>
-      <c r="F32" s="51"/>
-      <c r="G32" s="51"/>
-      <c r="H32" s="89"/>
-      <c r="I32" s="51"/>
-      <c r="J32" s="51"/>
-    </row>
-    <row r="33" spans="1:10" s="30" customFormat="1" ht="13.2" outlineLevel="1">
-      <c r="A33" s="49"/>
-      <c r="B33" s="50"/>
-      <c r="C33" s="51"/>
-      <c r="D33" s="139"/>
-      <c r="E33" s="140"/>
-      <c r="F33" s="51"/>
-      <c r="G33" s="51"/>
-      <c r="H33" s="89"/>
-      <c r="I33" s="51"/>
-      <c r="J33" s="51"/>
-    </row>
-    <row r="34" spans="1:10" s="30" customFormat="1" ht="13.8" customHeight="1" outlineLevel="1">
-      <c r="A34" s="49"/>
-      <c r="B34" s="50"/>
-      <c r="C34" s="51"/>
-      <c r="D34" s="139"/>
-      <c r="E34" s="140"/>
-      <c r="F34" s="51"/>
-      <c r="G34" s="51"/>
-      <c r="H34" s="89"/>
-      <c r="I34" s="51"/>
-      <c r="J34" s="51"/>
-    </row>
-    <row r="35" spans="1:10" ht="12" customHeight="1"/>
-    <row r="36" spans="1:10" ht="12" customHeight="1"/>
-    <row r="37" spans="1:10" ht="12" customHeight="1"/>
-    <row r="38" spans="1:10" ht="12" customHeight="1"/>
-    <row r="39" spans="1:10" ht="12" customHeight="1"/>
-    <row r="40" spans="1:10" ht="12" customHeight="1"/>
-    <row r="41" spans="1:10" ht="12" customHeight="1"/>
-    <row r="42" spans="1:10" ht="12" customHeight="1"/>
-    <row r="43" spans="1:10" ht="12" customHeight="1"/>
-    <row r="44" spans="1:10" ht="12" customHeight="1"/>
-    <row r="45" spans="1:10" ht="12" customHeight="1"/>
-    <row r="46" spans="1:10" ht="12" customHeight="1"/>
-    <row r="47" spans="1:10" ht="12" customHeight="1"/>
-    <row r="48" spans="1:10" ht="12" customHeight="1"/>
-    <row r="49" ht="12" customHeight="1"/>
-    <row r="50" ht="12" customHeight="1"/>
-    <row r="51" ht="12" customHeight="1"/>
-    <row r="52" ht="12" customHeight="1"/>
-    <row r="53" ht="12" customHeight="1"/>
-    <row r="54" ht="12" customHeight="1"/>
-    <row r="55" ht="12" customHeight="1"/>
-    <row r="56" ht="12" customHeight="1"/>
-    <row r="57" ht="12" customHeight="1"/>
-    <row r="58" ht="12" customHeight="1"/>
-    <row r="59" ht="12" customHeight="1"/>
-    <row r="60" ht="12" customHeight="1"/>
-    <row r="61" ht="12" customHeight="1"/>
-    <row r="62" ht="12" customHeight="1"/>
-    <row r="63" ht="12" customHeight="1"/>
-    <row r="64" ht="12" customHeight="1"/>
-    <row r="65" ht="12" customHeight="1"/>
-    <row r="66" ht="12" customHeight="1"/>
-    <row r="67" ht="12" customHeight="1"/>
-    <row r="68" ht="12" customHeight="1"/>
-    <row r="69" ht="12" customHeight="1"/>
-    <row r="70" ht="12" customHeight="1"/>
-    <row r="71" ht="12" customHeight="1"/>
-    <row r="72" ht="12" customHeight="1"/>
-  </sheetData>
-  <mergeCells count="40">
-    <mergeCell ref="D13:E13"/>
-    <mergeCell ref="D17:E17"/>
-    <mergeCell ref="D16:E16"/>
-    <mergeCell ref="D15:E15"/>
-    <mergeCell ref="D14:E14"/>
-    <mergeCell ref="D18:E18"/>
-    <mergeCell ref="B1:D2"/>
-    <mergeCell ref="D9:F10"/>
-    <mergeCell ref="B3:D3"/>
-    <mergeCell ref="D19:E19"/>
-    <mergeCell ref="A20:C20"/>
-    <mergeCell ref="D27:E27"/>
-    <mergeCell ref="A28:C28"/>
-    <mergeCell ref="D34:E34"/>
-    <mergeCell ref="D21:E21"/>
-    <mergeCell ref="D30:E30"/>
-    <mergeCell ref="D22:E22"/>
-    <mergeCell ref="D23:E23"/>
-    <mergeCell ref="D24:E24"/>
-    <mergeCell ref="D25:E25"/>
-    <mergeCell ref="D31:E31"/>
-    <mergeCell ref="D32:E32"/>
-    <mergeCell ref="D33:E33"/>
-    <mergeCell ref="H6:J6"/>
-    <mergeCell ref="H7:J7"/>
-    <mergeCell ref="A8:D8"/>
-    <mergeCell ref="A11:J11"/>
-    <mergeCell ref="A12:J12"/>
-    <mergeCell ref="A9:A10"/>
-    <mergeCell ref="B9:B10"/>
-    <mergeCell ref="C9:C10"/>
-    <mergeCell ref="G9:G10"/>
-    <mergeCell ref="H9:H10"/>
-    <mergeCell ref="I9:I10"/>
-    <mergeCell ref="J9:J10"/>
-    <mergeCell ref="H3:J3"/>
-    <mergeCell ref="B4:D4"/>
-    <mergeCell ref="H4:J4"/>
-    <mergeCell ref="B5:D5"/>
-    <mergeCell ref="H5:J5"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
-  <headerFooter alignWithMargins="0"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{20690ED2-4B8F-4386-AEC9-67E105CBDE46}">
-  <dimension ref="A1:L71"/>
-  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="13.8" outlineLevelRow="1"/>
-  <cols>
-    <col min="1" max="1" width="18" customWidth="1"/>
-    <col min="2" max="2" width="18.109375" customWidth="1"/>
-    <col min="3" max="3" width="42.109375" customWidth="1"/>
-    <col min="6" max="6" width="23.6640625" customWidth="1"/>
-    <col min="7" max="7" width="18.44140625" hidden="1" customWidth="1"/>
-    <col min="8" max="8" width="38" customWidth="1"/>
-    <col min="9" max="9" width="17.109375" customWidth="1"/>
-    <col min="10" max="10" width="8.77734375" style="6"/>
-    <col min="11" max="11" width="18" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:12" s="25" customFormat="1" ht="12.75" customHeight="1">
-      <c r="A1" s="31" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="126"/>
-      <c r="C1" s="126"/>
-      <c r="D1" s="126"/>
-      <c r="E1" s="32"/>
-      <c r="F1" s="32"/>
-      <c r="G1" s="32"/>
-      <c r="H1" s="32"/>
-      <c r="I1" s="32"/>
-      <c r="J1" s="52"/>
-      <c r="K1" s="32"/>
-      <c r="L1" s="33"/>
-    </row>
-    <row r="2" spans="1:12" s="25" customFormat="1" ht="11.25" customHeight="1" thickBot="1">
-      <c r="A2" s="33"/>
-      <c r="B2" s="127"/>
-      <c r="C2" s="127"/>
-      <c r="D2" s="127"/>
-      <c r="E2" s="32"/>
-      <c r="F2" s="32"/>
-      <c r="G2" s="32"/>
-      <c r="H2" s="32"/>
-      <c r="I2" s="32"/>
-      <c r="J2" s="52"/>
-      <c r="K2" s="32"/>
-      <c r="L2" s="33"/>
-    </row>
-    <row r="3" spans="1:12" s="26" customFormat="1" ht="15" customHeight="1">
-      <c r="A3" s="34" t="s">
-        <v>18</v>
-      </c>
-      <c r="B3" s="96" t="s">
-        <v>4</v>
-      </c>
-      <c r="C3" s="96"/>
-      <c r="D3" s="97"/>
-      <c r="E3" s="35"/>
-      <c r="F3" s="35"/>
-      <c r="G3" s="35"/>
-      <c r="H3" s="35"/>
-      <c r="I3" s="102"/>
-      <c r="J3" s="102"/>
-      <c r="K3" s="102"/>
-      <c r="L3" s="53"/>
-    </row>
-    <row r="4" spans="1:12" s="26" customFormat="1" ht="13.2">
-      <c r="A4" s="36" t="s">
-        <v>19</v>
-      </c>
-      <c r="B4" s="128" t="s">
-        <v>48</v>
-      </c>
-      <c r="C4" s="129"/>
-      <c r="D4" s="130"/>
-      <c r="E4" s="35"/>
-      <c r="F4" s="35"/>
-      <c r="G4" s="35"/>
-      <c r="H4" s="35"/>
-      <c r="I4" s="102"/>
-      <c r="J4" s="102"/>
-      <c r="K4" s="102"/>
-      <c r="L4" s="53"/>
-    </row>
-    <row r="5" spans="1:12" s="27" customFormat="1" ht="15" customHeight="1">
-      <c r="A5" s="36" t="s">
-        <v>20</v>
-      </c>
-      <c r="B5" s="122" t="s">
-        <v>44</v>
-      </c>
-      <c r="C5" s="123"/>
-      <c r="D5" s="124"/>
-      <c r="E5" s="37"/>
-      <c r="F5" s="37"/>
-      <c r="G5" s="37"/>
-      <c r="H5" s="37"/>
-      <c r="I5" s="125"/>
-      <c r="J5" s="125"/>
-      <c r="K5" s="125"/>
-      <c r="L5" s="54"/>
-    </row>
-    <row r="6" spans="1:12" s="26" customFormat="1" ht="15" customHeight="1">
-      <c r="A6" s="38" t="s">
-        <v>21</v>
-      </c>
-      <c r="B6" s="39">
-        <f>COUNTIF(J12:J33,"Pass")</f>
-        <v>0</v>
-      </c>
-      <c r="C6" s="40" t="s">
-        <v>22</v>
-      </c>
-      <c r="D6" s="41">
-        <f>COUNTIF(J10:J752,"Pending")</f>
-        <v>0</v>
-      </c>
-      <c r="E6" s="42"/>
-      <c r="F6" s="42"/>
-      <c r="G6" s="42"/>
-      <c r="H6" s="42"/>
-      <c r="I6" s="102"/>
-      <c r="J6" s="102"/>
-      <c r="K6" s="102"/>
-      <c r="L6" s="53"/>
-    </row>
-    <row r="7" spans="1:12" s="26" customFormat="1" ht="15" customHeight="1" thickBot="1">
-      <c r="A7" s="43" t="s">
-        <v>23</v>
-      </c>
-      <c r="B7" s="44">
-        <f>COUNTIF(J12:J33,"Fail")</f>
-        <v>0</v>
-      </c>
-      <c r="C7" s="45" t="s">
-        <v>24</v>
-      </c>
-      <c r="D7" s="46">
-        <f>COUNTIF(A12:A33, "TC*")</f>
-        <v>1</v>
-      </c>
-      <c r="E7" s="47"/>
-      <c r="F7" s="47"/>
-      <c r="G7" s="47"/>
-      <c r="H7" s="47"/>
-      <c r="I7" s="102"/>
-      <c r="J7" s="102"/>
-      <c r="K7" s="102"/>
-      <c r="L7" s="53"/>
-    </row>
-    <row r="8" spans="1:12" s="26" customFormat="1" ht="15" customHeight="1">
-      <c r="A8" s="103"/>
-      <c r="B8" s="103"/>
-      <c r="C8" s="103"/>
-      <c r="D8" s="103"/>
-      <c r="E8" s="42"/>
-      <c r="F8" s="42"/>
-      <c r="G8" s="42"/>
-      <c r="H8" s="42"/>
-      <c r="I8" s="42"/>
-      <c r="J8" s="55"/>
-      <c r="K8" s="55"/>
-      <c r="L8" s="53"/>
-    </row>
-    <row r="9" spans="1:12" s="28" customFormat="1" ht="12" customHeight="1">
-      <c r="A9" s="104" t="s">
-        <v>25</v>
-      </c>
-      <c r="B9" s="106" t="s">
-        <v>26</v>
-      </c>
-      <c r="C9" s="104" t="s">
-        <v>27</v>
-      </c>
-      <c r="D9" s="108" t="s">
-        <v>28</v>
-      </c>
-      <c r="E9" s="109"/>
-      <c r="F9" s="109"/>
-      <c r="G9" s="110"/>
-      <c r="H9" s="114" t="s">
-        <v>29</v>
-      </c>
-      <c r="I9" s="115" t="s">
-        <v>30</v>
-      </c>
-      <c r="J9" s="115" t="s">
-        <v>31</v>
-      </c>
-      <c r="K9" s="115" t="s">
-        <v>32</v>
-      </c>
-      <c r="L9" s="56"/>
-    </row>
-    <row r="10" spans="1:12" s="26" customFormat="1" ht="12" customHeight="1">
-      <c r="A10" s="105"/>
-      <c r="B10" s="107"/>
-      <c r="C10" s="105"/>
-      <c r="D10" s="111"/>
-      <c r="E10" s="112"/>
-      <c r="F10" s="112"/>
-      <c r="G10" s="113"/>
-      <c r="H10" s="104"/>
-      <c r="I10" s="104"/>
-      <c r="J10" s="104"/>
-      <c r="K10" s="104"/>
-      <c r="L10" s="53"/>
-    </row>
-    <row r="11" spans="1:12" s="29" customFormat="1" ht="15">
-      <c r="A11" s="116"/>
-      <c r="B11" s="116"/>
-      <c r="C11" s="116"/>
-      <c r="D11" s="116"/>
-      <c r="E11" s="116"/>
-      <c r="F11" s="116"/>
-      <c r="G11" s="116"/>
-      <c r="H11" s="116"/>
-      <c r="I11" s="116"/>
-      <c r="J11" s="116"/>
-      <c r="K11" s="117"/>
-    </row>
-    <row r="12" spans="1:12" s="30" customFormat="1" ht="13.2">
-      <c r="A12" s="118" t="s">
-        <v>33</v>
-      </c>
-      <c r="B12" s="119"/>
-      <c r="C12" s="119"/>
-      <c r="D12" s="119"/>
-      <c r="E12" s="119"/>
-      <c r="F12" s="119"/>
-      <c r="G12" s="119"/>
-      <c r="H12" s="119"/>
-      <c r="I12" s="119"/>
-      <c r="J12" s="119"/>
-      <c r="K12" s="120"/>
-    </row>
-    <row r="13" spans="1:12" s="30" customFormat="1" ht="13.2" outlineLevel="1">
-      <c r="A13" s="49" t="s">
-        <v>45</v>
-      </c>
-      <c r="B13" s="50"/>
-      <c r="C13" s="51"/>
-      <c r="D13" s="121"/>
-      <c r="E13" s="121"/>
-      <c r="F13" s="121"/>
-      <c r="G13" s="51"/>
-      <c r="H13" s="51"/>
-      <c r="I13" s="89"/>
-      <c r="J13" s="51"/>
-      <c r="K13" s="51"/>
-    </row>
-    <row r="14" spans="1:12" s="30" customFormat="1" ht="13.2" outlineLevel="1">
-      <c r="A14" s="49"/>
-      <c r="B14" s="50"/>
-      <c r="C14" s="51"/>
-      <c r="D14" s="99"/>
-      <c r="E14" s="99"/>
-      <c r="F14" s="99"/>
-      <c r="G14" s="51"/>
-      <c r="H14" s="51"/>
-      <c r="I14" s="89"/>
-      <c r="J14" s="51"/>
-      <c r="K14" s="51"/>
-    </row>
-    <row r="15" spans="1:12" s="30" customFormat="1" ht="13.2" outlineLevel="1">
-      <c r="A15" s="49"/>
-      <c r="B15" s="50"/>
-      <c r="C15" s="51"/>
-      <c r="D15" s="99"/>
-      <c r="E15" s="99"/>
-      <c r="F15" s="99"/>
-      <c r="G15" s="51"/>
-      <c r="H15" s="51"/>
-      <c r="I15" s="89"/>
-      <c r="J15" s="51"/>
-      <c r="K15" s="51"/>
-    </row>
-    <row r="16" spans="1:12" s="30" customFormat="1" ht="13.2" outlineLevel="1">
-      <c r="A16" s="49"/>
-      <c r="B16" s="50"/>
-      <c r="C16" s="51"/>
-      <c r="D16" s="99"/>
-      <c r="E16" s="99"/>
-      <c r="F16" s="99"/>
-      <c r="G16" s="51"/>
-      <c r="H16" s="51"/>
-      <c r="I16" s="89"/>
-      <c r="J16" s="51"/>
-      <c r="K16" s="51"/>
-    </row>
-    <row r="17" spans="1:11" s="30" customFormat="1" ht="13.2" outlineLevel="1">
-      <c r="A17" s="49"/>
-      <c r="B17" s="50"/>
-      <c r="C17" s="51"/>
-      <c r="D17" s="99"/>
-      <c r="E17" s="99"/>
-      <c r="F17" s="99"/>
-      <c r="G17" s="51"/>
-      <c r="H17" s="51"/>
-      <c r="I17" s="89"/>
-      <c r="J17" s="51"/>
-      <c r="K17" s="51"/>
-    </row>
-    <row r="18" spans="1:11" s="30" customFormat="1" ht="13.2" outlineLevel="1">
-      <c r="A18" s="49"/>
-      <c r="B18" s="50"/>
-      <c r="C18" s="51"/>
-      <c r="D18" s="99"/>
-      <c r="E18" s="99"/>
-      <c r="F18" s="99"/>
-      <c r="G18" s="51"/>
-      <c r="H18" s="51"/>
-      <c r="I18" s="89"/>
-      <c r="J18" s="51"/>
-      <c r="K18" s="51"/>
-    </row>
-    <row r="19" spans="1:11" s="30" customFormat="1" ht="13.2" outlineLevel="1">
-      <c r="A19" s="49"/>
-      <c r="B19" s="50"/>
-      <c r="C19" s="51"/>
-      <c r="D19" s="99"/>
-      <c r="E19" s="99"/>
-      <c r="F19" s="99"/>
-      <c r="G19" s="51"/>
-      <c r="H19" s="51"/>
-      <c r="I19" s="89"/>
-      <c r="J19" s="51"/>
-      <c r="K19" s="51"/>
-    </row>
-    <row r="20" spans="1:11" s="30" customFormat="1" ht="13.2" outlineLevel="1">
-      <c r="A20" s="100"/>
-      <c r="B20" s="101"/>
-      <c r="C20" s="101"/>
-      <c r="D20" s="48"/>
-      <c r="E20" s="48"/>
-      <c r="F20" s="48"/>
-      <c r="G20" s="48"/>
-      <c r="H20" s="48"/>
-      <c r="I20" s="48"/>
-      <c r="J20" s="48"/>
-      <c r="K20" s="57"/>
-    </row>
-    <row r="21" spans="1:11" s="30" customFormat="1" ht="13.2" outlineLevel="1">
-      <c r="A21" s="49"/>
-      <c r="B21" s="50"/>
-      <c r="C21" s="51"/>
-      <c r="D21" s="99"/>
-      <c r="E21" s="99"/>
-      <c r="F21" s="99"/>
-      <c r="G21" s="51"/>
-      <c r="H21" s="51"/>
-      <c r="I21" s="89"/>
-      <c r="J21" s="51"/>
-      <c r="K21" s="51"/>
-    </row>
-    <row r="22" spans="1:11" s="30" customFormat="1" ht="13.2" outlineLevel="1">
-      <c r="A22" s="49"/>
-      <c r="B22" s="50"/>
-      <c r="C22" s="51"/>
-      <c r="D22" s="99"/>
-      <c r="E22" s="99"/>
-      <c r="F22" s="99"/>
-      <c r="G22" s="51"/>
-      <c r="H22" s="51"/>
-      <c r="I22" s="89"/>
-      <c r="J22" s="51"/>
-      <c r="K22" s="51"/>
-    </row>
-    <row r="23" spans="1:11" s="30" customFormat="1" ht="13.2" outlineLevel="1">
-      <c r="A23" s="49"/>
-      <c r="B23" s="50"/>
-      <c r="C23" s="51"/>
-      <c r="D23" s="99"/>
-      <c r="E23" s="99"/>
-      <c r="F23" s="99"/>
-      <c r="G23" s="51"/>
-      <c r="H23" s="51"/>
-      <c r="I23" s="89"/>
-      <c r="J23" s="51"/>
-      <c r="K23" s="51"/>
-    </row>
-    <row r="24" spans="1:11" s="30" customFormat="1" ht="13.2" outlineLevel="1">
-      <c r="A24" s="49"/>
-      <c r="B24" s="50"/>
-      <c r="C24" s="51"/>
-      <c r="D24" s="99"/>
-      <c r="E24" s="99"/>
-      <c r="F24" s="99"/>
-      <c r="G24" s="51"/>
-      <c r="H24" s="51"/>
-      <c r="I24" s="89"/>
-      <c r="J24" s="51"/>
-      <c r="K24" s="51"/>
-    </row>
-    <row r="25" spans="1:11" s="30" customFormat="1" ht="13.2" outlineLevel="1">
-      <c r="A25" s="49"/>
-      <c r="B25" s="50"/>
-      <c r="C25" s="51"/>
-      <c r="D25" s="99"/>
-      <c r="E25" s="99"/>
-      <c r="F25" s="99"/>
-      <c r="G25" s="51"/>
-      <c r="H25" s="51"/>
-      <c r="I25" s="89"/>
-      <c r="J25" s="51"/>
-      <c r="K25" s="51"/>
-    </row>
-    <row r="26" spans="1:11" s="30" customFormat="1" ht="18" customHeight="1" outlineLevel="1">
-      <c r="A26" s="49"/>
-      <c r="B26" s="50"/>
-      <c r="C26" s="51"/>
-      <c r="D26" s="99"/>
-      <c r="E26" s="99"/>
-      <c r="F26" s="99"/>
-      <c r="G26" s="51"/>
-      <c r="H26" s="51"/>
-      <c r="I26" s="89"/>
-      <c r="J26" s="51"/>
-      <c r="K26" s="51"/>
-    </row>
-    <row r="27" spans="1:11" s="30" customFormat="1" ht="13.2" outlineLevel="1">
-      <c r="A27" s="100"/>
-      <c r="B27" s="101"/>
-      <c r="C27" s="101"/>
-      <c r="D27" s="48"/>
-      <c r="E27" s="48"/>
-      <c r="F27" s="48"/>
-      <c r="G27" s="48"/>
-      <c r="H27" s="48"/>
-      <c r="I27" s="48"/>
-      <c r="J27" s="48"/>
-      <c r="K27" s="57"/>
-    </row>
-    <row r="28" spans="1:11" s="30" customFormat="1" ht="13.2" outlineLevel="1">
-      <c r="A28" s="49"/>
-      <c r="B28" s="50"/>
-      <c r="C28" s="51"/>
-      <c r="D28" s="99"/>
-      <c r="E28" s="99"/>
-      <c r="F28" s="99"/>
-      <c r="G28" s="51"/>
-      <c r="H28" s="51"/>
-      <c r="I28" s="89"/>
-      <c r="J28" s="51"/>
-      <c r="K28" s="51"/>
-    </row>
-    <row r="29" spans="1:11" s="30" customFormat="1" ht="13.2" outlineLevel="1">
-      <c r="A29" s="49"/>
-      <c r="B29" s="50"/>
-      <c r="C29" s="51"/>
-      <c r="D29" s="99"/>
-      <c r="E29" s="99"/>
-      <c r="F29" s="99"/>
-      <c r="G29" s="51"/>
-      <c r="H29" s="51"/>
-      <c r="I29" s="89"/>
-      <c r="J29" s="51"/>
-      <c r="K29" s="51"/>
-    </row>
-    <row r="30" spans="1:11" s="30" customFormat="1" ht="13.2" outlineLevel="1">
-      <c r="A30" s="49"/>
-      <c r="B30" s="50"/>
-      <c r="C30" s="51"/>
-      <c r="D30" s="99"/>
-      <c r="E30" s="99"/>
-      <c r="F30" s="99"/>
-      <c r="G30" s="51"/>
-      <c r="H30" s="51"/>
-      <c r="I30" s="89"/>
-      <c r="J30" s="51"/>
-      <c r="K30" s="51"/>
-    </row>
-    <row r="31" spans="1:11" s="30" customFormat="1" ht="13.2" outlineLevel="1">
-      <c r="A31" s="49"/>
-      <c r="B31" s="50"/>
-      <c r="C31" s="51"/>
-      <c r="D31" s="99"/>
-      <c r="E31" s="99"/>
-      <c r="F31" s="99"/>
-      <c r="G31" s="51"/>
-      <c r="H31" s="51"/>
-      <c r="I31" s="89"/>
-      <c r="J31" s="51"/>
-      <c r="K31" s="51"/>
-    </row>
-    <row r="32" spans="1:11" s="30" customFormat="1" ht="13.2" outlineLevel="1">
-      <c r="A32" s="49"/>
-      <c r="B32" s="50"/>
-      <c r="C32" s="51"/>
-      <c r="D32" s="99"/>
-      <c r="E32" s="99"/>
-      <c r="F32" s="99"/>
-      <c r="G32" s="51"/>
-      <c r="H32" s="51"/>
-      <c r="I32" s="89"/>
-      <c r="J32" s="51"/>
-      <c r="K32" s="51"/>
-    </row>
-    <row r="33" spans="1:11" s="30" customFormat="1" ht="13.8" customHeight="1" outlineLevel="1">
-      <c r="A33" s="49"/>
-      <c r="B33" s="50"/>
-      <c r="C33" s="51"/>
-      <c r="D33" s="99"/>
-      <c r="E33" s="99"/>
-      <c r="F33" s="99"/>
-      <c r="G33" s="51"/>
-      <c r="H33" s="51"/>
-      <c r="I33" s="89"/>
-      <c r="J33" s="51"/>
-      <c r="K33" s="51"/>
-    </row>
-    <row r="34" spans="1:11" ht="12" customHeight="1"/>
-    <row r="35" spans="1:11" ht="12" customHeight="1"/>
-    <row r="36" spans="1:11" ht="12" customHeight="1"/>
-    <row r="37" spans="1:11" ht="12" customHeight="1"/>
-    <row r="38" spans="1:11" ht="12" customHeight="1"/>
-    <row r="39" spans="1:11" ht="12" customHeight="1"/>
-    <row r="40" spans="1:11" ht="12" customHeight="1"/>
-    <row r="41" spans="1:11" ht="12" customHeight="1"/>
-    <row r="42" spans="1:11" ht="12" customHeight="1"/>
-    <row r="43" spans="1:11" ht="12" customHeight="1"/>
-    <row r="44" spans="1:11" ht="12" customHeight="1"/>
-    <row r="45" spans="1:11" ht="12" customHeight="1"/>
-    <row r="46" spans="1:11" ht="12" customHeight="1"/>
-    <row r="47" spans="1:11" ht="12" customHeight="1"/>
-    <row r="48" spans="1:11" ht="12" customHeight="1"/>
-    <row r="49" ht="12" customHeight="1"/>
-    <row r="50" ht="12" customHeight="1"/>
-    <row r="51" ht="12" customHeight="1"/>
-    <row r="52" ht="12" customHeight="1"/>
-    <row r="53" ht="12" customHeight="1"/>
-    <row r="54" ht="12" customHeight="1"/>
-    <row r="55" ht="12" customHeight="1"/>
-    <row r="56" ht="12" customHeight="1"/>
-    <row r="57" ht="12" customHeight="1"/>
-    <row r="58" ht="12" customHeight="1"/>
-    <row r="59" ht="12" customHeight="1"/>
-    <row r="60" ht="12" customHeight="1"/>
-    <row r="61" ht="12" customHeight="1"/>
-    <row r="62" ht="12" customHeight="1"/>
-    <row r="63" ht="12" customHeight="1"/>
-    <row r="64" ht="12" customHeight="1"/>
-    <row r="65" ht="12" customHeight="1"/>
-    <row r="66" ht="12" customHeight="1"/>
-    <row r="67" ht="12" customHeight="1"/>
-    <row r="68" ht="12" customHeight="1"/>
-    <row r="69" ht="12" customHeight="1"/>
-    <row r="70" ht="12" customHeight="1"/>
-    <row r="71" ht="12" customHeight="1"/>
-  </sheetData>
-  <mergeCells count="41">
-    <mergeCell ref="D33:F33"/>
-    <mergeCell ref="D22:F22"/>
-    <mergeCell ref="D23:F23"/>
-    <mergeCell ref="D24:F24"/>
-    <mergeCell ref="D25:F25"/>
-    <mergeCell ref="D26:F26"/>
-    <mergeCell ref="D28:F28"/>
-    <mergeCell ref="D29:F29"/>
-    <mergeCell ref="D30:F30"/>
-    <mergeCell ref="D31:F31"/>
-    <mergeCell ref="D32:F32"/>
-    <mergeCell ref="A27:C27"/>
-    <mergeCell ref="D16:F16"/>
-    <mergeCell ref="D17:F17"/>
-    <mergeCell ref="D18:F18"/>
-    <mergeCell ref="D19:F19"/>
-    <mergeCell ref="A20:C20"/>
-    <mergeCell ref="D21:F21"/>
-    <mergeCell ref="D15:F15"/>
-    <mergeCell ref="I6:K6"/>
-    <mergeCell ref="I7:K7"/>
-    <mergeCell ref="A8:D8"/>
-    <mergeCell ref="A9:A10"/>
-    <mergeCell ref="B9:B10"/>
-    <mergeCell ref="C9:C10"/>
-    <mergeCell ref="D9:G10"/>
-    <mergeCell ref="H9:H10"/>
-    <mergeCell ref="I9:I10"/>
-    <mergeCell ref="J9:J10"/>
-    <mergeCell ref="K9:K10"/>
-    <mergeCell ref="A11:K11"/>
-    <mergeCell ref="A12:K12"/>
-    <mergeCell ref="D13:F13"/>
-    <mergeCell ref="D14:F14"/>
-    <mergeCell ref="B5:D5"/>
-    <mergeCell ref="I5:K5"/>
-    <mergeCell ref="B1:D2"/>
-    <mergeCell ref="B3:D3"/>
-    <mergeCell ref="I3:K3"/>
-    <mergeCell ref="B4:D4"/>
-    <mergeCell ref="I4:K4"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:G22"/>
